--- a/Outcome/Publish/figure_data/fig4.xlsx
+++ b/Outcome/Publish/figure_data/fig4.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="51">
   <si>
     <t xml:space="preserve">disease</t>
   </si>
@@ -53,25 +53,25 @@
     <t xml:space="preserve">Pneumonia</t>
   </si>
   <si>
-    <t xml:space="preserve">ETS</t>
+    <t xml:space="preserve">Hybrid*</t>
   </si>
   <si>
     <t xml:space="preserve">Respiratory IDs</t>
   </si>
   <si>
-    <t xml:space="preserve">TBATS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hybrid*</t>
+    <t xml:space="preserve">Neural Network</t>
   </si>
   <si>
     <t xml:space="preserve">Bayesian structural</t>
   </si>
   <si>
+    <t xml:space="preserve">ETS</t>
+  </si>
+  <si>
     <t xml:space="preserve">SARIMA</t>
   </si>
   <si>
-    <t xml:space="preserve">Neural Network</t>
+    <t xml:space="preserve">TBATS</t>
   </si>
   <si>
     <t xml:space="preserve">Influenza</t>
@@ -102,9 +102,6 @@
   </si>
   <si>
     <t xml:space="preserve">Scrub Typhus</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chikungunya</t>
   </si>
   <si>
     <t xml:space="preserve">Leptospirosis</t>
@@ -542,28 +539,28 @@
         <v>13</v>
       </c>
       <c r="C2" t="n">
-        <v>199.83</v>
+        <v>14.16</v>
       </c>
       <c r="D2" t="n">
-        <v>25033.32</v>
+        <v>4642.13</v>
       </c>
       <c r="E2" t="n">
-        <v>6.39</v>
+        <v>0.95</v>
       </c>
       <c r="F2" t="n">
-        <v>0.58</v>
+        <v>0.47</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.41</v>
+        <v>0.06</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.42</v>
+        <v>0.03</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.22</v>
+        <v>-0.04</v>
       </c>
       <c r="J2" t="n">
-        <v>-1.05</v>
+        <v>0.04</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
@@ -580,28 +577,28 @@
         <v>15</v>
       </c>
       <c r="C3" t="n">
-        <v>199.82</v>
+        <v>16.84</v>
       </c>
       <c r="D3" t="n">
-        <v>23921.41</v>
+        <v>5100.87</v>
       </c>
       <c r="E3" t="n">
-        <v>6.48</v>
+        <v>1.15</v>
       </c>
       <c r="F3" t="n">
-        <v>0.57</v>
+        <v>0.24</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.41</v>
+        <v>-1.01</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.31</v>
+        <v>-0.6</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.26</v>
+        <v>-1.12</v>
       </c>
       <c r="J3" t="n">
-        <v>-0.97</v>
+        <v>-2.73</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
@@ -618,28 +615,28 @@
         <v>16</v>
       </c>
       <c r="C4" t="n">
-        <v>199.83</v>
+        <v>11.86</v>
       </c>
       <c r="D4" t="n">
-        <v>24906.78</v>
+        <v>4119.05</v>
       </c>
       <c r="E4" t="n">
-        <v>7.01</v>
+        <v>0.75</v>
       </c>
       <c r="F4" t="n">
-        <v>0.46</v>
+        <v>0.57</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.41</v>
+        <v>0.98</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.4</v>
+        <v>0.74</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.47</v>
+        <v>0.99</v>
       </c>
       <c r="J4" t="n">
-        <v>-1.28</v>
+        <v>2.71</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
@@ -656,31 +653,31 @@
         <v>17</v>
       </c>
       <c r="C5" t="n">
-        <v>1.14</v>
+        <v>13.78</v>
       </c>
       <c r="D5" t="n">
-        <v>0.16</v>
+        <v>4515.34</v>
       </c>
       <c r="E5" t="n">
-        <v>0.74</v>
+        <v>0.86</v>
       </c>
       <c r="F5" t="n">
         <v>0.59</v>
       </c>
       <c r="G5" t="n">
-        <v>2.04</v>
+        <v>0.21</v>
       </c>
       <c r="H5" t="n">
-        <v>2.04</v>
+        <v>0.2</v>
       </c>
       <c r="I5" t="n">
-        <v>2.02</v>
+        <v>0.41</v>
       </c>
       <c r="J5" t="n">
-        <v>6.1</v>
+        <v>0.82</v>
       </c>
       <c r="K5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L5" t="s">
         <v>14</v>
@@ -694,28 +691,28 @@
         <v>18</v>
       </c>
       <c r="C6" t="n">
-        <v>199.84</v>
+        <v>17.64</v>
       </c>
       <c r="D6" t="n">
-        <v>26063.07</v>
+        <v>5826.04</v>
       </c>
       <c r="E6" t="n">
-        <v>7.11</v>
+        <v>1.18</v>
       </c>
       <c r="F6" t="n">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.41</v>
+        <v>-1.33</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.52</v>
+        <v>-1.59</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.51</v>
+        <v>-1.25</v>
       </c>
       <c r="J6" t="n">
-        <v>-1.43</v>
+        <v>-4.18</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
@@ -732,31 +729,31 @@
         <v>19</v>
       </c>
       <c r="C7" t="n">
-        <v>199.83</v>
+        <v>11.59</v>
       </c>
       <c r="D7" t="n">
-        <v>24816.74</v>
+        <v>3760.98</v>
       </c>
       <c r="E7" t="n">
-        <v>7.27</v>
+        <v>0.75</v>
       </c>
       <c r="F7" t="n">
-        <v>0.23</v>
+        <v>0.57</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.41</v>
+        <v>1.09</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.39</v>
+        <v>1.23</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.57</v>
+        <v>1.02</v>
       </c>
       <c r="J7" t="n">
-        <v>-1.37</v>
+        <v>3.34</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L7" t="s">
         <v>14</v>
@@ -767,34 +764,34 @@
         <v>20</v>
       </c>
       <c r="B8" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C8" t="n">
-        <v>16.27</v>
+        <v>101.28</v>
       </c>
       <c r="D8" t="n">
-        <v>2.34</v>
+        <v>25326.8</v>
       </c>
       <c r="E8" t="n">
-        <v>4.86</v>
+        <v>18.85</v>
       </c>
       <c r="F8" t="n">
-        <v>0.01</v>
+        <v>0.5</v>
       </c>
       <c r="G8" t="n">
-        <v>2.04</v>
+        <v>-0.95</v>
       </c>
       <c r="H8" t="n">
-        <v>1.54</v>
+        <v>0.38</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.3</v>
+        <v>-2.02</v>
       </c>
       <c r="J8" t="n">
-        <v>3.28</v>
+        <v>-2.6</v>
       </c>
       <c r="K8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L8" t="s">
         <v>14</v>
@@ -805,31 +802,31 @@
         <v>20</v>
       </c>
       <c r="B9" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="C9" t="n">
-        <v>199.76</v>
+        <v>57.57</v>
       </c>
       <c r="D9" t="n">
-        <v>21922.41</v>
+        <v>17168.21</v>
       </c>
       <c r="E9" t="n">
-        <v>3.52</v>
+        <v>2.52</v>
       </c>
       <c r="F9" t="n">
-        <v>0.31</v>
+        <v>0.33</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.41</v>
+        <v>0.48</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.31</v>
+        <v>0.41</v>
       </c>
       <c r="I9" t="n">
-        <v>0.31</v>
+        <v>0.39</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.41</v>
+        <v>1.27</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
@@ -846,28 +843,28 @@
         <v>16</v>
       </c>
       <c r="C10" t="n">
-        <v>199.73</v>
+        <v>119.84</v>
       </c>
       <c r="D10" t="n">
-        <v>20195.7</v>
+        <v>583636.71</v>
       </c>
       <c r="E10" t="n">
-        <v>3.33</v>
+        <v>4.08</v>
       </c>
       <c r="F10" t="n">
-        <v>0.4</v>
+        <v>0.02</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.41</v>
+        <v>-1.56</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.16</v>
+        <v>-2.04</v>
       </c>
       <c r="I10" t="n">
-        <v>0.39</v>
+        <v>0.16</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.17</v>
+        <v>-3.45</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
@@ -881,31 +878,31 @@
         <v>20</v>
       </c>
       <c r="B11" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="C11" t="n">
-        <v>199.8</v>
+        <v>55.67</v>
       </c>
       <c r="D11" t="n">
-        <v>34755.34</v>
+        <v>15505.1</v>
       </c>
       <c r="E11" t="n">
-        <v>2.45</v>
+        <v>1.81</v>
       </c>
       <c r="F11" t="n">
-        <v>0.21</v>
+        <v>0.47</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.41</v>
+        <v>0.54</v>
       </c>
       <c r="H11" t="n">
-        <v>-1.39</v>
+        <v>0.42</v>
       </c>
       <c r="I11" t="n">
-        <v>0.8</v>
+        <v>0.49</v>
       </c>
       <c r="J11" t="n">
-        <v>-1</v>
+        <v>1.45</v>
       </c>
       <c r="K11" t="n">
         <v>0</v>
@@ -919,34 +916,34 @@
         <v>20</v>
       </c>
       <c r="B12" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C12" t="n">
-        <v>199.73</v>
+        <v>46.61</v>
       </c>
       <c r="D12" t="n">
-        <v>22504.1</v>
+        <v>17747.28</v>
       </c>
       <c r="E12" t="n">
-        <v>2.69</v>
+        <v>1.17</v>
       </c>
       <c r="F12" t="n">
-        <v>0.52</v>
+        <v>0.18</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.41</v>
+        <v>0.83</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.36</v>
+        <v>0.41</v>
       </c>
       <c r="I12" t="n">
-        <v>0.69</v>
+        <v>0.58</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.08</v>
+        <v>1.83</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L12" t="s">
         <v>14</v>
@@ -957,31 +954,31 @@
         <v>20</v>
       </c>
       <c r="B13" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C13" t="n">
-        <v>199.58</v>
+        <v>51.69</v>
       </c>
       <c r="D13" t="n">
-        <v>10300.74</v>
+        <v>16621.43</v>
       </c>
       <c r="E13" t="n">
-        <v>8.34</v>
+        <v>2.38</v>
       </c>
       <c r="F13" t="n">
-        <v>0.58</v>
+        <v>0.26</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.41</v>
+        <v>0.67</v>
       </c>
       <c r="H13" t="n">
-        <v>0.67</v>
+        <v>0.42</v>
       </c>
       <c r="I13" t="n">
-        <v>-1.89</v>
+        <v>0.41</v>
       </c>
       <c r="J13" t="n">
-        <v>-1.62</v>
+        <v>1.49</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
@@ -995,34 +992,34 @@
         <v>21</v>
       </c>
       <c r="B14" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C14" t="n">
-        <v>199.25</v>
+        <v>21.29</v>
       </c>
       <c r="D14" t="n">
-        <v>6244.33</v>
+        <v>1201.94</v>
       </c>
       <c r="E14" t="n">
-        <v>4.4</v>
+        <v>1.13</v>
       </c>
       <c r="F14" t="n">
-        <v>0.94</v>
+        <v>0.93</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.41</v>
+        <v>1.04</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.35</v>
+        <v>1.6</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.37</v>
+        <v>0.77</v>
       </c>
       <c r="J14" t="n">
-        <v>-1.12</v>
+        <v>3.42</v>
       </c>
       <c r="K14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L14" t="s">
         <v>14</v>
@@ -1033,31 +1030,31 @@
         <v>21</v>
       </c>
       <c r="B15" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C15" t="n">
-        <v>199.24</v>
+        <v>21.95</v>
       </c>
       <c r="D15" t="n">
-        <v>5310.52</v>
+        <v>2067.97</v>
       </c>
       <c r="E15" t="n">
-        <v>5.61</v>
+        <v>1.08</v>
       </c>
       <c r="F15" t="n">
-        <v>0.91</v>
+        <v>0.97</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.41</v>
+        <v>0.94</v>
       </c>
       <c r="H15" t="n">
-        <v>0</v>
+        <v>0.52</v>
       </c>
       <c r="I15" t="n">
-        <v>-1.38</v>
+        <v>1.1</v>
       </c>
       <c r="J15" t="n">
-        <v>-1.79</v>
+        <v>2.56</v>
       </c>
       <c r="K15" t="n">
         <v>0</v>
@@ -1071,31 +1068,31 @@
         <v>21</v>
       </c>
       <c r="B16" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="C16" t="n">
-        <v>199.21</v>
+        <v>24.36</v>
       </c>
       <c r="D16" t="n">
-        <v>6088.57</v>
+        <v>2236.26</v>
       </c>
       <c r="E16" t="n">
-        <v>4.21</v>
+        <v>1.15</v>
       </c>
       <c r="F16" t="n">
-        <v>0.95</v>
+        <v>0.96</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.41</v>
+        <v>0.57</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.29</v>
+        <v>0.31</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.21</v>
+        <v>0.64</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.91</v>
+        <v>1.53</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
@@ -1109,31 +1106,31 @@
         <v>21</v>
       </c>
       <c r="B17" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>199.29</v>
+        <v>37.15</v>
       </c>
       <c r="D17" t="n">
-        <v>7252.87</v>
+        <v>3190.05</v>
       </c>
       <c r="E17" t="n">
-        <v>3.8</v>
+        <v>1.45</v>
       </c>
       <c r="F17" t="n">
-        <v>0.94</v>
+        <v>0.96</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.41</v>
+        <v>-1.38</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.72</v>
+        <v>-0.88</v>
       </c>
       <c r="I17" t="n">
-        <v>0.13</v>
+        <v>-1.42</v>
       </c>
       <c r="J17" t="n">
-        <v>-1</v>
+        <v>-3.67</v>
       </c>
       <c r="K17" t="n">
         <v>0</v>
@@ -1147,31 +1144,31 @@
         <v>21</v>
       </c>
       <c r="B18" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>199.27</v>
+        <v>33.53</v>
       </c>
       <c r="D18" t="n">
-        <v>6966.68</v>
+        <v>3256.09</v>
       </c>
       <c r="E18" t="n">
-        <v>3.8</v>
+        <v>1.37</v>
       </c>
       <c r="F18" t="n">
-        <v>0.94</v>
+        <v>0.96</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.41</v>
+        <v>-0.82</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.62</v>
+        <v>-0.96</v>
       </c>
       <c r="I18" t="n">
-        <v>0.13</v>
+        <v>-0.86</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.9</v>
+        <v>-2.64</v>
       </c>
       <c r="K18" t="n">
         <v>0</v>
@@ -1185,34 +1182,34 @@
         <v>21</v>
       </c>
       <c r="B19" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C19" t="n">
-        <v>4.32</v>
+        <v>30.49</v>
       </c>
       <c r="D19" t="n">
-        <v>0.42</v>
+        <v>2968.22</v>
       </c>
       <c r="E19" t="n">
-        <v>1.92</v>
+        <v>1.28</v>
       </c>
       <c r="F19" t="n">
-        <v>0.95</v>
+        <v>0.97</v>
       </c>
       <c r="G19" t="n">
-        <v>2.04</v>
+        <v>-0.36</v>
       </c>
       <c r="H19" t="n">
-        <v>1.97</v>
+        <v>-0.6</v>
       </c>
       <c r="I19" t="n">
-        <v>1.7</v>
+        <v>-0.23</v>
       </c>
       <c r="J19" t="n">
-        <v>5.71</v>
+        <v>-1.19</v>
       </c>
       <c r="K19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L19" t="s">
         <v>14</v>
@@ -1223,31 +1220,31 @@
         <v>22</v>
       </c>
       <c r="B20" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C20" t="n">
-        <v>187.82</v>
+        <v>24.48</v>
       </c>
       <c r="D20" t="n">
-        <v>167.38</v>
+        <v>56.77</v>
       </c>
       <c r="E20" t="n">
-        <v>11.92</v>
+        <v>4.96</v>
       </c>
       <c r="F20" t="n">
-        <v>0.51</v>
+        <v>0.7</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.41</v>
+        <v>-0.08</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.48</v>
+        <v>-0.08</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.26</v>
+        <v>-1.39</v>
       </c>
       <c r="J20" t="n">
-        <v>-1.15</v>
+        <v>-1.55</v>
       </c>
       <c r="K20" t="n">
         <v>0</v>
@@ -1261,31 +1258,31 @@
         <v>22</v>
       </c>
       <c r="B21" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="C21" t="n">
-        <v>187.16</v>
+        <v>33.51</v>
       </c>
       <c r="D21" t="n">
-        <v>157.17</v>
+        <v>71.07</v>
       </c>
       <c r="E21" t="n">
-        <v>15.96</v>
+        <v>4.66</v>
       </c>
       <c r="F21" t="n">
-        <v>0.73</v>
+        <v>0.29</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.4</v>
+        <v>-1.95</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.33</v>
+        <v>-1.94</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.27</v>
+        <v>-1.08</v>
       </c>
       <c r="J21" t="n">
-        <v>-2</v>
+        <v>-4.97</v>
       </c>
       <c r="K21" t="n">
         <v>0</v>
@@ -1299,31 +1296,31 @@
         <v>22</v>
       </c>
       <c r="B22" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C22" t="n">
-        <v>187.52</v>
+        <v>21.78</v>
       </c>
       <c r="D22" t="n">
-        <v>163.14</v>
+        <v>52.36</v>
       </c>
       <c r="E22" t="n">
-        <v>10.93</v>
+        <v>3.52</v>
       </c>
       <c r="F22" t="n">
-        <v>0.39</v>
+        <v>0.58</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.41</v>
+        <v>0.48</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.42</v>
+        <v>0.5</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.01</v>
+        <v>0.12</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.84</v>
+        <v>1.1</v>
       </c>
       <c r="K22" t="n">
         <v>0</v>
@@ -1337,31 +1334,31 @@
         <v>22</v>
       </c>
       <c r="B23" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C23" t="n">
-        <v>187.32</v>
+        <v>22.04</v>
       </c>
       <c r="D23" t="n">
-        <v>162.01</v>
+        <v>54.6</v>
       </c>
       <c r="E23" t="n">
-        <v>9.8</v>
+        <v>2.99</v>
       </c>
       <c r="F23" t="n">
-        <v>0.6</v>
+        <v>0.35</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.41</v>
+        <v>0.43</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.4</v>
+        <v>0.2</v>
       </c>
       <c r="I23" t="n">
-        <v>0.27</v>
+        <v>0.67</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.54</v>
+        <v>1.3</v>
       </c>
       <c r="K23" t="n">
         <v>0</v>
@@ -1378,28 +1375,28 @@
         <v>17</v>
       </c>
       <c r="C24" t="n">
-        <v>6.77</v>
+        <v>20.01</v>
       </c>
       <c r="D24" t="n">
-        <v>0.39</v>
+        <v>49.74</v>
       </c>
       <c r="E24" t="n">
-        <v>3.92</v>
+        <v>2.92</v>
       </c>
       <c r="F24" t="n">
-        <v>0.36</v>
+        <v>0.47</v>
       </c>
       <c r="G24" t="n">
-        <v>2.04</v>
+        <v>0.85</v>
       </c>
       <c r="H24" t="n">
-        <v>2.04</v>
+        <v>0.84</v>
       </c>
       <c r="I24" t="n">
-        <v>1.74</v>
+        <v>0.74</v>
       </c>
       <c r="J24" t="n">
-        <v>5.82</v>
+        <v>2.43</v>
       </c>
       <c r="K24" t="n">
         <v>1</v>
@@ -1413,31 +1410,31 @@
         <v>22</v>
       </c>
       <c r="B25" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C25" t="n">
-        <v>187.51</v>
+        <v>22.78</v>
       </c>
       <c r="D25" t="n">
-        <v>162.82</v>
+        <v>52.43</v>
       </c>
       <c r="E25" t="n">
-        <v>12.75</v>
+        <v>2.74</v>
       </c>
       <c r="F25" t="n">
         <v>0.6</v>
       </c>
       <c r="G25" t="n">
-        <v>-0.41</v>
+        <v>0.27</v>
       </c>
       <c r="H25" t="n">
-        <v>-0.41</v>
+        <v>0.49</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.47</v>
+        <v>0.94</v>
       </c>
       <c r="J25" t="n">
-        <v>-1.29</v>
+        <v>1.69</v>
       </c>
       <c r="K25" t="n">
         <v>0</v>
@@ -1451,34 +1448,34 @@
         <v>23</v>
       </c>
       <c r="B26" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C26" t="n">
-        <v>197.79</v>
+        <v>23.76</v>
       </c>
       <c r="D26" t="n">
-        <v>1143.23</v>
+        <v>159.37</v>
       </c>
       <c r="E26" t="n">
-        <v>12.72</v>
+        <v>3.06</v>
       </c>
       <c r="F26" t="n">
-        <v>0.23</v>
+        <v>0.04</v>
       </c>
       <c r="G26" t="n">
-        <v>-0.42</v>
+        <v>1.22</v>
       </c>
       <c r="H26" t="n">
-        <v>-0.81</v>
+        <v>0.77</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.08</v>
+        <v>1.39</v>
       </c>
       <c r="J26" t="n">
-        <v>-1.31</v>
+        <v>3.39</v>
       </c>
       <c r="K26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L26" t="s">
         <v>14</v>
@@ -1489,25 +1486,31 @@
         <v>23</v>
       </c>
       <c r="B27" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="C27" t="n">
-        <v>197.28</v>
+        <v>46.94</v>
       </c>
       <c r="D27" t="n">
-        <v>912.72</v>
-      </c>
-      <c r="E27"/>
-      <c r="F27"/>
+        <v>347.11</v>
+      </c>
+      <c r="E27" t="n">
+        <v>6.07</v>
+      </c>
+      <c r="F27" t="n">
+        <v>0.04</v>
+      </c>
       <c r="G27" t="n">
-        <v>-0.41</v>
+        <v>0.54</v>
       </c>
       <c r="H27" t="n">
-        <v>-0.31</v>
-      </c>
-      <c r="I27"/>
+        <v>0.52</v>
+      </c>
+      <c r="I27" t="n">
+        <v>-0.4</v>
+      </c>
       <c r="J27" t="n">
-        <v>-0.73</v>
+        <v>0.66</v>
       </c>
       <c r="K27" t="n">
         <v>0</v>
@@ -1524,28 +1527,28 @@
         <v>16</v>
       </c>
       <c r="C28" t="n">
-        <v>197.16</v>
+        <v>123.87</v>
       </c>
       <c r="D28" t="n">
-        <v>880.65</v>
+        <v>2187.75</v>
       </c>
       <c r="E28" t="n">
-        <v>18.52</v>
+        <v>7</v>
       </c>
       <c r="F28" t="n">
-        <v>0.23</v>
+        <v>0.37</v>
       </c>
       <c r="G28" t="n">
-        <v>-0.41</v>
+        <v>-1.71</v>
       </c>
       <c r="H28" t="n">
-        <v>-0.24</v>
+        <v>-1.97</v>
       </c>
       <c r="I28" t="n">
-        <v>-1.56</v>
+        <v>-0.95</v>
       </c>
       <c r="J28" t="n">
-        <v>-2.22</v>
+        <v>-4.64</v>
       </c>
       <c r="K28" t="n">
         <v>0</v>
@@ -1559,31 +1562,31 @@
         <v>23</v>
       </c>
       <c r="B29" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="C29" t="n">
-        <v>197.9</v>
+        <v>75.41</v>
       </c>
       <c r="D29" t="n">
-        <v>1215.63</v>
+        <v>682.16</v>
       </c>
       <c r="E29" t="n">
-        <v>7.77</v>
+        <v>4.25</v>
       </c>
       <c r="F29" t="n">
-        <v>0.14</v>
+        <v>0.1</v>
       </c>
       <c r="G29" t="n">
-        <v>-0.42</v>
+        <v>-0.29</v>
       </c>
       <c r="H29" t="n">
-        <v>-0.97</v>
+        <v>0.06</v>
       </c>
       <c r="I29" t="n">
-        <v>1.19</v>
+        <v>0.68</v>
       </c>
       <c r="J29" t="n">
-        <v>-0.21</v>
+        <v>0.45</v>
       </c>
       <c r="K29" t="n">
         <v>0</v>
@@ -1600,31 +1603,31 @@
         <v>17</v>
       </c>
       <c r="C30" t="n">
-        <v>21.38</v>
+        <v>70.98</v>
       </c>
       <c r="D30" t="n">
-        <v>1.58</v>
+        <v>606.05</v>
       </c>
       <c r="E30" t="n">
-        <v>12.13</v>
+        <v>6.62</v>
       </c>
       <c r="F30" t="n">
-        <v>0.41</v>
+        <v>0.19</v>
       </c>
       <c r="G30" t="n">
-        <v>2.04</v>
+        <v>-0.16</v>
       </c>
       <c r="H30" t="n">
-        <v>1.66</v>
+        <v>0.17</v>
       </c>
       <c r="I30" t="n">
-        <v>0.07</v>
+        <v>-0.73</v>
       </c>
       <c r="J30" t="n">
-        <v>3.78</v>
+        <v>-0.72</v>
       </c>
       <c r="K30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L30" t="s">
         <v>14</v>
@@ -1635,31 +1638,25 @@
         <v>23</v>
       </c>
       <c r="B31" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C31" t="n">
-        <v>194.46</v>
+        <v>51.76</v>
       </c>
       <c r="D31" t="n">
-        <v>455.07</v>
-      </c>
-      <c r="E31" t="n">
-        <v>10.92</v>
-      </c>
-      <c r="F31" t="n">
-        <v>0.06</v>
-      </c>
+        <v>388.27</v>
+      </c>
+      <c r="E31"/>
+      <c r="F31"/>
       <c r="G31" t="n">
-        <v>-0.37</v>
+        <v>0.4</v>
       </c>
       <c r="H31" t="n">
-        <v>0.68</v>
-      </c>
-      <c r="I31" t="n">
-        <v>0.38</v>
-      </c>
+        <v>0.46</v>
+      </c>
+      <c r="I31"/>
       <c r="J31" t="n">
-        <v>0.69</v>
+        <v>0.86</v>
       </c>
       <c r="K31" t="n">
         <v>0</v>
@@ -1673,34 +1670,34 @@
         <v>24</v>
       </c>
       <c r="B32" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C32" t="n">
-        <v>7.35</v>
+        <v>40.2</v>
       </c>
       <c r="D32" t="n">
-        <v>0.45</v>
+        <v>96.77</v>
       </c>
       <c r="E32" t="n">
-        <v>1.67</v>
+        <v>1.83</v>
       </c>
       <c r="F32" t="n">
-        <v>0.59</v>
+        <v>0.49</v>
       </c>
       <c r="G32" t="n">
-        <v>2.04</v>
+        <v>-0.99</v>
       </c>
       <c r="H32" t="n">
-        <v>2.02</v>
+        <v>-0.79</v>
       </c>
       <c r="I32" t="n">
-        <v>1.96</v>
+        <v>-1.61</v>
       </c>
       <c r="J32" t="n">
-        <v>6.03</v>
+        <v>-3.38</v>
       </c>
       <c r="K32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L32" t="s">
         <v>14</v>
@@ -1714,28 +1711,28 @@
         <v>18</v>
       </c>
       <c r="C33" t="n">
-        <v>191.99</v>
+        <v>34.81</v>
       </c>
       <c r="D33" t="n">
-        <v>277.76</v>
+        <v>87.41</v>
       </c>
       <c r="E33" t="n">
-        <v>4.5</v>
+        <v>1.3</v>
       </c>
       <c r="F33" t="n">
-        <v>0.66</v>
+        <v>0.73</v>
       </c>
       <c r="G33" t="n">
-        <v>-0.41</v>
+        <v>-0.02</v>
       </c>
       <c r="H33" t="n">
-        <v>-0.5</v>
+        <v>-0.07</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.08</v>
+        <v>0.29</v>
       </c>
       <c r="J33" t="n">
-        <v>-0.99</v>
+        <v>0.2</v>
       </c>
       <c r="K33" t="n">
         <v>0</v>
@@ -1749,34 +1746,34 @@
         <v>24</v>
       </c>
       <c r="B34" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="C34" t="n">
-        <v>190.98</v>
+        <v>24.59</v>
       </c>
       <c r="D34" t="n">
-        <v>239.97</v>
+        <v>63.37</v>
       </c>
       <c r="E34" t="n">
-        <v>4.64</v>
+        <v>0.96</v>
       </c>
       <c r="F34" t="n">
-        <v>0.57</v>
+        <v>0.55</v>
       </c>
       <c r="G34" t="n">
-        <v>-0.4</v>
+        <v>1.83</v>
       </c>
       <c r="H34" t="n">
-        <v>-0.16</v>
+        <v>1.75</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.18</v>
+        <v>1.51</v>
       </c>
       <c r="J34" t="n">
-        <v>-0.73</v>
+        <v>5.09</v>
       </c>
       <c r="K34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L34" t="s">
         <v>14</v>
@@ -1787,31 +1784,31 @@
         <v>24</v>
       </c>
       <c r="B35" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="C35" t="n">
-        <v>192.18</v>
+        <v>36.23</v>
       </c>
       <c r="D35" t="n">
-        <v>273.96</v>
+        <v>92.08</v>
       </c>
       <c r="E35" t="n">
-        <v>4.99</v>
+        <v>1.45</v>
       </c>
       <c r="F35" t="n">
-        <v>0.54</v>
+        <v>0.5</v>
       </c>
       <c r="G35" t="n">
-        <v>-0.41</v>
+        <v>-0.27</v>
       </c>
       <c r="H35" t="n">
-        <v>-0.47</v>
+        <v>-0.43</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.43</v>
+        <v>-0.25</v>
       </c>
       <c r="J35" t="n">
-        <v>-1.31</v>
+        <v>-0.95</v>
       </c>
       <c r="K35" t="n">
         <v>0</v>
@@ -1825,31 +1822,31 @@
         <v>24</v>
       </c>
       <c r="B36" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="C36" t="n">
-        <v>192.26</v>
+        <v>38.87</v>
       </c>
       <c r="D36" t="n">
-        <v>278.91</v>
+        <v>98.87</v>
       </c>
       <c r="E36" t="n">
-        <v>5.62</v>
+        <v>1.36</v>
       </c>
       <c r="F36" t="n">
-        <v>0.44</v>
+        <v>0.58</v>
       </c>
       <c r="G36" t="n">
-        <v>-0.41</v>
+        <v>-0.75</v>
       </c>
       <c r="H36" t="n">
-        <v>-0.51</v>
+        <v>-0.94</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.88</v>
+        <v>0.07</v>
       </c>
       <c r="J36" t="n">
-        <v>-1.8</v>
+        <v>-1.63</v>
       </c>
       <c r="K36" t="n">
         <v>0</v>
@@ -1863,31 +1860,31 @@
         <v>24</v>
       </c>
       <c r="B37" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C37" t="n">
-        <v>191.87</v>
+        <v>33.56</v>
       </c>
       <c r="D37" t="n">
-        <v>265.86</v>
+        <v>80.12</v>
       </c>
       <c r="E37" t="n">
-        <v>4.94</v>
+        <v>1.38</v>
       </c>
       <c r="F37" t="n">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="G37" t="n">
-        <v>-0.41</v>
+        <v>0.21</v>
       </c>
       <c r="H37" t="n">
-        <v>-0.39</v>
+        <v>0.48</v>
       </c>
       <c r="I37" t="n">
-        <v>-0.39</v>
+        <v>0</v>
       </c>
       <c r="J37" t="n">
-        <v>-1.19</v>
+        <v>0.68</v>
       </c>
       <c r="K37" t="n">
         <v>0</v>
@@ -1901,31 +1898,25 @@
         <v>25</v>
       </c>
       <c r="B38" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C38" t="n">
-        <v>166.84</v>
+        <v>29.9</v>
       </c>
       <c r="D38" t="n">
-        <v>35.74</v>
-      </c>
-      <c r="E38" t="n">
-        <v>8.2</v>
-      </c>
-      <c r="F38" t="n">
-        <v>0.2</v>
-      </c>
+        <v>12.07</v>
+      </c>
+      <c r="E38"/>
+      <c r="F38"/>
       <c r="G38" t="n">
-        <v>-0.48</v>
+        <v>0.15</v>
       </c>
       <c r="H38" t="n">
-        <v>-0.79</v>
-      </c>
-      <c r="I38" t="n">
-        <v>0.58</v>
-      </c>
+        <v>0.14</v>
+      </c>
+      <c r="I38"/>
       <c r="J38" t="n">
-        <v>-0.69</v>
+        <v>0.29</v>
       </c>
       <c r="K38" t="n">
         <v>0</v>
@@ -1939,34 +1930,34 @@
         <v>25</v>
       </c>
       <c r="B39" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C39" t="n">
-        <v>9.91</v>
+        <v>34.72</v>
       </c>
       <c r="D39" t="n">
-        <v>0.41</v>
+        <v>14.56</v>
       </c>
       <c r="E39" t="n">
-        <v>1.58</v>
+        <v>1.24</v>
       </c>
       <c r="F39" t="n">
-        <v>0.37</v>
+        <v>0.3</v>
       </c>
       <c r="G39" t="n">
-        <v>2.04</v>
+        <v>-1.93</v>
       </c>
       <c r="H39" t="n">
-        <v>1.97</v>
+        <v>-1.75</v>
       </c>
       <c r="I39" t="n">
-        <v>1.12</v>
+        <v>0.9</v>
       </c>
       <c r="J39" t="n">
-        <v>5.13</v>
+        <v>-2.78</v>
       </c>
       <c r="K39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L39" t="s">
         <v>14</v>
@@ -1980,28 +1971,28 @@
         <v>19</v>
       </c>
       <c r="C40" t="n">
-        <v>157.01</v>
+        <v>30.34</v>
       </c>
       <c r="D40" t="n">
-        <v>25.44</v>
+        <v>11.83</v>
       </c>
       <c r="E40" t="n">
-        <v>32.39</v>
+        <v>2.47</v>
       </c>
       <c r="F40" t="n">
-        <v>0.1</v>
+        <v>0.15</v>
       </c>
       <c r="G40" t="n">
-        <v>-0.32</v>
+        <v>-0.04</v>
       </c>
       <c r="H40" t="n">
-        <v>0.01</v>
+        <v>0.32</v>
       </c>
       <c r="I40" t="n">
-        <v>-1.41</v>
+        <v>0.64</v>
       </c>
       <c r="J40" t="n">
-        <v>-1.71</v>
+        <v>0.92</v>
       </c>
       <c r="K40" t="n">
         <v>0</v>
@@ -2015,25 +2006,31 @@
         <v>25</v>
       </c>
       <c r="B41" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C41" t="n">
-        <v>161.32</v>
+        <v>29.55</v>
       </c>
       <c r="D41" t="n">
-        <v>29.01</v>
-      </c>
-      <c r="E41"/>
-      <c r="F41"/>
+        <v>12.9</v>
+      </c>
+      <c r="E41" t="n">
+        <v>12.95</v>
+      </c>
+      <c r="F41" t="n">
+        <v>0.08</v>
+      </c>
       <c r="G41" t="n">
-        <v>-0.39</v>
+        <v>0.3</v>
       </c>
       <c r="H41" t="n">
-        <v>-0.27</v>
-      </c>
-      <c r="I41"/>
+        <v>-0.49</v>
+      </c>
+      <c r="I41" t="n">
+        <v>-1.57</v>
+      </c>
       <c r="J41" t="n">
-        <v>-0.65</v>
+        <v>-1.76</v>
       </c>
       <c r="K41" t="n">
         <v>0</v>
@@ -2047,31 +2044,31 @@
         <v>25</v>
       </c>
       <c r="B42" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C42" t="n">
-        <v>163.28</v>
+        <v>28.56</v>
       </c>
       <c r="D42" t="n">
-        <v>30.94</v>
+        <v>11.13</v>
       </c>
       <c r="E42" t="n">
-        <v>22.43</v>
+        <v>7.33</v>
       </c>
       <c r="F42" t="n">
-        <v>0.36</v>
+        <v>0.3</v>
       </c>
       <c r="G42" t="n">
-        <v>-0.42</v>
+        <v>0.73</v>
       </c>
       <c r="H42" t="n">
-        <v>-0.42</v>
+        <v>0.85</v>
       </c>
       <c r="I42" t="n">
-        <v>-0.59</v>
+        <v>-0.39</v>
       </c>
       <c r="J42" t="n">
-        <v>-1.43</v>
+        <v>1.2</v>
       </c>
       <c r="K42" t="n">
         <v>0</v>
@@ -2088,31 +2085,31 @@
         <v>18</v>
       </c>
       <c r="C43" t="n">
-        <v>164.21</v>
+        <v>28.45</v>
       </c>
       <c r="D43" t="n">
-        <v>32.09</v>
+        <v>11.04</v>
       </c>
       <c r="E43" t="n">
-        <v>11.58</v>
+        <v>3.51</v>
       </c>
       <c r="F43" t="n">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="G43" t="n">
-        <v>-0.43</v>
+        <v>0.78</v>
       </c>
       <c r="H43" t="n">
-        <v>-0.51</v>
+        <v>0.92</v>
       </c>
       <c r="I43" t="n">
-        <v>0.3</v>
+        <v>0.42</v>
       </c>
       <c r="J43" t="n">
-        <v>-0.64</v>
+        <v>2.12</v>
       </c>
       <c r="K43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L43" t="s">
         <v>14</v>
@@ -2123,31 +2120,31 @@
         <v>26</v>
       </c>
       <c r="B44" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="C44" t="n">
-        <v>199.52</v>
+        <v>14.81</v>
       </c>
       <c r="D44" t="n">
-        <v>11460.88</v>
+        <v>1990.08</v>
       </c>
       <c r="E44" t="n">
-        <v>3.61</v>
+        <v>0.62</v>
       </c>
       <c r="F44" t="n">
-        <v>0.93</v>
+        <v>0.96</v>
       </c>
       <c r="G44" t="n">
-        <v>-0.41</v>
+        <v>0.85</v>
       </c>
       <c r="H44" t="n">
-        <v>-0.54</v>
+        <v>0.55</v>
       </c>
       <c r="I44" t="n">
-        <v>-0.16</v>
+        <v>0.74</v>
       </c>
       <c r="J44" t="n">
-        <v>-1.11</v>
+        <v>2.14</v>
       </c>
       <c r="K44" t="n">
         <v>0</v>
@@ -2161,34 +2158,34 @@
         <v>26</v>
       </c>
       <c r="B45" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="C45" t="n">
-        <v>9.17</v>
+        <v>21.94</v>
       </c>
       <c r="D45" t="n">
-        <v>1.08</v>
+        <v>3055.78</v>
       </c>
       <c r="E45" t="n">
-        <v>3.36</v>
+        <v>0.93</v>
       </c>
       <c r="F45" t="n">
-        <v>0.6</v>
+        <v>0.93</v>
       </c>
       <c r="G45" t="n">
-        <v>2.04</v>
+        <v>0.56</v>
       </c>
       <c r="H45" t="n">
-        <v>1.83</v>
+        <v>0.44</v>
       </c>
       <c r="I45" t="n">
-        <v>0.23</v>
+        <v>0.46</v>
       </c>
       <c r="J45" t="n">
-        <v>4.09</v>
+        <v>1.47</v>
       </c>
       <c r="K45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L45" t="s">
         <v>27</v>
@@ -2199,31 +2196,31 @@
         <v>26</v>
       </c>
       <c r="B46" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C46" t="n">
-        <v>199.37</v>
+        <v>46.67</v>
       </c>
       <c r="D46" t="n">
-        <v>7155.12</v>
+        <v>5151.77</v>
       </c>
       <c r="E46" t="n">
-        <v>4.22</v>
+        <v>0.93</v>
       </c>
       <c r="F46" t="n">
-        <v>0.89</v>
+        <v>0.65</v>
       </c>
       <c r="G46" t="n">
         <v>-0.41</v>
       </c>
       <c r="H46" t="n">
-        <v>0.35</v>
+        <v>0.23</v>
       </c>
       <c r="I46" t="n">
-        <v>-1.1</v>
+        <v>0.46</v>
       </c>
       <c r="J46" t="n">
-        <v>-1.17</v>
+        <v>0.27</v>
       </c>
       <c r="K46" t="n">
         <v>0</v>
@@ -2237,31 +2234,31 @@
         <v>26</v>
       </c>
       <c r="B47" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C47" t="n">
-        <v>199.47</v>
+        <v>40.97</v>
       </c>
       <c r="D47" t="n">
-        <v>9733.98</v>
+        <v>5545.28</v>
       </c>
       <c r="E47" t="n">
-        <v>3.51</v>
+        <v>2.72</v>
       </c>
       <c r="F47" t="n">
-        <v>0.86</v>
+        <v>0.92</v>
       </c>
       <c r="G47" t="n">
-        <v>-0.41</v>
+        <v>-0.19</v>
       </c>
       <c r="H47" t="n">
-        <v>-0.19</v>
+        <v>0.19</v>
       </c>
       <c r="I47" t="n">
-        <v>0</v>
+        <v>-1.21</v>
       </c>
       <c r="J47" t="n">
-        <v>-0.6</v>
+        <v>-1.21</v>
       </c>
       <c r="K47" t="n">
         <v>0</v>
@@ -2275,31 +2272,31 @@
         <v>26</v>
       </c>
       <c r="B48" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C48" t="n">
-        <v>199.51</v>
+        <v>79.5</v>
       </c>
       <c r="D48" t="n">
-        <v>10842.11</v>
+        <v>27140.34</v>
       </c>
       <c r="E48" t="n">
-        <v>3.98</v>
+        <v>2.86</v>
       </c>
       <c r="F48" t="n">
-        <v>0.94</v>
+        <v>0.56</v>
       </c>
       <c r="G48" t="n">
-        <v>-0.41</v>
+        <v>-1.71</v>
       </c>
       <c r="H48" t="n">
-        <v>-0.42</v>
+        <v>-2.01</v>
       </c>
       <c r="I48" t="n">
-        <v>-0.74</v>
+        <v>-1.33</v>
       </c>
       <c r="J48" t="n">
-        <v>-1.56</v>
+        <v>-5.06</v>
       </c>
       <c r="K48" t="n">
         <v>0</v>
@@ -2313,34 +2310,34 @@
         <v>26</v>
       </c>
       <c r="B49" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C49" t="n">
-        <v>199.36</v>
+        <v>13.25</v>
       </c>
       <c r="D49" t="n">
-        <v>13765.91</v>
+        <v>1528.12</v>
       </c>
       <c r="E49" t="n">
-        <v>2.37</v>
+        <v>0.46</v>
       </c>
       <c r="F49" t="n">
-        <v>0.53</v>
+        <v>0.96</v>
       </c>
       <c r="G49" t="n">
-        <v>-0.41</v>
+        <v>0.91</v>
       </c>
       <c r="H49" t="n">
-        <v>-1.02</v>
+        <v>0.6</v>
       </c>
       <c r="I49" t="n">
-        <v>1.78</v>
+        <v>0.89</v>
       </c>
       <c r="J49" t="n">
-        <v>0.35</v>
+        <v>2.4</v>
       </c>
       <c r="K49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L49" t="s">
         <v>27</v>
@@ -2351,31 +2348,31 @@
         <v>28</v>
       </c>
       <c r="B50" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C50" t="n">
-        <v>182.26</v>
+        <v>30.9</v>
       </c>
       <c r="D50" t="n">
-        <v>121.98</v>
+        <v>90.2</v>
       </c>
       <c r="E50" t="n">
-        <v>3.66</v>
+        <v>3.61</v>
       </c>
       <c r="F50" t="n">
-        <v>0.84</v>
+        <v>0.77</v>
       </c>
       <c r="G50" t="n">
-        <v>-0.38</v>
+        <v>-0.52</v>
       </c>
       <c r="H50" t="n">
-        <v>-0.13</v>
+        <v>-1.55</v>
       </c>
       <c r="I50" t="n">
-        <v>0.2</v>
+        <v>-1.91</v>
       </c>
       <c r="J50" t="n">
-        <v>-0.31</v>
+        <v>-3.97</v>
       </c>
       <c r="K50" t="n">
         <v>0</v>
@@ -2389,31 +2386,31 @@
         <v>28</v>
       </c>
       <c r="B51" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C51" t="n">
-        <v>185.41</v>
+        <v>27.64</v>
       </c>
       <c r="D51" t="n">
-        <v>150.68</v>
+        <v>67.27</v>
       </c>
       <c r="E51" t="n">
-        <v>3.66</v>
+        <v>1.57</v>
       </c>
       <c r="F51" t="n">
-        <v>0.76</v>
+        <v>0.92</v>
       </c>
       <c r="G51" t="n">
-        <v>-0.42</v>
+        <v>0.24</v>
       </c>
       <c r="H51" t="n">
-        <v>-0.63</v>
+        <v>0.12</v>
       </c>
       <c r="I51" t="n">
-        <v>0.2</v>
+        <v>0.22</v>
       </c>
       <c r="J51" t="n">
-        <v>-0.85</v>
+        <v>0.57</v>
       </c>
       <c r="K51" t="n">
         <v>0</v>
@@ -2427,34 +2424,34 @@
         <v>28</v>
       </c>
       <c r="B52" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C52" t="n">
-        <v>6.61</v>
+        <v>31.44</v>
       </c>
       <c r="D52" t="n">
-        <v>0.36</v>
+        <v>73.25</v>
       </c>
       <c r="E52" t="n">
-        <v>1.35</v>
+        <v>1.68</v>
       </c>
       <c r="F52" t="n">
-        <v>0.88</v>
+        <v>0.91</v>
       </c>
       <c r="G52" t="n">
-        <v>2.04</v>
+        <v>-0.64</v>
       </c>
       <c r="H52" t="n">
-        <v>1.98</v>
+        <v>-0.32</v>
       </c>
       <c r="I52" t="n">
-        <v>1.31</v>
+        <v>0.1</v>
       </c>
       <c r="J52" t="n">
-        <v>5.33</v>
+        <v>-0.86</v>
       </c>
       <c r="K52" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L52" t="s">
         <v>27</v>
@@ -2465,31 +2462,31 @@
         <v>28</v>
       </c>
       <c r="B53" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="C53" t="n">
-        <v>184.49</v>
+        <v>24.75</v>
       </c>
       <c r="D53" t="n">
-        <v>135.23</v>
+        <v>55.03</v>
       </c>
       <c r="E53" t="n">
-        <v>4.23</v>
+        <v>1.05</v>
       </c>
       <c r="F53" t="n">
-        <v>0.82</v>
+        <v>0.88</v>
       </c>
       <c r="G53" t="n">
-        <v>-0.41</v>
+        <v>0.9</v>
       </c>
       <c r="H53" t="n">
-        <v>-0.36</v>
+        <v>1</v>
       </c>
       <c r="I53" t="n">
-        <v>-0.08</v>
+        <v>0.76</v>
       </c>
       <c r="J53" t="n">
-        <v>-0.85</v>
+        <v>2.67</v>
       </c>
       <c r="K53" t="n">
         <v>0</v>
@@ -2503,34 +2500,34 @@
         <v>28</v>
       </c>
       <c r="B54" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="C54" t="n">
-        <v>185.72</v>
+        <v>22.95</v>
       </c>
       <c r="D54" t="n">
-        <v>155.02</v>
+        <v>53.04</v>
       </c>
       <c r="E54" t="n">
-        <v>3.74</v>
+        <v>0.96</v>
       </c>
       <c r="F54" t="n">
-        <v>0.77</v>
+        <v>0.87</v>
       </c>
       <c r="G54" t="n">
-        <v>-0.42</v>
+        <v>1.32</v>
       </c>
       <c r="H54" t="n">
-        <v>-0.71</v>
+        <v>1.15</v>
       </c>
       <c r="I54" t="n">
-        <v>0.16</v>
+        <v>0.85</v>
       </c>
       <c r="J54" t="n">
-        <v>-0.97</v>
+        <v>3.32</v>
       </c>
       <c r="K54" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L54" t="s">
         <v>27</v>
@@ -2541,31 +2538,31 @@
         <v>28</v>
       </c>
       <c r="B55" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C55" t="n">
-        <v>184.61</v>
+        <v>34.28</v>
       </c>
       <c r="D55" t="n">
-        <v>123.24</v>
+        <v>74.45</v>
       </c>
       <c r="E55" t="n">
-        <v>7.78</v>
+        <v>1.81</v>
       </c>
       <c r="F55" t="n">
-        <v>0.76</v>
+        <v>0.94</v>
       </c>
       <c r="G55" t="n">
-        <v>-0.41</v>
+        <v>-1.3</v>
       </c>
       <c r="H55" t="n">
-        <v>-0.15</v>
+        <v>-0.4</v>
       </c>
       <c r="I55" t="n">
-        <v>-1.78</v>
+        <v>-0.03</v>
       </c>
       <c r="J55" t="n">
-        <v>-2.35</v>
+        <v>-1.74</v>
       </c>
       <c r="K55" t="n">
         <v>0</v>
@@ -2579,34 +2576,34 @@
         <v>29</v>
       </c>
       <c r="B56" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="C56" t="n">
-        <v>196.09</v>
+        <v>12.11</v>
       </c>
       <c r="D56" t="n">
-        <v>780.23</v>
+        <v>100.91</v>
       </c>
       <c r="E56" t="n">
-        <v>5.69</v>
+        <v>0.6</v>
       </c>
       <c r="F56" t="n">
-        <v>0.9</v>
+        <v>0.93</v>
       </c>
       <c r="G56" t="n">
-        <v>-0.41</v>
+        <v>1.07</v>
       </c>
       <c r="H56" t="n">
-        <v>-0.29</v>
+        <v>1.18</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.16</v>
+        <v>1.02</v>
       </c>
       <c r="J56" t="n">
-        <v>-0.86</v>
+        <v>3.28</v>
       </c>
       <c r="K56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L56" t="s">
         <v>27</v>
@@ -2617,31 +2614,31 @@
         <v>29</v>
       </c>
       <c r="B57" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="C57" t="n">
-        <v>196.39</v>
+        <v>17.41</v>
       </c>
       <c r="D57" t="n">
-        <v>810.2</v>
+        <v>175.38</v>
       </c>
       <c r="E57" t="n">
-        <v>8.22</v>
+        <v>1.2</v>
       </c>
       <c r="F57" t="n">
-        <v>0.7</v>
+        <v>0.72</v>
       </c>
       <c r="G57" t="n">
-        <v>-0.41</v>
+        <v>-0.63</v>
       </c>
       <c r="H57" t="n">
-        <v>-0.38</v>
+        <v>-1.02</v>
       </c>
       <c r="I57" t="n">
-        <v>-1.17</v>
+        <v>-1.5</v>
       </c>
       <c r="J57" t="n">
-        <v>-1.96</v>
+        <v>-3.15</v>
       </c>
       <c r="K57" t="n">
         <v>0</v>
@@ -2655,34 +2652,34 @@
         <v>29</v>
       </c>
       <c r="B58" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C58" t="n">
-        <v>1.89</v>
+        <v>15.18</v>
       </c>
       <c r="D58" t="n">
-        <v>0.18</v>
+        <v>132.61</v>
       </c>
       <c r="E58" t="n">
-        <v>0.62</v>
+        <v>0.76</v>
       </c>
       <c r="F58" t="n">
-        <v>0.88</v>
+        <v>0.92</v>
       </c>
       <c r="G58" t="n">
-        <v>2.04</v>
+        <v>0.09</v>
       </c>
       <c r="H58" t="n">
-        <v>2.03</v>
+        <v>0.24</v>
       </c>
       <c r="I58" t="n">
-        <v>1.86</v>
+        <v>0.36</v>
       </c>
       <c r="J58" t="n">
-        <v>5.93</v>
+        <v>0.69</v>
       </c>
       <c r="K58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L58" t="s">
         <v>27</v>
@@ -2696,28 +2693,28 @@
         <v>18</v>
       </c>
       <c r="C59" t="n">
-        <v>196.44</v>
+        <v>20.33</v>
       </c>
       <c r="D59" t="n">
-        <v>873.63</v>
+        <v>185.53</v>
       </c>
       <c r="E59" t="n">
-        <v>5.53</v>
+        <v>1.04</v>
       </c>
       <c r="F59" t="n">
-        <v>0.88</v>
+        <v>0.91</v>
       </c>
       <c r="G59" t="n">
-        <v>-0.41</v>
+        <v>-1.56</v>
       </c>
       <c r="H59" t="n">
-        <v>-0.57</v>
+        <v>-1.32</v>
       </c>
       <c r="I59" t="n">
-        <v>-0.1</v>
+        <v>-0.83</v>
       </c>
       <c r="J59" t="n">
-        <v>-1.08</v>
+        <v>-3.71</v>
       </c>
       <c r="K59" t="n">
         <v>0</v>
@@ -2734,28 +2731,28 @@
         <v>16</v>
       </c>
       <c r="C60" t="n">
-        <v>196.27</v>
+        <v>12.33</v>
       </c>
       <c r="D60" t="n">
-        <v>815.59</v>
+        <v>112.01</v>
       </c>
       <c r="E60" t="n">
-        <v>6.17</v>
+        <v>0.62</v>
       </c>
       <c r="F60" t="n">
-        <v>0.87</v>
+        <v>0.92</v>
       </c>
       <c r="G60" t="n">
-        <v>-0.41</v>
+        <v>1</v>
       </c>
       <c r="H60" t="n">
-        <v>-0.4</v>
+        <v>0.86</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.36</v>
+        <v>0.95</v>
       </c>
       <c r="J60" t="n">
-        <v>-1.16</v>
+        <v>2.81</v>
       </c>
       <c r="K60" t="n">
         <v>0</v>
@@ -2769,31 +2766,31 @@
         <v>29</v>
       </c>
       <c r="B61" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C61" t="n">
-        <v>196.2</v>
+        <v>15.37</v>
       </c>
       <c r="D61" t="n">
-        <v>816.87</v>
+        <v>138.69</v>
       </c>
       <c r="E61" t="n">
-        <v>5.44</v>
+        <v>0.85</v>
       </c>
       <c r="F61" t="n">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="G61" t="n">
-        <v>-0.41</v>
+        <v>0.03</v>
       </c>
       <c r="H61" t="n">
-        <v>-0.4</v>
+        <v>0.06</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.07</v>
+        <v>-0.01</v>
       </c>
       <c r="J61" t="n">
-        <v>-0.87</v>
+        <v>0.08</v>
       </c>
       <c r="K61" t="n">
         <v>0</v>
@@ -2807,34 +2804,34 @@
         <v>30</v>
       </c>
       <c r="B62" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C62" t="n">
-        <v>197.56</v>
+        <v>24.64</v>
       </c>
       <c r="D62" t="n">
-        <v>1740.04</v>
+        <v>72.51</v>
       </c>
       <c r="E62" t="n">
-        <v>2.42</v>
+        <v>1.15</v>
       </c>
       <c r="F62" t="n">
-        <v>0.55</v>
+        <v>0.62</v>
       </c>
       <c r="G62" t="n">
-        <v>-0.44</v>
+        <v>1.3</v>
       </c>
       <c r="H62" t="n">
-        <v>0.17</v>
+        <v>1.15</v>
       </c>
       <c r="I62" t="n">
-        <v>1.46</v>
+        <v>0.73</v>
       </c>
       <c r="J62" t="n">
-        <v>1.2</v>
+        <v>3.17</v>
       </c>
       <c r="K62" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L62" t="s">
         <v>27</v>
@@ -2845,31 +2842,31 @@
         <v>30</v>
       </c>
       <c r="B63" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C63" t="n">
-        <v>199.63</v>
+        <v>27.42</v>
       </c>
       <c r="D63" t="n">
-        <v>9767.13</v>
+        <v>88.5</v>
       </c>
       <c r="E63" t="n">
-        <v>5.7</v>
+        <v>1.22</v>
       </c>
       <c r="F63" t="n">
-        <v>0.18</v>
+        <v>0.59</v>
       </c>
       <c r="G63" t="n">
-        <v>-0.47</v>
+        <v>-1.08</v>
       </c>
       <c r="H63" t="n">
-        <v>-2.01</v>
+        <v>-1.28</v>
       </c>
       <c r="I63" t="n">
-        <v>-0.4</v>
+        <v>0.11</v>
       </c>
       <c r="J63" t="n">
-        <v>-2.89</v>
+        <v>-2.26</v>
       </c>
       <c r="K63" t="n">
         <v>0</v>
@@ -2886,28 +2883,28 @@
         <v>16</v>
       </c>
       <c r="C64" t="n">
-        <v>197.11</v>
+        <v>25.68</v>
       </c>
       <c r="D64" t="n">
-        <v>1084.47</v>
+        <v>71.81</v>
       </c>
       <c r="E64" t="n">
-        <v>7.12</v>
+        <v>1.12</v>
       </c>
       <c r="F64" t="n">
-        <v>0.46</v>
+        <v>0.63</v>
       </c>
       <c r="G64" t="n">
-        <v>-0.43</v>
+        <v>0.41</v>
       </c>
       <c r="H64" t="n">
-        <v>0.35</v>
+        <v>1.25</v>
       </c>
       <c r="I64" t="n">
-        <v>-1.21</v>
+        <v>0.97</v>
       </c>
       <c r="J64" t="n">
-        <v>-1.3</v>
+        <v>2.63</v>
       </c>
       <c r="K64" t="n">
         <v>0</v>
@@ -2921,25 +2918,31 @@
         <v>30</v>
       </c>
       <c r="B65" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="C65" t="n">
-        <v>197.95</v>
+        <v>26.57</v>
       </c>
       <c r="D65" t="n">
-        <v>1324.55</v>
-      </c>
-      <c r="E65"/>
-      <c r="F65"/>
+        <v>83.29</v>
+      </c>
+      <c r="E65" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="F65" t="n">
+        <v>0.63</v>
+      </c>
       <c r="G65" t="n">
-        <v>-0.45</v>
+        <v>-0.35</v>
       </c>
       <c r="H65" t="n">
-        <v>0.29</v>
-      </c>
-      <c r="I65"/>
+        <v>-0.49</v>
+      </c>
+      <c r="I65" t="n">
+        <v>0.27</v>
+      </c>
       <c r="J65" t="n">
-        <v>-0.16</v>
+        <v>-0.58</v>
       </c>
       <c r="K65" t="n">
         <v>0</v>
@@ -2956,28 +2959,28 @@
         <v>15</v>
       </c>
       <c r="C66" t="n">
-        <v>184.86</v>
+        <v>27.42</v>
       </c>
       <c r="D66" t="n">
-        <v>329.62</v>
+        <v>83.15</v>
       </c>
       <c r="E66" t="n">
-        <v>4.28</v>
+        <v>1.42</v>
       </c>
       <c r="F66" t="n">
-        <v>0.01</v>
+        <v>0.73</v>
       </c>
       <c r="G66" t="n">
-        <v>-0.24</v>
+        <v>-1.08</v>
       </c>
       <c r="H66" t="n">
-        <v>0.56</v>
+        <v>-0.47</v>
       </c>
       <c r="I66" t="n">
-        <v>0.4</v>
+        <v>-1.84</v>
       </c>
       <c r="J66" t="n">
-        <v>0.72</v>
+        <v>-3.39</v>
       </c>
       <c r="K66" t="n">
         <v>0</v>
@@ -2991,34 +2994,34 @@
         <v>30</v>
       </c>
       <c r="B67" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="C67" t="n">
-        <v>41.83</v>
+        <v>25.21</v>
       </c>
       <c r="D67" t="n">
-        <v>4.13</v>
+        <v>81.11</v>
       </c>
       <c r="E67" t="n">
-        <v>5.43</v>
+        <v>1.25</v>
       </c>
       <c r="F67" t="n">
-        <v>0.4</v>
+        <v>0.65</v>
       </c>
       <c r="G67" t="n">
-        <v>2.03</v>
+        <v>0.82</v>
       </c>
       <c r="H67" t="n">
-        <v>0.64</v>
+        <v>-0.16</v>
       </c>
       <c r="I67" t="n">
-        <v>-0.25</v>
+        <v>-0.24</v>
       </c>
       <c r="J67" t="n">
-        <v>2.43</v>
+        <v>0.42</v>
       </c>
       <c r="K67" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L67" t="s">
         <v>27</v>
@@ -3029,31 +3032,31 @@
         <v>31</v>
       </c>
       <c r="B68" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="C68" t="n">
-        <v>190.84</v>
+        <v>26.4</v>
       </c>
       <c r="D68" t="n">
-        <v>255.29</v>
+        <v>12.5</v>
       </c>
       <c r="E68" t="n">
-        <v>5.3</v>
+        <v>1.46</v>
       </c>
       <c r="F68" t="n">
-        <v>0.65</v>
+        <v>0.77</v>
       </c>
       <c r="G68" t="n">
-        <v>-0.42</v>
+        <v>-2</v>
       </c>
       <c r="H68" t="n">
-        <v>-0.48</v>
+        <v>-1.55</v>
       </c>
       <c r="I68" t="n">
-        <v>-0.79</v>
+        <v>-1.99</v>
       </c>
       <c r="J68" t="n">
-        <v>-1.69</v>
+        <v>-5.54</v>
       </c>
       <c r="K68" t="n">
         <v>0</v>
@@ -3070,28 +3073,28 @@
         <v>16</v>
       </c>
       <c r="C69" t="n">
-        <v>190.18</v>
+        <v>16.6</v>
       </c>
       <c r="D69" t="n">
-        <v>246.99</v>
+        <v>11.49</v>
       </c>
       <c r="E69" t="n">
-        <v>4.84</v>
+        <v>1.02</v>
       </c>
       <c r="F69" t="n">
-        <v>0.6</v>
+        <v>0.78</v>
       </c>
       <c r="G69" t="n">
-        <v>-0.41</v>
+        <v>0.25</v>
       </c>
       <c r="H69" t="n">
-        <v>-0.4</v>
+        <v>-0.22</v>
       </c>
       <c r="I69" t="n">
-        <v>-0.48</v>
+        <v>0.11</v>
       </c>
       <c r="J69" t="n">
-        <v>-1.29</v>
+        <v>0.14</v>
       </c>
       <c r="K69" t="n">
         <v>0</v>
@@ -3105,34 +3108,34 @@
         <v>31</v>
       </c>
       <c r="B70" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="C70" t="n">
-        <v>4.92</v>
+        <v>14.93</v>
       </c>
       <c r="D70" t="n">
-        <v>0.31</v>
+        <v>11.01</v>
       </c>
       <c r="E70" t="n">
-        <v>1.16</v>
+        <v>0.94</v>
       </c>
       <c r="F70" t="n">
-        <v>0.59</v>
+        <v>0.85</v>
       </c>
       <c r="G70" t="n">
-        <v>2.04</v>
+        <v>0.63</v>
       </c>
       <c r="H70" t="n">
-        <v>2.04</v>
+        <v>0.41</v>
       </c>
       <c r="I70" t="n">
-        <v>1.99</v>
+        <v>0.5</v>
       </c>
       <c r="J70" t="n">
-        <v>6.07</v>
+        <v>1.54</v>
       </c>
       <c r="K70" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L70" t="s">
         <v>27</v>
@@ -3143,31 +3146,31 @@
         <v>31</v>
       </c>
       <c r="B71" t="s">
+        <v>19</v>
+      </c>
+      <c r="C71" t="n">
         <v>15</v>
       </c>
-      <c r="C71" t="n">
-        <v>190.08</v>
-      </c>
       <c r="D71" t="n">
-        <v>252.07</v>
+        <v>11.24</v>
       </c>
       <c r="E71" t="n">
-        <v>4.35</v>
+        <v>0.95</v>
       </c>
       <c r="F71" t="n">
-        <v>0.57</v>
+        <v>0.82</v>
       </c>
       <c r="G71" t="n">
-        <v>-0.41</v>
+        <v>0.62</v>
       </c>
       <c r="H71" t="n">
-        <v>-0.45</v>
+        <v>0.11</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.15</v>
+        <v>0.47</v>
       </c>
       <c r="J71" t="n">
-        <v>-1</v>
+        <v>1.19</v>
       </c>
       <c r="K71" t="n">
         <v>0</v>
@@ -3181,31 +3184,31 @@
         <v>31</v>
       </c>
       <c r="B72" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="C72" t="n">
-        <v>189.93</v>
+        <v>16.06</v>
       </c>
       <c r="D72" t="n">
-        <v>247.87</v>
+        <v>11.51</v>
       </c>
       <c r="E72" t="n">
-        <v>4.41</v>
+        <v>1.01</v>
       </c>
       <c r="F72" t="n">
-        <v>0.61</v>
+        <v>0.79</v>
       </c>
       <c r="G72" t="n">
-        <v>-0.41</v>
+        <v>0.37</v>
       </c>
       <c r="H72" t="n">
-        <v>-0.41</v>
+        <v>-0.26</v>
       </c>
       <c r="I72" t="n">
-        <v>-0.19</v>
+        <v>0.19</v>
       </c>
       <c r="J72" t="n">
-        <v>-1</v>
+        <v>0.3</v>
       </c>
       <c r="K72" t="n">
         <v>0</v>
@@ -3222,31 +3225,31 @@
         <v>18</v>
       </c>
       <c r="C73" t="n">
-        <v>189.79</v>
+        <v>17.11</v>
       </c>
       <c r="D73" t="n">
-        <v>237.4</v>
+        <v>10.16</v>
       </c>
       <c r="E73" t="n">
-        <v>4.69</v>
+        <v>0.9</v>
       </c>
       <c r="F73" t="n">
-        <v>0.59</v>
+        <v>0.8</v>
       </c>
       <c r="G73" t="n">
-        <v>-0.4</v>
+        <v>0.13</v>
       </c>
       <c r="H73" t="n">
-        <v>-0.3</v>
+        <v>1.52</v>
       </c>
       <c r="I73" t="n">
-        <v>-0.38</v>
+        <v>0.72</v>
       </c>
       <c r="J73" t="n">
-        <v>-1.08</v>
+        <v>2.37</v>
       </c>
       <c r="K73" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L73" t="s">
         <v>27</v>
@@ -3257,37 +3260,37 @@
         <v>32</v>
       </c>
       <c r="B74" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C74" t="n">
-        <v>5.19</v>
+        <v>30.54</v>
       </c>
       <c r="D74" t="n">
-        <v>0.24</v>
+        <v>2016.4</v>
       </c>
       <c r="E74" t="n">
-        <v>0.8</v>
+        <v>0.85</v>
       </c>
       <c r="F74" t="n">
-        <v>0.87</v>
+        <v>0.84</v>
       </c>
       <c r="G74" t="n">
-        <v>2.04</v>
+        <v>0.48</v>
       </c>
       <c r="H74" t="n">
-        <v>2.03</v>
+        <v>0.41</v>
       </c>
       <c r="I74" t="n">
-        <v>2.04</v>
+        <v>0.05</v>
       </c>
       <c r="J74" t="n">
-        <v>6.11</v>
+        <v>0.94</v>
       </c>
       <c r="K74" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L74" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
     </row>
     <row r="75">
@@ -3295,37 +3298,37 @@
         <v>32</v>
       </c>
       <c r="B75" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="C75" t="n">
-        <v>152.92</v>
+        <v>32.83</v>
       </c>
       <c r="D75" t="n">
-        <v>25.72</v>
+        <v>3120.22</v>
       </c>
       <c r="E75" t="n">
-        <v>4.15</v>
+        <v>1.56</v>
       </c>
       <c r="F75" t="n">
-        <v>0.89</v>
+        <v>0.75</v>
       </c>
       <c r="G75" t="n">
-        <v>-0.4</v>
+        <v>0.02</v>
       </c>
       <c r="H75" t="n">
-        <v>-0.38</v>
+        <v>-1.2</v>
       </c>
       <c r="I75" t="n">
-        <v>-0.45</v>
+        <v>-1.84</v>
       </c>
       <c r="J75" t="n">
-        <v>-1.23</v>
+        <v>-3.02</v>
       </c>
       <c r="K75" t="n">
         <v>0</v>
       </c>
       <c r="L75" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
     </row>
     <row r="76">
@@ -3333,37 +3336,37 @@
         <v>32</v>
       </c>
       <c r="B76" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="C76" t="n">
-        <v>152.75</v>
+        <v>42.31</v>
       </c>
       <c r="D76" t="n">
-        <v>25.55</v>
+        <v>3173.73</v>
       </c>
       <c r="E76" t="n">
-        <v>3.97</v>
+        <v>0.7</v>
       </c>
       <c r="F76" t="n">
-        <v>0.91</v>
+        <v>0.89</v>
       </c>
       <c r="G76" t="n">
-        <v>-0.39</v>
+        <v>-1.85</v>
       </c>
       <c r="H76" t="n">
-        <v>-0.37</v>
+        <v>-1.28</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.31</v>
+        <v>0.44</v>
       </c>
       <c r="J76" t="n">
-        <v>-1.07</v>
+        <v>-2.7</v>
       </c>
       <c r="K76" t="n">
         <v>0</v>
       </c>
       <c r="L76" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
     </row>
     <row r="77">
@@ -3371,37 +3374,37 @@
         <v>32</v>
       </c>
       <c r="B77" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C77" t="n">
-        <v>156.44</v>
+        <v>27.57</v>
       </c>
       <c r="D77" t="n">
-        <v>28.31</v>
+        <v>1575.93</v>
       </c>
       <c r="E77" t="n">
-        <v>4.11</v>
+        <v>0.44</v>
       </c>
       <c r="F77" t="n">
-        <v>0.88</v>
+        <v>0.96</v>
       </c>
       <c r="G77" t="n">
-        <v>-0.45</v>
+        <v>1.07</v>
       </c>
       <c r="H77" t="n">
-        <v>-0.63</v>
+        <v>1.06</v>
       </c>
       <c r="I77" t="n">
-        <v>-0.43</v>
+        <v>1.13</v>
       </c>
       <c r="J77" t="n">
-        <v>-1.51</v>
+        <v>3.25</v>
       </c>
       <c r="K77" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L77" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
     </row>
     <row r="78">
@@ -3409,37 +3412,37 @@
         <v>32</v>
       </c>
       <c r="B78" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="C78" t="n">
-        <v>152.32</v>
+        <v>30.82</v>
       </c>
       <c r="D78" t="n">
-        <v>24.59</v>
+        <v>1797.23</v>
       </c>
       <c r="E78" t="n">
-        <v>4.03</v>
+        <v>0.72</v>
       </c>
       <c r="F78" t="n">
-        <v>0.76</v>
+        <v>0.85</v>
       </c>
       <c r="G78" t="n">
-        <v>-0.39</v>
+        <v>0.42</v>
       </c>
       <c r="H78" t="n">
-        <v>-0.28</v>
+        <v>0.73</v>
       </c>
       <c r="I78" t="n">
-        <v>-0.36</v>
+        <v>0.37</v>
       </c>
       <c r="J78" t="n">
-        <v>-1.03</v>
+        <v>1.53</v>
       </c>
       <c r="K78" t="n">
         <v>0</v>
       </c>
       <c r="L78" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
     </row>
     <row r="79">
@@ -3447,265 +3450,265 @@
         <v>32</v>
       </c>
       <c r="B79" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="C79" t="n">
-        <v>153.71</v>
+        <v>33.63</v>
       </c>
       <c r="D79" t="n">
-        <v>25.63</v>
+        <v>2109.09</v>
       </c>
       <c r="E79" t="n">
-        <v>4.19</v>
+        <v>0.92</v>
       </c>
       <c r="F79" t="n">
-        <v>0.92</v>
+        <v>0.79</v>
       </c>
       <c r="G79" t="n">
-        <v>-0.41</v>
+        <v>-0.13</v>
       </c>
       <c r="H79" t="n">
-        <v>-0.37</v>
+        <v>0.28</v>
       </c>
       <c r="I79" t="n">
-        <v>-0.48</v>
+        <v>-0.14</v>
       </c>
       <c r="J79" t="n">
-        <v>-1.26</v>
+        <v>0</v>
       </c>
       <c r="K79" t="n">
         <v>0</v>
       </c>
       <c r="L79" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="s">
+        <v>34</v>
+      </c>
+      <c r="B80" t="s">
+        <v>13</v>
+      </c>
+      <c r="C80" t="n">
+        <v>16.79</v>
+      </c>
+      <c r="D80" t="n">
+        <v>39.7</v>
+      </c>
+      <c r="E80" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="F80" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="G80" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="H80" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="I80" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="J80" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="K80" t="n">
+        <v>0</v>
+      </c>
+      <c r="L80" t="s">
         <v>33</v>
-      </c>
-      <c r="B80" t="s">
-        <v>18</v>
-      </c>
-      <c r="C80" t="n">
-        <v>199.43</v>
-      </c>
-      <c r="D80" t="n">
-        <v>9734.7</v>
-      </c>
-      <c r="E80" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="F80" t="n">
-        <v>0.81</v>
-      </c>
-      <c r="G80" t="n">
-        <v>-0.41</v>
-      </c>
-      <c r="H80" t="n">
-        <v>-1.09</v>
-      </c>
-      <c r="I80" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="J80" t="n">
-        <v>-1.42</v>
-      </c>
-      <c r="K80" t="n">
-        <v>0</v>
-      </c>
-      <c r="L80" t="s">
-        <v>34</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="s">
+        <v>34</v>
+      </c>
+      <c r="B81" t="s">
+        <v>15</v>
+      </c>
+      <c r="C81" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="D81" t="n">
+        <v>29.7</v>
+      </c>
+      <c r="E81" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="F81" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="G81" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="H81" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="I81" t="n">
+        <v>-1.77</v>
+      </c>
+      <c r="J81" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="K81" t="n">
+        <v>1</v>
+      </c>
+      <c r="L81" t="s">
         <v>33</v>
-      </c>
-      <c r="B81" t="s">
-        <v>16</v>
-      </c>
-      <c r="C81" t="n">
-        <v>199.29</v>
-      </c>
-      <c r="D81" t="n">
-        <v>6918.56</v>
-      </c>
-      <c r="E81" t="n">
-        <v>2.67</v>
-      </c>
-      <c r="F81" t="n">
-        <v>0.83</v>
-      </c>
-      <c r="G81" t="n">
-        <v>-0.41</v>
-      </c>
-      <c r="H81" t="n">
-        <v>-0.26</v>
-      </c>
-      <c r="I81" t="n">
-        <v>-0.32</v>
-      </c>
-      <c r="J81" t="n">
-        <v>-0.99</v>
-      </c>
-      <c r="K81" t="n">
-        <v>0</v>
-      </c>
-      <c r="L81" t="s">
-        <v>34</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="s">
+        <v>34</v>
+      </c>
+      <c r="B82" t="s">
+        <v>16</v>
+      </c>
+      <c r="C82" t="n">
+        <v>23.51</v>
+      </c>
+      <c r="D82" t="n">
+        <v>52.04</v>
+      </c>
+      <c r="E82" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="F82" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="G82" t="n">
+        <v>-1.07</v>
+      </c>
+      <c r="H82" t="n">
+        <v>-1.17</v>
+      </c>
+      <c r="I82" t="n">
+        <v>-0.51</v>
+      </c>
+      <c r="J82" t="n">
+        <v>-2.76</v>
+      </c>
+      <c r="K82" t="n">
+        <v>0</v>
+      </c>
+      <c r="L82" t="s">
         <v>33</v>
-      </c>
-      <c r="B82" t="s">
-        <v>15</v>
-      </c>
-      <c r="C82" t="n">
-        <v>199.28</v>
-      </c>
-      <c r="D82" t="n">
-        <v>6526.34</v>
-      </c>
-      <c r="E82" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="F82" t="n">
-        <v>0.78</v>
-      </c>
-      <c r="G82" t="n">
-        <v>-0.41</v>
-      </c>
-      <c r="H82" t="n">
-        <v>-0.15</v>
-      </c>
-      <c r="I82" t="n">
-        <v>-0.64</v>
-      </c>
-      <c r="J82" t="n">
-        <v>-1.2</v>
-      </c>
-      <c r="K82" t="n">
-        <v>0</v>
-      </c>
-      <c r="L82" t="s">
-        <v>34</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="s">
+        <v>34</v>
+      </c>
+      <c r="B83" t="s">
+        <v>18</v>
+      </c>
+      <c r="C83" t="n">
+        <v>19.8</v>
+      </c>
+      <c r="D83" t="n">
+        <v>45.1</v>
+      </c>
+      <c r="E83" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="F83" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="G83" t="n">
+        <v>-0.24</v>
+      </c>
+      <c r="H83" t="n">
+        <v>-0.26</v>
+      </c>
+      <c r="I83" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="J83" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="K83" t="n">
+        <v>0</v>
+      </c>
+      <c r="L83" t="s">
         <v>33</v>
-      </c>
-      <c r="B83" t="s">
-        <v>19</v>
-      </c>
-      <c r="C83" t="n">
-        <v>199.32</v>
-      </c>
-      <c r="D83" t="n">
-        <v>8256.1</v>
-      </c>
-      <c r="E83" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="F83" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="G83" t="n">
-        <v>-0.41</v>
-      </c>
-      <c r="H83" t="n">
-        <v>-0.66</v>
-      </c>
-      <c r="I83" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="J83" t="n">
-        <v>-1</v>
-      </c>
-      <c r="K83" t="n">
-        <v>0</v>
-      </c>
-      <c r="L83" t="s">
-        <v>34</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="s">
+        <v>34</v>
+      </c>
+      <c r="B84" t="s">
+        <v>19</v>
+      </c>
+      <c r="C84" t="n">
+        <v>21.03</v>
+      </c>
+      <c r="D84" t="n">
+        <v>46.49</v>
+      </c>
+      <c r="E84" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="F84" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="G84" t="n">
+        <v>-0.52</v>
+      </c>
+      <c r="H84" t="n">
+        <v>-0.44</v>
+      </c>
+      <c r="I84" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="J84" t="n">
+        <v>-0.31</v>
+      </c>
+      <c r="K84" t="n">
+        <v>0</v>
+      </c>
+      <c r="L84" t="s">
         <v>33</v>
-      </c>
-      <c r="B84" t="s">
-        <v>17</v>
-      </c>
-      <c r="C84" t="n">
-        <v>3.67</v>
-      </c>
-      <c r="D84" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="E84" t="n">
-        <v>0.85</v>
-      </c>
-      <c r="F84" t="n">
-        <v>0.88</v>
-      </c>
-      <c r="G84" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="H84" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="I84" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="J84" t="n">
-        <v>5.66</v>
-      </c>
-      <c r="K84" t="n">
-        <v>1</v>
-      </c>
-      <c r="L84" t="s">
-        <v>34</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="s">
+        <v>34</v>
+      </c>
+      <c r="B85" t="s">
+        <v>17</v>
+      </c>
+      <c r="C85" t="n">
+        <v>20.46</v>
+      </c>
+      <c r="D85" t="n">
+        <v>45.6</v>
+      </c>
+      <c r="E85" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="F85" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="G85" t="n">
+        <v>-0.39</v>
+      </c>
+      <c r="H85" t="n">
+        <v>-0.33</v>
+      </c>
+      <c r="I85" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="J85" t="n">
+        <v>-0.52</v>
+      </c>
+      <c r="K85" t="n">
+        <v>0</v>
+      </c>
+      <c r="L85" t="s">
         <v>33</v>
-      </c>
-      <c r="B85" t="s">
-        <v>13</v>
-      </c>
-      <c r="C85" t="n">
-        <v>199.11</v>
-      </c>
-      <c r="D85" t="n">
-        <v>4745.04</v>
-      </c>
-      <c r="E85" t="n">
-        <v>3.27</v>
-      </c>
-      <c r="F85" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="G85" t="n">
-        <v>-0.41</v>
-      </c>
-      <c r="H85" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="I85" t="n">
-        <v>-1.03</v>
-      </c>
-      <c r="J85" t="n">
-        <v>-1.06</v>
-      </c>
-      <c r="K85" t="n">
-        <v>0</v>
-      </c>
-      <c r="L85" t="s">
-        <v>34</v>
       </c>
     </row>
     <row r="86">
@@ -3713,37 +3716,37 @@
         <v>35</v>
       </c>
       <c r="B86" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C86" t="n">
-        <v>189.02</v>
+        <v>28.45</v>
       </c>
       <c r="D86" t="n">
-        <v>195.93</v>
+        <v>51.29</v>
       </c>
       <c r="E86" t="n">
-        <v>7.52</v>
+        <v>9.97</v>
       </c>
       <c r="F86" t="n">
-        <v>0.9</v>
+        <v>0.4</v>
       </c>
       <c r="G86" t="n">
-        <v>-0.41</v>
+        <v>-0.89</v>
       </c>
       <c r="H86" t="n">
-        <v>-0.37</v>
+        <v>-0.88</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.03</v>
+        <v>-2</v>
       </c>
       <c r="J86" t="n">
-        <v>-0.81</v>
+        <v>-3.77</v>
       </c>
       <c r="K86" t="n">
         <v>0</v>
       </c>
       <c r="L86" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="87">
@@ -3751,37 +3754,37 @@
         <v>35</v>
       </c>
       <c r="B87" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="C87" t="n">
-        <v>188.65</v>
+        <v>18.53</v>
       </c>
       <c r="D87" t="n">
-        <v>192.79</v>
+        <v>33.2</v>
       </c>
       <c r="E87" t="n">
-        <v>6.08</v>
+        <v>2.71</v>
       </c>
       <c r="F87" t="n">
-        <v>0.83</v>
+        <v>0.67</v>
       </c>
       <c r="G87" t="n">
-        <v>-0.4</v>
+        <v>0.29</v>
       </c>
       <c r="H87" t="n">
-        <v>-0.33</v>
+        <v>0.42</v>
       </c>
       <c r="I87" t="n">
-        <v>0.26</v>
+        <v>0.25</v>
       </c>
       <c r="J87" t="n">
-        <v>-0.48</v>
+        <v>0.97</v>
       </c>
       <c r="K87" t="n">
         <v>0</v>
       </c>
       <c r="L87" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="88">
@@ -3789,37 +3792,37 @@
         <v>35</v>
       </c>
       <c r="B88" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C88" t="n">
-        <v>188.59</v>
+        <v>29.78</v>
       </c>
       <c r="D88" t="n">
-        <v>190.9</v>
+        <v>54.4</v>
       </c>
       <c r="E88" t="n">
-        <v>6.49</v>
+        <v>2.92</v>
       </c>
       <c r="F88" t="n">
-        <v>0.87</v>
+        <v>0.8</v>
       </c>
       <c r="G88" t="n">
-        <v>-0.4</v>
+        <v>-1.05</v>
       </c>
       <c r="H88" t="n">
-        <v>-0.31</v>
+        <v>-1.1</v>
       </c>
       <c r="I88" t="n">
-        <v>0.17</v>
+        <v>0.19</v>
       </c>
       <c r="J88" t="n">
-        <v>-0.54</v>
+        <v>-1.96</v>
       </c>
       <c r="K88" t="n">
         <v>0</v>
       </c>
       <c r="L88" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="89">
@@ -3830,34 +3833,34 @@
         <v>19</v>
       </c>
       <c r="C89" t="n">
-        <v>190.65</v>
+        <v>10.73</v>
       </c>
       <c r="D89" t="n">
-        <v>223.93</v>
+        <v>21.91</v>
       </c>
       <c r="E89" t="n">
-        <v>16.61</v>
+        <v>1.36</v>
       </c>
       <c r="F89" t="n">
-        <v>0.75</v>
+        <v>0.64</v>
       </c>
       <c r="G89" t="n">
-        <v>-0.43</v>
+        <v>1.23</v>
       </c>
       <c r="H89" t="n">
-        <v>-0.71</v>
+        <v>1.23</v>
       </c>
       <c r="I89" t="n">
-        <v>-1.86</v>
+        <v>0.67</v>
       </c>
       <c r="J89" t="n">
-        <v>-3</v>
+        <v>3.13</v>
       </c>
       <c r="K89" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L89" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="90">
@@ -3868,34 +3871,34 @@
         <v>17</v>
       </c>
       <c r="C90" t="n">
-        <v>4.66</v>
+        <v>26.21</v>
       </c>
       <c r="D90" t="n">
+        <v>47.93</v>
+      </c>
+      <c r="E90" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="F90" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="G90" t="n">
+        <v>-0.63</v>
+      </c>
+      <c r="H90" t="n">
+        <v>-0.64</v>
+      </c>
+      <c r="I90" t="n">
         <v>0.26</v>
       </c>
-      <c r="E90" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="F90" t="n">
-        <v>0.83</v>
-      </c>
-      <c r="G90" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="H90" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="I90" t="n">
-        <v>1.16</v>
-      </c>
       <c r="J90" t="n">
-        <v>5.22</v>
+        <v>-1</v>
       </c>
       <c r="K90" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L90" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="91">
@@ -3903,37 +3906,37 @@
         <v>35</v>
       </c>
       <c r="B91" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="C91" t="n">
-        <v>188.54</v>
+        <v>12.16</v>
       </c>
       <c r="D91" t="n">
-        <v>189.34</v>
+        <v>25.68</v>
       </c>
       <c r="E91" t="n">
-        <v>5.87</v>
+        <v>1.52</v>
       </c>
       <c r="F91" t="n">
-        <v>0.9</v>
+        <v>0.48</v>
       </c>
       <c r="G91" t="n">
-        <v>-0.4</v>
+        <v>1.05</v>
       </c>
       <c r="H91" t="n">
-        <v>-0.29</v>
+        <v>0.96</v>
       </c>
       <c r="I91" t="n">
-        <v>0.3</v>
+        <v>0.62</v>
       </c>
       <c r="J91" t="n">
-        <v>-0.39</v>
+        <v>2.64</v>
       </c>
       <c r="K91" t="n">
         <v>0</v>
       </c>
       <c r="L91" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="92">
@@ -3941,37 +3944,37 @@
         <v>36</v>
       </c>
       <c r="B92" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="C92" t="n">
-        <v>190.12</v>
+        <v>29.35</v>
       </c>
       <c r="D92" t="n">
-        <v>194.32</v>
+        <v>25.03</v>
       </c>
       <c r="E92" t="n">
-        <v>39.59</v>
+        <v>3.32</v>
       </c>
       <c r="F92" t="n">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="G92" t="n">
-        <v>-0.42</v>
+        <v>-0.02</v>
       </c>
       <c r="H92" t="n">
-        <v>-0.62</v>
+        <v>0.29</v>
       </c>
       <c r="I92" t="n">
-        <v>-1.92</v>
+        <v>-0.68</v>
       </c>
       <c r="J92" t="n">
-        <v>-2.96</v>
+        <v>-0.41</v>
       </c>
       <c r="K92" t="n">
         <v>0</v>
       </c>
       <c r="L92" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="93">
@@ -3979,37 +3982,37 @@
         <v>36</v>
       </c>
       <c r="B93" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C93" t="n">
-        <v>189.06</v>
+        <v>29.87</v>
       </c>
       <c r="D93" t="n">
-        <v>176.79</v>
+        <v>36.24</v>
       </c>
       <c r="E93" t="n">
-        <v>15.32</v>
+        <v>3.25</v>
       </c>
       <c r="F93" t="n">
-        <v>0.68</v>
+        <v>0.06</v>
       </c>
       <c r="G93" t="n">
-        <v>-0.41</v>
+        <v>-0.12</v>
       </c>
       <c r="H93" t="n">
-        <v>-0.38</v>
+        <v>-1.67</v>
       </c>
       <c r="I93" t="n">
-        <v>0.04</v>
+        <v>-0.57</v>
       </c>
       <c r="J93" t="n">
-        <v>-0.75</v>
+        <v>-2.36</v>
       </c>
       <c r="K93" t="n">
         <v>0</v>
       </c>
       <c r="L93" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="94">
@@ -4017,37 +4020,37 @@
         <v>36</v>
       </c>
       <c r="B94" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C94" t="n">
-        <v>5.65</v>
+        <v>20.57</v>
       </c>
       <c r="D94" t="n">
-        <v>0.3</v>
+        <v>19.83</v>
       </c>
       <c r="E94" t="n">
-        <v>3.28</v>
+        <v>1.78</v>
       </c>
       <c r="F94" t="n">
-        <v>0.81</v>
+        <v>0.49</v>
       </c>
       <c r="G94" t="n">
-        <v>2.04</v>
+        <v>1.61</v>
       </c>
       <c r="H94" t="n">
-        <v>2.01</v>
+        <v>1.2</v>
       </c>
       <c r="I94" t="n">
-        <v>1.02</v>
+        <v>1.64</v>
       </c>
       <c r="J94" t="n">
-        <v>5.06</v>
+        <v>4.45</v>
       </c>
       <c r="K94" t="n">
         <v>1</v>
       </c>
       <c r="L94" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="95">
@@ -4055,37 +4058,37 @@
         <v>36</v>
       </c>
       <c r="B95" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C95" t="n">
-        <v>188</v>
+        <v>35.17</v>
       </c>
       <c r="D95" t="n">
-        <v>162.36</v>
+        <v>28.81</v>
       </c>
       <c r="E95" t="n">
-        <v>12.65</v>
+        <v>3.27</v>
       </c>
       <c r="F95" t="n">
-        <v>0.64</v>
+        <v>0.6</v>
       </c>
       <c r="G95" t="n">
-        <v>-0.39</v>
+        <v>-1.1</v>
       </c>
       <c r="H95" t="n">
-        <v>-0.18</v>
+        <v>-0.37</v>
       </c>
       <c r="I95" t="n">
-        <v>0.26</v>
+        <v>-0.6</v>
       </c>
       <c r="J95" t="n">
-        <v>-0.32</v>
+        <v>-2.08</v>
       </c>
       <c r="K95" t="n">
         <v>0</v>
       </c>
       <c r="L95" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="96">
@@ -4093,37 +4096,37 @@
         <v>36</v>
       </c>
       <c r="B96" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="C96" t="n">
-        <v>189.83</v>
+        <v>26.26</v>
       </c>
       <c r="D96" t="n">
-        <v>192.85</v>
+        <v>22.54</v>
       </c>
       <c r="E96" t="n">
-        <v>11.22</v>
+        <v>2.3</v>
       </c>
       <c r="F96" t="n">
-        <v>0.81</v>
+        <v>0.56</v>
       </c>
       <c r="G96" t="n">
-        <v>-0.42</v>
+        <v>0.55</v>
       </c>
       <c r="H96" t="n">
-        <v>-0.6</v>
+        <v>0.72</v>
       </c>
       <c r="I96" t="n">
-        <v>0.37</v>
+        <v>0.86</v>
       </c>
       <c r="J96" t="n">
-        <v>-0.64</v>
+        <v>2.13</v>
       </c>
       <c r="K96" t="n">
         <v>0</v>
       </c>
       <c r="L96" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="97">
@@ -4131,37 +4134,37 @@
         <v>36</v>
       </c>
       <c r="B97" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C97" t="n">
-        <v>188.35</v>
+        <v>34.22</v>
       </c>
       <c r="D97" t="n">
-        <v>165.81</v>
+        <v>27.65</v>
       </c>
       <c r="E97" t="n">
-        <v>12.85</v>
+        <v>3.3</v>
       </c>
       <c r="F97" t="n">
-        <v>0.48</v>
+        <v>0.65</v>
       </c>
       <c r="G97" t="n">
-        <v>-0.4</v>
+        <v>-0.93</v>
       </c>
       <c r="H97" t="n">
-        <v>-0.23</v>
+        <v>-0.17</v>
       </c>
       <c r="I97" t="n">
-        <v>0.24</v>
+        <v>-0.64</v>
       </c>
       <c r="J97" t="n">
-        <v>-0.39</v>
+        <v>-1.74</v>
       </c>
       <c r="K97" t="n">
         <v>0</v>
       </c>
       <c r="L97" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="98">
@@ -4169,37 +4172,37 @@
         <v>37</v>
       </c>
       <c r="B98" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="C98" t="n">
-        <v>179.54</v>
+        <v>16.6</v>
       </c>
       <c r="D98" t="n">
-        <v>85.51</v>
+        <v>18.02</v>
       </c>
       <c r="E98" t="n">
-        <v>10.24</v>
+        <v>1.31</v>
       </c>
       <c r="F98" t="n">
-        <v>0.08</v>
+        <v>0.68</v>
       </c>
       <c r="G98" t="n">
-        <v>-0.39</v>
+        <v>0.95</v>
       </c>
       <c r="H98" t="n">
-        <v>-0.42</v>
+        <v>0.98</v>
       </c>
       <c r="I98" t="n">
-        <v>-0.34</v>
+        <v>1</v>
       </c>
       <c r="J98" t="n">
-        <v>-1.15</v>
+        <v>2.92</v>
       </c>
       <c r="K98" t="n">
         <v>0</v>
       </c>
       <c r="L98" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="99">
@@ -4207,37 +4210,37 @@
         <v>37</v>
       </c>
       <c r="B99" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C99" t="n">
-        <v>181.48</v>
+        <v>19.35</v>
       </c>
       <c r="D99" t="n">
-        <v>86.08</v>
+        <v>20.86</v>
       </c>
       <c r="E99" t="n">
-        <v>11.51</v>
+        <v>2.74</v>
       </c>
       <c r="F99" t="n">
-        <v>0.39</v>
+        <v>0.18</v>
       </c>
       <c r="G99" t="n">
-        <v>-0.41</v>
+        <v>0.6</v>
       </c>
       <c r="H99" t="n">
-        <v>-0.43</v>
+        <v>0.63</v>
       </c>
       <c r="I99" t="n">
-        <v>-0.7</v>
+        <v>-1.53</v>
       </c>
       <c r="J99" t="n">
-        <v>-1.55</v>
+        <v>-0.31</v>
       </c>
       <c r="K99" t="n">
         <v>0</v>
       </c>
       <c r="L99" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="100">
@@ -4245,37 +4248,37 @@
         <v>37</v>
       </c>
       <c r="B100" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C100" t="n">
-        <v>4.66</v>
+        <v>34.75</v>
       </c>
       <c r="D100" t="n">
-        <v>0.25</v>
+        <v>37.77</v>
       </c>
       <c r="E100" t="n">
-        <v>1.86</v>
+        <v>2.17</v>
       </c>
       <c r="F100" t="n">
-        <v>0.6</v>
+        <v>0.76</v>
       </c>
       <c r="G100" t="n">
-        <v>2.04</v>
+        <v>-1.38</v>
       </c>
       <c r="H100" t="n">
-        <v>2.04</v>
+        <v>-1.45</v>
       </c>
       <c r="I100" t="n">
-        <v>2</v>
+        <v>-0.52</v>
       </c>
       <c r="J100" t="n">
-        <v>6.07</v>
+        <v>-3.34</v>
       </c>
       <c r="K100" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L100" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="101">
@@ -4283,37 +4286,37 @@
         <v>37</v>
       </c>
       <c r="B101" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C101" t="n">
-        <v>181.92</v>
+        <v>30.14</v>
       </c>
       <c r="D101" t="n">
-        <v>86.48</v>
+        <v>31.6</v>
       </c>
       <c r="E101" t="n">
-        <v>10.76</v>
+        <v>2</v>
       </c>
       <c r="F101" t="n">
-        <v>0.67</v>
+        <v>0.81</v>
       </c>
       <c r="G101" t="n">
-        <v>-0.42</v>
+        <v>-0.78</v>
       </c>
       <c r="H101" t="n">
-        <v>-0.44</v>
+        <v>-0.69</v>
       </c>
       <c r="I101" t="n">
-        <v>-0.49</v>
+        <v>-0.21</v>
       </c>
       <c r="J101" t="n">
-        <v>-1.36</v>
+        <v>-1.69</v>
       </c>
       <c r="K101" t="n">
         <v>0</v>
       </c>
       <c r="L101" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="102">
@@ -4324,34 +4327,34 @@
         <v>18</v>
       </c>
       <c r="C102" t="n">
-        <v>180.37</v>
+        <v>15.95</v>
       </c>
       <c r="D102" t="n">
-        <v>80.36</v>
+        <v>18.2</v>
       </c>
       <c r="E102" t="n">
-        <v>9.24</v>
+        <v>1.23</v>
       </c>
       <c r="F102" t="n">
-        <v>0.6</v>
+        <v>0.39</v>
       </c>
       <c r="G102" t="n">
-        <v>-0.4</v>
+        <v>1.03</v>
       </c>
       <c r="H102" t="n">
-        <v>-0.27</v>
+        <v>0.95</v>
       </c>
       <c r="I102" t="n">
-        <v>-0.07</v>
+        <v>1.15</v>
       </c>
       <c r="J102" t="n">
-        <v>-0.73</v>
+        <v>3.14</v>
       </c>
       <c r="K102" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L102" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="103">
@@ -4359,37 +4362,37 @@
         <v>37</v>
       </c>
       <c r="B103" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="C103" t="n">
-        <v>182.08</v>
+        <v>27.26</v>
       </c>
       <c r="D103" t="n">
-        <v>87.47</v>
+        <v>29.44</v>
       </c>
       <c r="E103" t="n">
-        <v>10.43</v>
+        <v>1.82</v>
       </c>
       <c r="F103" t="n">
-        <v>0.64</v>
+        <v>0.69</v>
       </c>
       <c r="G103" t="n">
         <v>-0.42</v>
       </c>
       <c r="H103" t="n">
-        <v>-0.47</v>
+        <v>-0.42</v>
       </c>
       <c r="I103" t="n">
-        <v>-0.4</v>
+        <v>0.11</v>
       </c>
       <c r="J103" t="n">
-        <v>-1.29</v>
+        <v>-0.73</v>
       </c>
       <c r="K103" t="n">
         <v>0</v>
       </c>
       <c r="L103" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="104">
@@ -4397,37 +4400,37 @@
         <v>38</v>
       </c>
       <c r="B104" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C104" t="n">
-        <v>179.91</v>
+        <v>137.27</v>
       </c>
       <c r="D104" t="n">
-        <v>82.66</v>
+        <v>0.39</v>
       </c>
       <c r="E104" t="n">
-        <v>7.4</v>
+        <v>1.1</v>
       </c>
       <c r="F104" t="n">
-        <v>0.34</v>
+        <v>0.59</v>
       </c>
       <c r="G104" t="n">
-        <v>-0.37</v>
+        <v>2.04</v>
       </c>
       <c r="H104" t="n">
-        <v>0.01</v>
+        <v>1.96</v>
       </c>
       <c r="I104" t="n">
-        <v>0.17</v>
+        <v>0.72</v>
       </c>
       <c r="J104" t="n">
-        <v>-0.19</v>
+        <v>4.72</v>
       </c>
       <c r="K104" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L104" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="105">
@@ -4435,37 +4438,37 @@
         <v>38</v>
       </c>
       <c r="B105" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C105" t="n">
-        <v>183.14</v>
+        <v>174.04</v>
       </c>
       <c r="D105" t="n">
-        <v>99.37</v>
+        <v>0.58</v>
       </c>
       <c r="E105" t="n">
-        <v>9.2</v>
+        <v>7.05</v>
       </c>
       <c r="F105" t="n">
-        <v>0.63</v>
+        <v>0.16</v>
       </c>
       <c r="G105" t="n">
-        <v>-0.41</v>
+        <v>-0.35</v>
       </c>
       <c r="H105" t="n">
-        <v>-0.38</v>
+        <v>-0.12</v>
       </c>
       <c r="I105" t="n">
-        <v>-0.34</v>
+        <v>-1.14</v>
       </c>
       <c r="J105" t="n">
-        <v>-1.13</v>
+        <v>-1.61</v>
       </c>
       <c r="K105" t="n">
         <v>0</v>
       </c>
       <c r="L105" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="106">
@@ -4473,37 +4476,37 @@
         <v>38</v>
       </c>
       <c r="B106" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C106" t="n">
-        <v>185.03</v>
+        <v>173.45</v>
       </c>
       <c r="D106" t="n">
-        <v>114.75</v>
+        <v>0.65</v>
       </c>
       <c r="E106" t="n">
-        <v>7.73</v>
+        <v>2.04</v>
       </c>
       <c r="F106" t="n">
-        <v>0.65</v>
+        <v>0.03</v>
       </c>
       <c r="G106" t="n">
-        <v>-0.44</v>
+        <v>-0.31</v>
       </c>
       <c r="H106" t="n">
-        <v>-0.73</v>
+        <v>-0.91</v>
       </c>
       <c r="I106" t="n">
-        <v>0.08</v>
+        <v>0.42</v>
       </c>
       <c r="J106" t="n">
-        <v>-1.1</v>
+        <v>-0.8</v>
       </c>
       <c r="K106" t="n">
         <v>0</v>
       </c>
       <c r="L106" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="107">
@@ -4511,37 +4514,31 @@
         <v>38</v>
       </c>
       <c r="B107" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="C107" t="n">
-        <v>185.45</v>
+        <v>175.72</v>
       </c>
       <c r="D107" t="n">
-        <v>118.28</v>
-      </c>
-      <c r="E107" t="n">
-        <v>7.75</v>
-      </c>
-      <c r="F107" t="n">
-        <v>0.77</v>
-      </c>
+        <v>0.6</v>
+      </c>
+      <c r="E107"/>
+      <c r="F107"/>
       <c r="G107" t="n">
-        <v>-0.45</v>
+        <v>-0.46</v>
       </c>
       <c r="H107" t="n">
-        <v>-0.82</v>
-      </c>
-      <c r="I107" t="n">
-        <v>0.07</v>
-      </c>
+        <v>-0.31</v>
+      </c>
+      <c r="I107"/>
       <c r="J107" t="n">
-        <v>-1.19</v>
+        <v>-0.77</v>
       </c>
       <c r="K107" t="n">
         <v>0</v>
       </c>
       <c r="L107" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="108">
@@ -4552,34 +4549,28 @@
         <v>17</v>
       </c>
       <c r="C108" t="n">
-        <v>7.51</v>
+        <v>175.72</v>
       </c>
       <c r="D108" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="E108" t="n">
-        <v>2.47</v>
-      </c>
-      <c r="F108" t="n">
-        <v>0.73</v>
-      </c>
+        <v>0.6</v>
+      </c>
+      <c r="E108"/>
+      <c r="F108"/>
       <c r="G108" t="n">
-        <v>2.04</v>
+        <v>-0.46</v>
       </c>
       <c r="H108" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="I108" t="n">
-        <v>1.57</v>
-      </c>
+        <v>-0.31</v>
+      </c>
+      <c r="I108"/>
       <c r="J108" t="n">
-        <v>5.52</v>
+        <v>-0.77</v>
       </c>
       <c r="K108" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L108" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="109">
@@ -4587,37 +4578,31 @@
         <v>38</v>
       </c>
       <c r="B109" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C109" t="n">
-        <v>180.25</v>
+        <v>175.68</v>
       </c>
       <c r="D109" t="n">
-        <v>82.45</v>
-      </c>
-      <c r="E109" t="n">
-        <v>13.41</v>
-      </c>
-      <c r="F109" t="n">
-        <v>0.14</v>
-      </c>
+        <v>0.6</v>
+      </c>
+      <c r="E109"/>
+      <c r="F109"/>
       <c r="G109" t="n">
-        <v>-0.37</v>
+        <v>-0.46</v>
       </c>
       <c r="H109" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="I109" t="n">
-        <v>-1.54</v>
-      </c>
+        <v>-0.31</v>
+      </c>
+      <c r="I109"/>
       <c r="J109" t="n">
-        <v>-1.9</v>
+        <v>-0.77</v>
       </c>
       <c r="K109" t="n">
         <v>0</v>
       </c>
       <c r="L109" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="110">
@@ -4628,28 +4613,34 @@
         <v>15</v>
       </c>
       <c r="C110" t="n">
-        <v>190.93</v>
+        <v>11.01</v>
       </c>
       <c r="D110" t="n">
-        <v>4.39</v>
-      </c>
-      <c r="E110"/>
-      <c r="F110"/>
+        <v>5.01</v>
+      </c>
+      <c r="E110" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="F110" t="n">
+        <v>0.17</v>
+      </c>
       <c r="G110" t="n">
-        <v>-0.54</v>
+        <v>0.37</v>
       </c>
       <c r="H110" t="n">
-        <v>-0.43</v>
-      </c>
-      <c r="I110"/>
+        <v>0.11</v>
+      </c>
+      <c r="I110" t="n">
+        <v>-2.03</v>
+      </c>
       <c r="J110" t="n">
-        <v>-0.97</v>
+        <v>-1.56</v>
       </c>
       <c r="K110" t="n">
         <v>0</v>
       </c>
       <c r="L110" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="111">
@@ -4657,31 +4648,37 @@
         <v>39</v>
       </c>
       <c r="B111" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C111" t="n">
-        <v>190.95</v>
+        <v>11.79</v>
       </c>
       <c r="D111" t="n">
-        <v>4.39</v>
-      </c>
-      <c r="E111"/>
-      <c r="F111"/>
+        <v>5.44</v>
+      </c>
+      <c r="E111" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="F111" t="n">
+        <v>0.72</v>
+      </c>
       <c r="G111" t="n">
-        <v>-0.54</v>
+        <v>-0.13</v>
       </c>
       <c r="H111" t="n">
-        <v>-0.43</v>
-      </c>
-      <c r="I111"/>
+        <v>-0.42</v>
+      </c>
+      <c r="I111" t="n">
+        <v>0.5</v>
+      </c>
       <c r="J111" t="n">
-        <v>-0.96</v>
+        <v>-0.05</v>
       </c>
       <c r="K111" t="n">
         <v>0</v>
       </c>
       <c r="L111" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="112">
@@ -4689,37 +4686,37 @@
         <v>39</v>
       </c>
       <c r="B112" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C112" t="n">
-        <v>187.11</v>
+        <v>8.9</v>
       </c>
       <c r="D112" t="n">
-        <v>4.36</v>
+        <v>3.5</v>
       </c>
       <c r="E112" t="n">
-        <v>73.89</v>
+        <v>0.7</v>
       </c>
       <c r="F112" t="n">
-        <v>0.27</v>
+        <v>0.63</v>
       </c>
       <c r="G112" t="n">
-        <v>-0.38</v>
+        <v>1.71</v>
       </c>
       <c r="H112" t="n">
-        <v>-0.35</v>
+        <v>1.97</v>
       </c>
       <c r="I112" t="n">
-        <v>-1.14</v>
+        <v>0.43</v>
       </c>
       <c r="J112" t="n">
-        <v>-1.87</v>
+        <v>4.1</v>
       </c>
       <c r="K112" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L112" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="113">
@@ -4727,37 +4724,37 @@
         <v>39</v>
       </c>
       <c r="B113" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="C113" t="n">
-        <v>178.3</v>
+        <v>13.25</v>
       </c>
       <c r="D113" t="n">
-        <v>4.38</v>
+        <v>5.68</v>
       </c>
       <c r="E113" t="n">
-        <v>16.18</v>
+        <v>0.65</v>
       </c>
       <c r="F113" t="n">
-        <v>0.36</v>
+        <v>0.7</v>
       </c>
       <c r="G113" t="n">
-        <v>-0.01</v>
+        <v>-1.05</v>
       </c>
       <c r="H113" t="n">
-        <v>-0.4</v>
+        <v>-0.71</v>
       </c>
       <c r="I113" t="n">
-        <v>0.41</v>
+        <v>0.47</v>
       </c>
       <c r="J113" t="n">
-        <v>-0.01</v>
+        <v>-1.29</v>
       </c>
       <c r="K113" t="n">
         <v>0</v>
       </c>
       <c r="L113" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="114">
@@ -4765,37 +4762,37 @@
         <v>39</v>
       </c>
       <c r="B114" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C114" t="n">
-        <v>130.09</v>
+        <v>13.01</v>
       </c>
       <c r="D114" t="n">
-        <v>3.23</v>
+        <v>5.49</v>
       </c>
       <c r="E114" t="n">
-        <v>4.13</v>
+        <v>0.77</v>
       </c>
       <c r="F114" t="n">
-        <v>0.04</v>
+        <v>0.52</v>
       </c>
       <c r="G114" t="n">
-        <v>2</v>
+        <v>-0.9</v>
       </c>
       <c r="H114" t="n">
-        <v>2.04</v>
+        <v>-0.48</v>
       </c>
       <c r="I114" t="n">
-        <v>0.73</v>
+        <v>0.38</v>
       </c>
       <c r="J114" t="n">
-        <v>4.77</v>
+        <v>-1.01</v>
       </c>
       <c r="K114" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L114" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="115">
@@ -4803,31 +4800,37 @@
         <v>39</v>
       </c>
       <c r="B115" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="C115" t="n">
-        <v>190.93</v>
+        <v>11.58</v>
       </c>
       <c r="D115" t="n">
-        <v>4.39</v>
-      </c>
-      <c r="E115"/>
-      <c r="F115"/>
+        <v>5.47</v>
+      </c>
+      <c r="E115" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="F115" t="n">
+        <v>0.24</v>
+      </c>
       <c r="G115" t="n">
-        <v>-0.54</v>
+        <v>0.01</v>
       </c>
       <c r="H115" t="n">
-        <v>-0.43</v>
-      </c>
-      <c r="I115"/>
+        <v>-0.46</v>
+      </c>
+      <c r="I115" t="n">
+        <v>0.26</v>
+      </c>
       <c r="J115" t="n">
-        <v>-0.97</v>
+        <v>-0.19</v>
       </c>
       <c r="K115" t="n">
         <v>0</v>
       </c>
       <c r="L115" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="116">
@@ -4835,37 +4838,37 @@
         <v>40</v>
       </c>
       <c r="B116" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C116" t="n">
-        <v>163.21</v>
+        <v>13.48</v>
       </c>
       <c r="D116" t="n">
-        <v>32.87</v>
+        <v>127.7</v>
       </c>
       <c r="E116" t="n">
-        <v>7.4</v>
+        <v>2.12</v>
       </c>
       <c r="F116" t="n">
-        <v>0.64</v>
+        <v>0.54</v>
       </c>
       <c r="G116" t="n">
-        <v>-0.41</v>
+        <v>-0.96</v>
       </c>
       <c r="H116" t="n">
-        <v>-0.38</v>
+        <v>-1.01</v>
       </c>
       <c r="I116" t="n">
-        <v>0.16</v>
+        <v>0.24</v>
       </c>
       <c r="J116" t="n">
-        <v>-0.63</v>
+        <v>-1.73</v>
       </c>
       <c r="K116" t="n">
         <v>0</v>
       </c>
       <c r="L116" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
     </row>
     <row r="117">
@@ -4873,37 +4876,37 @@
         <v>40</v>
       </c>
       <c r="B117" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C117" t="n">
-        <v>161.92</v>
+        <v>9.19</v>
       </c>
       <c r="D117" t="n">
-        <v>32.72</v>
+        <v>87.12</v>
       </c>
       <c r="E117" t="n">
-        <v>5.4</v>
+        <v>1.74</v>
       </c>
       <c r="F117" t="n">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="G117" t="n">
-        <v>-0.39</v>
+        <v>0.55</v>
       </c>
       <c r="H117" t="n">
-        <v>-0.37</v>
+        <v>0.58</v>
       </c>
       <c r="I117" t="n">
-        <v>0.36</v>
+        <v>0.46</v>
       </c>
       <c r="J117" t="n">
-        <v>-0.4</v>
+        <v>1.59</v>
       </c>
       <c r="K117" t="n">
         <v>0</v>
       </c>
       <c r="L117" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
     </row>
     <row r="118">
@@ -4911,37 +4914,37 @@
         <v>40</v>
       </c>
       <c r="B118" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C118" t="n">
-        <v>165.29</v>
+        <v>7.47</v>
       </c>
       <c r="D118" t="n">
-        <v>34.96</v>
+        <v>68.59</v>
       </c>
       <c r="E118" t="n">
-        <v>7.21</v>
+        <v>6.06</v>
       </c>
       <c r="F118" t="n">
-        <v>0.26</v>
+        <v>0.37</v>
       </c>
       <c r="G118" t="n">
-        <v>-0.44</v>
+        <v>1.15</v>
       </c>
       <c r="H118" t="n">
-        <v>-0.54</v>
+        <v>1.3</v>
       </c>
       <c r="I118" t="n">
-        <v>0.18</v>
+        <v>-1.98</v>
       </c>
       <c r="J118" t="n">
-        <v>-0.79</v>
+        <v>0.48</v>
       </c>
       <c r="K118" t="n">
         <v>0</v>
       </c>
       <c r="L118" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
     </row>
     <row r="119">
@@ -4949,37 +4952,37 @@
         <v>40</v>
       </c>
       <c r="B119" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C119" t="n">
-        <v>3.65</v>
+        <v>8.82</v>
       </c>
       <c r="D119" t="n">
-        <v>0.15</v>
+        <v>88.54</v>
       </c>
       <c r="E119" t="n">
-        <v>0.64</v>
+        <v>1.16</v>
       </c>
       <c r="F119" t="n">
-        <v>0.65</v>
+        <v>0.44</v>
       </c>
       <c r="G119" t="n">
-        <v>2.04</v>
+        <v>0.68</v>
       </c>
       <c r="H119" t="n">
-        <v>2.03</v>
+        <v>0.52</v>
       </c>
       <c r="I119" t="n">
-        <v>0.84</v>
+        <v>0.78</v>
       </c>
       <c r="J119" t="n">
-        <v>4.91</v>
+        <v>1.98</v>
       </c>
       <c r="K119" t="n">
         <v>1</v>
       </c>
       <c r="L119" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
     </row>
     <row r="120">
@@ -4987,37 +4990,37 @@
         <v>40</v>
       </c>
       <c r="B120" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C120" t="n">
-        <v>161.83</v>
+        <v>10.79</v>
       </c>
       <c r="D120" t="n">
-        <v>30.37</v>
+        <v>104.66</v>
       </c>
       <c r="E120" t="n">
-        <v>28.85</v>
+        <v>1.77</v>
       </c>
       <c r="F120" t="n">
-        <v>0.18</v>
+        <v>0.55</v>
       </c>
       <c r="G120" t="n">
-        <v>-0.39</v>
+        <v>-0.01</v>
       </c>
       <c r="H120" t="n">
-        <v>-0.2</v>
+        <v>-0.11</v>
       </c>
       <c r="I120" t="n">
-        <v>-1.98</v>
+        <v>0.44</v>
       </c>
       <c r="J120" t="n">
-        <v>-2.57</v>
+        <v>0.32</v>
       </c>
       <c r="K120" t="n">
         <v>0</v>
       </c>
       <c r="L120" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
     </row>
     <row r="121">
@@ -5025,265 +5028,265 @@
         <v>40</v>
       </c>
       <c r="B121" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C121" t="n">
-        <v>163.71</v>
+        <v>14.76</v>
       </c>
       <c r="D121" t="n">
-        <v>34.93</v>
+        <v>134.86</v>
       </c>
       <c r="E121" t="n">
-        <v>4.74</v>
+        <v>2.43</v>
       </c>
       <c r="F121" t="n">
-        <v>0.71</v>
+        <v>0.54</v>
       </c>
       <c r="G121" t="n">
-        <v>-0.42</v>
+        <v>-1.41</v>
       </c>
       <c r="H121" t="n">
-        <v>-0.53</v>
+        <v>-1.29</v>
       </c>
       <c r="I121" t="n">
-        <v>0.43</v>
+        <v>0.06</v>
       </c>
       <c r="J121" t="n">
-        <v>-0.52</v>
+        <v>-2.64</v>
       </c>
       <c r="K121" t="n">
         <v>0</v>
       </c>
       <c r="L121" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="s">
+        <v>42</v>
+      </c>
+      <c r="B122" t="s">
+        <v>15</v>
+      </c>
+      <c r="C122" t="n">
+        <v>56.07</v>
+      </c>
+      <c r="D122" t="n">
+        <v>853.08</v>
+      </c>
+      <c r="E122" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="F122" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="G122" t="n">
+        <v>-2.01</v>
+      </c>
+      <c r="H122" t="n">
+        <v>-2.02</v>
+      </c>
+      <c r="I122" t="n">
+        <v>-1.04</v>
+      </c>
+      <c r="J122" t="n">
+        <v>-5.07</v>
+      </c>
+      <c r="K122" t="n">
+        <v>0</v>
+      </c>
+      <c r="L122" t="s">
         <v>41</v>
-      </c>
-      <c r="B122" t="s">
-        <v>13</v>
-      </c>
-      <c r="C122" t="n">
-        <v>196.98</v>
-      </c>
-      <c r="D122" t="n">
-        <v>880.3</v>
-      </c>
-      <c r="E122" t="n">
-        <v>17.07</v>
-      </c>
-      <c r="F122" t="n">
-        <v>0.56</v>
-      </c>
-      <c r="G122" t="n">
-        <v>-0.41</v>
-      </c>
-      <c r="H122" t="n">
-        <v>-0.45</v>
-      </c>
-      <c r="I122" t="n">
-        <v>0.29</v>
-      </c>
-      <c r="J122" t="n">
-        <v>-0.57</v>
-      </c>
-      <c r="K122" t="n">
-        <v>0</v>
-      </c>
-      <c r="L122" t="s">
-        <v>42</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="s">
+        <v>42</v>
+      </c>
+      <c r="B123" t="s">
+        <v>13</v>
+      </c>
+      <c r="C123" t="n">
+        <v>13.68</v>
+      </c>
+      <c r="D123" t="n">
+        <v>158.89</v>
+      </c>
+      <c r="E123" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="F123" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="G123" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="H123" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="I123" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="J123" t="n">
+        <v>0.81</v>
+      </c>
+      <c r="K123" t="n">
+        <v>0</v>
+      </c>
+      <c r="L123" t="s">
         <v>41</v>
-      </c>
-      <c r="B123" t="s">
-        <v>17</v>
-      </c>
-      <c r="C123" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="D123" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="E123" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="F123" t="n">
-        <v>0.54</v>
-      </c>
-      <c r="G123" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="H123" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="I123" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="J123" t="n">
-        <v>4.87</v>
-      </c>
-      <c r="K123" t="n">
-        <v>1</v>
-      </c>
-      <c r="L123" t="s">
-        <v>42</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="s">
+        <v>42</v>
+      </c>
+      <c r="B124" t="s">
+        <v>16</v>
+      </c>
+      <c r="C124" t="n">
+        <v>13.28</v>
+      </c>
+      <c r="D124" t="n">
+        <v>130.8</v>
+      </c>
+      <c r="E124" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="F124" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="G124" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="H124" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="I124" t="n">
+        <v>-0.69</v>
+      </c>
+      <c r="J124" t="n">
+        <v>-0.07</v>
+      </c>
+      <c r="K124" t="n">
+        <v>0</v>
+      </c>
+      <c r="L124" t="s">
         <v>41</v>
-      </c>
-      <c r="B124" t="s">
-        <v>18</v>
-      </c>
-      <c r="C124" t="n">
-        <v>197.06</v>
-      </c>
-      <c r="D124" t="n">
-        <v>904.92</v>
-      </c>
-      <c r="E124" t="n">
-        <v>16.58</v>
-      </c>
-      <c r="F124" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="G124" t="n">
-        <v>-0.41</v>
-      </c>
-      <c r="H124" t="n">
-        <v>-0.52</v>
-      </c>
-      <c r="I124" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="J124" t="n">
-        <v>-0.63</v>
-      </c>
-      <c r="K124" t="n">
-        <v>0</v>
-      </c>
-      <c r="L124" t="s">
-        <v>42</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="s">
+        <v>42</v>
+      </c>
+      <c r="B125" t="s">
+        <v>19</v>
+      </c>
+      <c r="C125" t="n">
+        <v>12.87</v>
+      </c>
+      <c r="D125" t="n">
+        <v>110.82</v>
+      </c>
+      <c r="E125" t="n">
+        <v>1</v>
+      </c>
+      <c r="F125" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="G125" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="H125" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="I125" t="n">
+        <v>-0.27</v>
+      </c>
+      <c r="J125" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="K125" t="n">
+        <v>0</v>
+      </c>
+      <c r="L125" t="s">
         <v>41</v>
-      </c>
-      <c r="B125" t="s">
-        <v>16</v>
-      </c>
-      <c r="C125" t="n">
-        <v>196.94</v>
-      </c>
-      <c r="D125" t="n">
-        <v>864.33</v>
-      </c>
-      <c r="E125" t="n">
-        <v>19.65</v>
-      </c>
-      <c r="F125" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="G125" t="n">
-        <v>-0.41</v>
-      </c>
-      <c r="H125" t="n">
-        <v>-0.41</v>
-      </c>
-      <c r="I125" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="J125" t="n">
-        <v>-0.62</v>
-      </c>
-      <c r="K125" t="n">
-        <v>0</v>
-      </c>
-      <c r="L125" t="s">
-        <v>42</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="s">
+        <v>42</v>
+      </c>
+      <c r="B126" t="s">
+        <v>17</v>
+      </c>
+      <c r="C126" t="n">
+        <v>11.62</v>
+      </c>
+      <c r="D126" t="n">
+        <v>95.18</v>
+      </c>
+      <c r="E126" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="F126" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="G126" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="H126" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="I126" t="n">
+        <v>-0.11</v>
+      </c>
+      <c r="J126" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="K126" t="n">
+        <v>0</v>
+      </c>
+      <c r="L126" t="s">
         <v>41</v>
-      </c>
-      <c r="B126" t="s">
-        <v>15</v>
-      </c>
-      <c r="C126" t="n">
-        <v>196.91</v>
-      </c>
-      <c r="D126" t="n">
-        <v>857.26</v>
-      </c>
-      <c r="E126" t="n">
-        <v>13.58</v>
-      </c>
-      <c r="F126" t="n">
-        <v>0.46</v>
-      </c>
-      <c r="G126" t="n">
-        <v>-0.41</v>
-      </c>
-      <c r="H126" t="n">
-        <v>-0.39</v>
-      </c>
-      <c r="I126" t="n">
-        <v>0.41</v>
-      </c>
-      <c r="J126" t="n">
-        <v>-0.39</v>
-      </c>
-      <c r="K126" t="n">
-        <v>0</v>
-      </c>
-      <c r="L126" t="s">
-        <v>42</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="s">
+        <v>42</v>
+      </c>
+      <c r="B127" t="s">
+        <v>18</v>
+      </c>
+      <c r="C127" t="n">
+        <v>4.57</v>
+      </c>
+      <c r="D127" t="n">
+        <v>43.36</v>
+      </c>
+      <c r="E127" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="F127" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="G127" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="H127" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="I127" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="J127" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="K127" t="n">
+        <v>1</v>
+      </c>
+      <c r="L127" t="s">
         <v>41</v>
-      </c>
-      <c r="B127" t="s">
-        <v>19</v>
-      </c>
-      <c r="C127" t="n">
-        <v>196.78</v>
-      </c>
-      <c r="D127" t="n">
-        <v>814.67</v>
-      </c>
-      <c r="E127" t="n">
-        <v>82.57</v>
-      </c>
-      <c r="F127" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="G127" t="n">
-        <v>-0.41</v>
-      </c>
-      <c r="H127" t="n">
-        <v>-0.27</v>
-      </c>
-      <c r="I127" t="n">
-        <v>-2</v>
-      </c>
-      <c r="J127" t="n">
-        <v>-2.67</v>
-      </c>
-      <c r="K127" t="n">
-        <v>0</v>
-      </c>
-      <c r="L127" t="s">
-        <v>42</v>
       </c>
     </row>
     <row r="128">
@@ -5291,37 +5294,37 @@
         <v>43</v>
       </c>
       <c r="B128" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C128" t="n">
-        <v>196.4</v>
+        <v>8.29</v>
       </c>
       <c r="D128" t="n">
-        <v>733.6</v>
+        <v>65.58</v>
       </c>
       <c r="E128" t="n">
-        <v>9.05</v>
+        <v>0.48</v>
       </c>
       <c r="F128" t="n">
-        <v>0.79</v>
+        <v>0.63</v>
       </c>
       <c r="G128" t="n">
-        <v>-0.4</v>
+        <v>-0.57</v>
       </c>
       <c r="H128" t="n">
-        <v>0.04</v>
+        <v>-1.2</v>
       </c>
       <c r="I128" t="n">
-        <v>-0.82</v>
+        <v>1.32</v>
       </c>
       <c r="J128" t="n">
-        <v>-1.19</v>
+        <v>-0.45</v>
       </c>
       <c r="K128" t="n">
         <v>0</v>
       </c>
       <c r="L128" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="129">
@@ -5329,37 +5332,37 @@
         <v>43</v>
       </c>
       <c r="B129" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C129" t="n">
-        <v>196.22</v>
+        <v>6.59</v>
       </c>
       <c r="D129" t="n">
-        <v>719.39</v>
+        <v>56.19</v>
       </c>
       <c r="E129" t="n">
-        <v>7.72</v>
+        <v>0.55</v>
       </c>
       <c r="F129" t="n">
-        <v>0.32</v>
+        <v>0.82</v>
       </c>
       <c r="G129" t="n">
-        <v>-0.4</v>
+        <v>1.71</v>
       </c>
       <c r="H129" t="n">
-        <v>0.07</v>
+        <v>1.49</v>
       </c>
       <c r="I129" t="n">
-        <v>-0.44</v>
+        <v>0.77</v>
       </c>
       <c r="J129" t="n">
-        <v>-0.77</v>
+        <v>3.98</v>
       </c>
       <c r="K129" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L129" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="130">
@@ -5367,37 +5370,37 @@
         <v>43</v>
       </c>
       <c r="B130" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="C130" t="n">
-        <v>197.92</v>
+        <v>8.38</v>
       </c>
       <c r="D130" t="n">
-        <v>1548.85</v>
+        <v>63.81</v>
       </c>
       <c r="E130" t="n">
-        <v>2.49</v>
+        <v>0.67</v>
       </c>
       <c r="F130" t="n">
-        <v>0.41</v>
+        <v>0.82</v>
       </c>
       <c r="G130" t="n">
-        <v>-0.42</v>
+        <v>-0.69</v>
       </c>
       <c r="H130" t="n">
-        <v>-1.62</v>
+        <v>-0.69</v>
       </c>
       <c r="I130" t="n">
-        <v>1.06</v>
+        <v>-0.15</v>
       </c>
       <c r="J130" t="n">
-        <v>-0.98</v>
+        <v>-1.53</v>
       </c>
       <c r="K130" t="n">
         <v>0</v>
       </c>
       <c r="L130" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="131">
@@ -5405,37 +5408,37 @@
         <v>43</v>
       </c>
       <c r="B131" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="C131" t="n">
-        <v>196.29</v>
+        <v>7.57</v>
       </c>
       <c r="D131" t="n">
-        <v>735.98</v>
+        <v>60.99</v>
       </c>
       <c r="E131" t="n">
-        <v>8.39</v>
+        <v>0.63</v>
       </c>
       <c r="F131" t="n">
-        <v>0.52</v>
+        <v>0.81</v>
       </c>
       <c r="G131" t="n">
-        <v>-0.4</v>
+        <v>0.4</v>
       </c>
       <c r="H131" t="n">
-        <v>0.04</v>
+        <v>0.12</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.63</v>
+        <v>0.14</v>
       </c>
       <c r="J131" t="n">
-        <v>-1</v>
+        <v>0.66</v>
       </c>
       <c r="K131" t="n">
         <v>0</v>
       </c>
       <c r="L131" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="132">
@@ -5443,37 +5446,37 @@
         <v>43</v>
       </c>
       <c r="B132" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C132" t="n">
-        <v>196.56</v>
+        <v>8.64</v>
       </c>
       <c r="D132" t="n">
-        <v>782.49</v>
+        <v>63.09</v>
       </c>
       <c r="E132" t="n">
-        <v>8.42</v>
+        <v>0.84</v>
       </c>
       <c r="F132" t="n">
-        <v>0.52</v>
+        <v>0.84</v>
       </c>
       <c r="G132" t="n">
-        <v>-0.41</v>
+        <v>-1.03</v>
       </c>
       <c r="H132" t="n">
-        <v>-0.06</v>
+        <v>-0.49</v>
       </c>
       <c r="I132" t="n">
-        <v>-0.64</v>
+        <v>-1.51</v>
       </c>
       <c r="J132" t="n">
-        <v>-1.11</v>
+        <v>-3.03</v>
       </c>
       <c r="K132" t="n">
         <v>0</v>
       </c>
       <c r="L132" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="133">
@@ -5484,34 +5487,34 @@
         <v>17</v>
       </c>
       <c r="C133" t="n">
-        <v>1.89</v>
+        <v>7.74</v>
       </c>
       <c r="D133" t="n">
-        <v>0.15</v>
+        <v>58.69</v>
       </c>
       <c r="E133" t="n">
-        <v>1.05</v>
+        <v>0.72</v>
       </c>
       <c r="F133" t="n">
-        <v>0.5</v>
+        <v>0.85</v>
       </c>
       <c r="G133" t="n">
-        <v>2.04</v>
+        <v>0.18</v>
       </c>
       <c r="H133" t="n">
-        <v>1.54</v>
+        <v>0.78</v>
       </c>
       <c r="I133" t="n">
-        <v>1.48</v>
+        <v>-0.58</v>
       </c>
       <c r="J133" t="n">
-        <v>5.06</v>
+        <v>0.37</v>
       </c>
       <c r="K133" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L133" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="134">
@@ -5519,37 +5522,37 @@
         <v>44</v>
       </c>
       <c r="B134" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C134" t="n">
-        <v>195.76</v>
+        <v>9.25</v>
       </c>
       <c r="D134" t="n">
-        <v>601.86</v>
+        <v>39.98</v>
       </c>
       <c r="E134" t="n">
-        <v>5.94</v>
+        <v>1.08</v>
       </c>
       <c r="F134" t="n">
-        <v>0.6</v>
+        <v>0.68</v>
       </c>
       <c r="G134" t="n">
-        <v>-0.41</v>
+        <v>0.13</v>
       </c>
       <c r="H134" t="n">
-        <v>-0.34</v>
+        <v>0.24</v>
       </c>
       <c r="I134" t="n">
-        <v>0.4</v>
+        <v>0.27</v>
       </c>
       <c r="J134" t="n">
-        <v>-0.34</v>
+        <v>0.64</v>
       </c>
       <c r="K134" t="n">
         <v>0</v>
       </c>
       <c r="L134" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="135">
@@ -5560,34 +5563,34 @@
         <v>16</v>
       </c>
       <c r="C135" t="n">
-        <v>195.87</v>
+        <v>8.66</v>
       </c>
       <c r="D135" t="n">
-        <v>619.02</v>
+        <v>37.72</v>
       </c>
       <c r="E135" t="n">
-        <v>8.81</v>
+        <v>0.9</v>
       </c>
       <c r="F135" t="n">
-        <v>0.81</v>
+        <v>0.71</v>
       </c>
       <c r="G135" t="n">
-        <v>-0.41</v>
+        <v>0.52</v>
       </c>
       <c r="H135" t="n">
-        <v>-0.41</v>
+        <v>0.61</v>
       </c>
       <c r="I135" t="n">
-        <v>-0.38</v>
+        <v>0.98</v>
       </c>
       <c r="J135" t="n">
-        <v>-1.2</v>
+        <v>2.11</v>
       </c>
       <c r="K135" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L135" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="136">
@@ -5595,37 +5598,37 @@
         <v>44</v>
       </c>
       <c r="B136" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="C136" t="n">
-        <v>195.88</v>
+        <v>12.49</v>
       </c>
       <c r="D136" t="n">
-        <v>621.75</v>
+        <v>53.45</v>
       </c>
       <c r="E136" t="n">
-        <v>8.84</v>
+        <v>1.3</v>
       </c>
       <c r="F136" t="n">
-        <v>0.78</v>
+        <v>0.69</v>
       </c>
       <c r="G136" t="n">
-        <v>-0.41</v>
+        <v>-1.98</v>
       </c>
       <c r="H136" t="n">
-        <v>-0.42</v>
+        <v>-1.95</v>
       </c>
       <c r="I136" t="n">
-        <v>-0.39</v>
+        <v>-0.66</v>
       </c>
       <c r="J136" t="n">
-        <v>-1.22</v>
+        <v>-4.58</v>
       </c>
       <c r="K136" t="n">
         <v>0</v>
       </c>
       <c r="L136" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="137">
@@ -5633,37 +5636,37 @@
         <v>44</v>
       </c>
       <c r="B137" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="C137" t="n">
-        <v>195.9</v>
+        <v>8.71</v>
       </c>
       <c r="D137" t="n">
-        <v>628.31</v>
+        <v>37.5</v>
       </c>
       <c r="E137" t="n">
-        <v>10.26</v>
+        <v>1.16</v>
       </c>
       <c r="F137" t="n">
-        <v>0.83</v>
+        <v>0.73</v>
       </c>
       <c r="G137" t="n">
-        <v>-0.41</v>
+        <v>0.49</v>
       </c>
       <c r="H137" t="n">
-        <v>-0.45</v>
+        <v>0.64</v>
       </c>
       <c r="I137" t="n">
-        <v>-0.78</v>
+        <v>-0.06</v>
       </c>
       <c r="J137" t="n">
-        <v>-1.64</v>
+        <v>1.07</v>
       </c>
       <c r="K137" t="n">
         <v>0</v>
       </c>
       <c r="L137" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="138">
@@ -5671,37 +5674,37 @@
         <v>44</v>
       </c>
       <c r="B138" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C138" t="n">
-        <v>1.22</v>
+        <v>9.32</v>
       </c>
       <c r="D138" t="n">
-        <v>0.11</v>
+        <v>42.19</v>
       </c>
       <c r="E138" t="n">
-        <v>0.66</v>
+        <v>0.89</v>
       </c>
       <c r="F138" t="n">
-        <v>0.76</v>
+        <v>0.55</v>
       </c>
       <c r="G138" t="n">
-        <v>2.04</v>
+        <v>0.09</v>
       </c>
       <c r="H138" t="n">
-        <v>2.04</v>
+        <v>-0.12</v>
       </c>
       <c r="I138" t="n">
-        <v>1.85</v>
+        <v>1.03</v>
       </c>
       <c r="J138" t="n">
-        <v>5.93</v>
+        <v>1</v>
       </c>
       <c r="K138" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L138" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="139">
@@ -5709,37 +5712,37 @@
         <v>44</v>
       </c>
       <c r="B139" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C139" t="n">
-        <v>195.88</v>
+        <v>8.31</v>
       </c>
       <c r="D139" t="n">
-        <v>622.48</v>
+        <v>37.94</v>
       </c>
       <c r="E139" t="n">
-        <v>9.94</v>
+        <v>1.53</v>
       </c>
       <c r="F139" t="n">
-        <v>0.82</v>
+        <v>0.81</v>
       </c>
       <c r="G139" t="n">
-        <v>-0.41</v>
+        <v>0.75</v>
       </c>
       <c r="H139" t="n">
-        <v>-0.42</v>
+        <v>0.57</v>
       </c>
       <c r="I139" t="n">
-        <v>-0.7</v>
+        <v>-1.57</v>
       </c>
       <c r="J139" t="n">
-        <v>-1.53</v>
+        <v>-0.25</v>
       </c>
       <c r="K139" t="n">
         <v>0</v>
       </c>
       <c r="L139" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="140">
@@ -5747,37 +5750,37 @@
         <v>45</v>
       </c>
       <c r="B140" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C140" t="n">
-        <v>193.61</v>
+        <v>6.93</v>
       </c>
       <c r="D140" t="n">
-        <v>361.08</v>
+        <v>16.43</v>
       </c>
       <c r="E140" t="n">
-        <v>12.93</v>
+        <v>4.86</v>
       </c>
       <c r="F140" t="n">
-        <v>0.76</v>
+        <v>0.11</v>
       </c>
       <c r="G140" t="n">
-        <v>-0.41</v>
+        <v>1.25</v>
       </c>
       <c r="H140" t="n">
-        <v>-0.4</v>
+        <v>1.07</v>
       </c>
       <c r="I140" t="n">
-        <v>-0.45</v>
+        <v>-2.03</v>
       </c>
       <c r="J140" t="n">
-        <v>-1.26</v>
+        <v>0.29</v>
       </c>
       <c r="K140" t="n">
         <v>0</v>
       </c>
       <c r="L140" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="141">
@@ -5785,37 +5788,37 @@
         <v>45</v>
       </c>
       <c r="B141" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="C141" t="n">
-        <v>193.41</v>
+        <v>9.95</v>
       </c>
       <c r="D141" t="n">
-        <v>345.76</v>
+        <v>19.51</v>
       </c>
       <c r="E141" t="n">
-        <v>17.42</v>
+        <v>1.77</v>
       </c>
       <c r="F141" t="n">
-        <v>0.79</v>
+        <v>0.03</v>
       </c>
       <c r="G141" t="n">
-        <v>-0.41</v>
+        <v>0.35</v>
       </c>
       <c r="H141" t="n">
-        <v>-0.3</v>
+        <v>0.52</v>
       </c>
       <c r="I141" t="n">
-        <v>-1.27</v>
+        <v>0.3</v>
       </c>
       <c r="J141" t="n">
-        <v>-1.97</v>
+        <v>1.17</v>
       </c>
       <c r="K141" t="n">
         <v>0</v>
       </c>
       <c r="L141" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="142">
@@ -5823,37 +5826,37 @@
         <v>45</v>
       </c>
       <c r="B142" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C142" t="n">
-        <v>1.45</v>
+        <v>13.52</v>
       </c>
       <c r="D142" t="n">
-        <v>0.1</v>
+        <v>27.36</v>
       </c>
       <c r="E142" t="n">
-        <v>0.9</v>
+        <v>1.54</v>
       </c>
       <c r="F142" t="n">
-        <v>0.68</v>
+        <v>0.02</v>
       </c>
       <c r="G142" t="n">
-        <v>2.04</v>
+        <v>-0.71</v>
       </c>
       <c r="H142" t="n">
-        <v>2.03</v>
+        <v>-0.9</v>
       </c>
       <c r="I142" t="n">
-        <v>1.76</v>
+        <v>0.47</v>
       </c>
       <c r="J142" t="n">
-        <v>5.83</v>
+        <v>-1.13</v>
       </c>
       <c r="K142" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L142" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="143">
@@ -5861,37 +5864,37 @@
         <v>45</v>
       </c>
       <c r="B143" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="C143" t="n">
-        <v>193.65</v>
+        <v>8.05</v>
       </c>
       <c r="D143" t="n">
-        <v>364.88</v>
+        <v>16.82</v>
       </c>
       <c r="E143" t="n">
-        <v>11.54</v>
+        <v>1.82</v>
       </c>
       <c r="F143" t="n">
-        <v>0.7</v>
+        <v>0.07</v>
       </c>
       <c r="G143" t="n">
-        <v>-0.41</v>
+        <v>0.92</v>
       </c>
       <c r="H143" t="n">
-        <v>-0.43</v>
+        <v>1</v>
       </c>
       <c r="I143" t="n">
-        <v>-0.19</v>
+        <v>0.27</v>
       </c>
       <c r="J143" t="n">
-        <v>-1.03</v>
+        <v>2.19</v>
       </c>
       <c r="K143" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L143" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="144">
@@ -5899,37 +5902,37 @@
         <v>45</v>
       </c>
       <c r="B144" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C144" t="n">
-        <v>194.03</v>
+        <v>15.61</v>
       </c>
       <c r="D144" t="n">
-        <v>387.38</v>
+        <v>29.31</v>
       </c>
       <c r="E144" t="n">
-        <v>11.02</v>
+        <v>1.66</v>
       </c>
       <c r="F144" t="n">
-        <v>0.71</v>
+        <v>0.02</v>
       </c>
       <c r="G144" t="n">
-        <v>-0.41</v>
+        <v>-1.32</v>
       </c>
       <c r="H144" t="n">
-        <v>-0.58</v>
+        <v>-1.25</v>
       </c>
       <c r="I144" t="n">
-        <v>-0.1</v>
+        <v>0.39</v>
       </c>
       <c r="J144" t="n">
-        <v>-1.09</v>
+        <v>-2.18</v>
       </c>
       <c r="K144" t="n">
         <v>0</v>
       </c>
       <c r="L144" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="145">
@@ -5937,37 +5940,37 @@
         <v>45</v>
       </c>
       <c r="B145" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C145" t="n">
-        <v>193.37</v>
+        <v>12.77</v>
       </c>
       <c r="D145" t="n">
-        <v>349.78</v>
+        <v>24.9</v>
       </c>
       <c r="E145" t="n">
-        <v>9.15</v>
+        <v>1.39</v>
       </c>
       <c r="F145" t="n">
-        <v>0.57</v>
+        <v>0.01</v>
       </c>
       <c r="G145" t="n">
-        <v>-0.41</v>
+        <v>-0.48</v>
       </c>
       <c r="H145" t="n">
-        <v>-0.33</v>
+        <v>-0.45</v>
       </c>
       <c r="I145" t="n">
-        <v>0.25</v>
+        <v>0.59</v>
       </c>
       <c r="J145" t="n">
-        <v>-0.48</v>
+        <v>-0.34</v>
       </c>
       <c r="K145" t="n">
         <v>0</v>
       </c>
       <c r="L145" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="146">
@@ -5975,37 +5978,37 @@
         <v>46</v>
       </c>
       <c r="B146" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="C146" t="n">
-        <v>187.98</v>
+        <v>7.62</v>
       </c>
       <c r="D146" t="n">
-        <v>160.54</v>
+        <v>9.93</v>
       </c>
       <c r="E146" t="n">
-        <v>64.65</v>
+        <v>0.98</v>
       </c>
       <c r="F146" t="n">
-        <v>0.1</v>
+        <v>0.07</v>
       </c>
       <c r="G146" t="n">
-        <v>-0.4</v>
+        <v>1.33</v>
       </c>
       <c r="H146" t="n">
-        <v>-0.26</v>
+        <v>1.38</v>
       </c>
       <c r="I146" t="n">
-        <v>-1.94</v>
+        <v>1.8</v>
       </c>
       <c r="J146" t="n">
-        <v>-2.6</v>
+        <v>4.51</v>
       </c>
       <c r="K146" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L146" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="147">
@@ -6013,37 +6016,37 @@
         <v>46</v>
       </c>
       <c r="B147" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="C147" t="n">
-        <v>2.9</v>
+        <v>10.2</v>
       </c>
       <c r="D147" t="n">
-        <v>0.16</v>
+        <v>13.18</v>
       </c>
       <c r="E147" t="n">
-        <v>1.67</v>
+        <v>2.39</v>
       </c>
       <c r="F147" t="n">
-        <v>0.02</v>
+        <v>0.12</v>
       </c>
       <c r="G147" t="n">
-        <v>2.04</v>
+        <v>0.66</v>
       </c>
       <c r="H147" t="n">
-        <v>2.03</v>
+        <v>0.68</v>
       </c>
       <c r="I147" t="n">
-        <v>0.89</v>
+        <v>-0.34</v>
       </c>
       <c r="J147" t="n">
-        <v>4.96</v>
+        <v>1.01</v>
       </c>
       <c r="K147" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L147" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="148">
@@ -6054,34 +6057,34 @@
         <v>16</v>
       </c>
       <c r="C148" t="n">
-        <v>188.63</v>
+        <v>16.54</v>
       </c>
       <c r="D148" t="n">
-        <v>171.4</v>
+        <v>20.79</v>
       </c>
       <c r="E148" t="n">
-        <v>17.7</v>
+        <v>2.53</v>
       </c>
       <c r="F148" t="n">
-        <v>0.02</v>
+        <v>0.14</v>
       </c>
       <c r="G148" t="n">
-        <v>-0.41</v>
+        <v>-0.97</v>
       </c>
       <c r="H148" t="n">
-        <v>-0.41</v>
+        <v>-0.95</v>
       </c>
       <c r="I148" t="n">
-        <v>0.17</v>
+        <v>-0.54</v>
       </c>
       <c r="J148" t="n">
-        <v>-0.65</v>
+        <v>-2.46</v>
       </c>
       <c r="K148" t="n">
         <v>0</v>
       </c>
       <c r="L148" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="149">
@@ -6089,37 +6092,37 @@
         <v>46</v>
       </c>
       <c r="B149" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="C149" t="n">
-        <v>189.16</v>
+        <v>16.2</v>
       </c>
       <c r="D149" t="n">
-        <v>181.6</v>
+        <v>20.69</v>
       </c>
       <c r="E149" t="n">
-        <v>11.62</v>
+        <v>1.85</v>
       </c>
       <c r="F149" t="n">
-        <v>0.01</v>
+        <v>0.11</v>
       </c>
       <c r="G149" t="n">
-        <v>-0.42</v>
+        <v>-0.88</v>
       </c>
       <c r="H149" t="n">
-        <v>-0.56</v>
+        <v>-0.93</v>
       </c>
       <c r="I149" t="n">
-        <v>0.44</v>
+        <v>0.49</v>
       </c>
       <c r="J149" t="n">
-        <v>-0.53</v>
+        <v>-1.32</v>
       </c>
       <c r="K149" t="n">
         <v>0</v>
       </c>
       <c r="L149" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="150">
@@ -6127,37 +6130,37 @@
         <v>46</v>
       </c>
       <c r="B150" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="C150" t="n">
-        <v>188.9</v>
+        <v>15.89</v>
       </c>
       <c r="D150" t="n">
-        <v>177</v>
+        <v>19.83</v>
       </c>
       <c r="E150" t="n">
-        <v>10.95</v>
+        <v>2.5</v>
       </c>
       <c r="F150" t="n">
-        <v>0.01</v>
+        <v>0.13</v>
       </c>
       <c r="G150" t="n">
-        <v>-0.41</v>
+        <v>-0.8</v>
       </c>
       <c r="H150" t="n">
+        <v>-0.74</v>
+      </c>
+      <c r="I150" t="n">
         <v>-0.49</v>
       </c>
-      <c r="I150" t="n">
-        <v>0.47</v>
-      </c>
       <c r="J150" t="n">
-        <v>-0.43</v>
+        <v>-2.04</v>
       </c>
       <c r="K150" t="n">
         <v>0</v>
       </c>
       <c r="L150" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="151">
@@ -6168,34 +6171,34 @@
         <v>18</v>
       </c>
       <c r="C151" t="n">
-        <v>188.23</v>
+        <v>10.21</v>
       </c>
       <c r="D151" t="n">
-        <v>165</v>
+        <v>13.77</v>
       </c>
       <c r="E151" t="n">
-        <v>21.77</v>
+        <v>2.78</v>
       </c>
       <c r="F151" t="n">
-        <v>0.06</v>
+        <v>0.01</v>
       </c>
       <c r="G151" t="n">
-        <v>-0.4</v>
+        <v>0.66</v>
       </c>
       <c r="H151" t="n">
-        <v>-0.32</v>
+        <v>0.56</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.02</v>
+        <v>-0.93</v>
       </c>
       <c r="J151" t="n">
-        <v>-0.74</v>
+        <v>0.29</v>
       </c>
       <c r="K151" t="n">
         <v>0</v>
       </c>
       <c r="L151" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="152">
@@ -6203,37 +6206,37 @@
         <v>47</v>
       </c>
       <c r="B152" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C152" t="n">
-        <v>183.53</v>
+        <v>27.09</v>
       </c>
       <c r="D152" t="n">
-        <v>104.85</v>
+        <v>16.65</v>
       </c>
       <c r="E152" t="n">
-        <v>12.44</v>
+        <v>2.15</v>
       </c>
       <c r="F152" t="n">
-        <v>0.07</v>
+        <v>0.53</v>
       </c>
       <c r="G152" t="n">
-        <v>-0.39</v>
+        <v>0.41</v>
       </c>
       <c r="H152" t="n">
-        <v>-0.19</v>
+        <v>0.27</v>
       </c>
       <c r="I152" t="n">
-        <v>0.35</v>
+        <v>0.48</v>
       </c>
       <c r="J152" t="n">
-        <v>-0.23</v>
+        <v>1.17</v>
       </c>
       <c r="K152" t="n">
         <v>0</v>
       </c>
       <c r="L152" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="153">
@@ -6241,37 +6244,37 @@
         <v>47</v>
       </c>
       <c r="B153" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C153" t="n">
-        <v>184.75</v>
+        <v>71.22</v>
       </c>
       <c r="D153" t="n">
-        <v>113.79</v>
+        <v>28.25</v>
       </c>
       <c r="E153" t="n">
-        <v>22.05</v>
+        <v>6.98</v>
       </c>
       <c r="F153" t="n">
-        <v>0.11</v>
+        <v>0.25</v>
       </c>
       <c r="G153" t="n">
-        <v>-0.41</v>
+        <v>-2.04</v>
       </c>
       <c r="H153" t="n">
-        <v>-0.38</v>
+        <v>-1.95</v>
       </c>
       <c r="I153" t="n">
-        <v>-0.74</v>
+        <v>-2.01</v>
       </c>
       <c r="J153" t="n">
-        <v>-1.53</v>
+        <v>-6</v>
       </c>
       <c r="K153" t="n">
         <v>0</v>
       </c>
       <c r="L153" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="154">
@@ -6282,34 +6285,34 @@
         <v>17</v>
       </c>
       <c r="C154" t="n">
-        <v>3.32</v>
+        <v>26.52</v>
       </c>
       <c r="D154" t="n">
-        <v>0.17</v>
+        <v>14.53</v>
       </c>
       <c r="E154" t="n">
-        <v>2.58</v>
+        <v>2.09</v>
       </c>
       <c r="F154" t="n">
-        <v>0.16</v>
+        <v>0.73</v>
       </c>
       <c r="G154" t="n">
-        <v>2.04</v>
+        <v>0.45</v>
       </c>
       <c r="H154" t="n">
-        <v>2.02</v>
+        <v>0.68</v>
       </c>
       <c r="I154" t="n">
-        <v>1.48</v>
+        <v>0.51</v>
       </c>
       <c r="J154" t="n">
-        <v>5.54</v>
+        <v>1.64</v>
       </c>
       <c r="K154" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L154" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="155">
@@ -6317,37 +6320,37 @@
         <v>47</v>
       </c>
       <c r="B155" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C155" t="n">
-        <v>185.66</v>
+        <v>26.44</v>
       </c>
       <c r="D155" t="n">
-        <v>121.94</v>
+        <v>14.18</v>
       </c>
       <c r="E155" t="n">
-        <v>11.95</v>
+        <v>2.03</v>
       </c>
       <c r="F155" t="n">
-        <v>0.12</v>
+        <v>0.68</v>
       </c>
       <c r="G155" t="n">
-        <v>-0.42</v>
+        <v>0.45</v>
       </c>
       <c r="H155" t="n">
-        <v>-0.55</v>
+        <v>0.75</v>
       </c>
       <c r="I155" t="n">
-        <v>0.41</v>
+        <v>0.55</v>
       </c>
       <c r="J155" t="n">
-        <v>-0.56</v>
+        <v>1.74</v>
       </c>
       <c r="K155" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L155" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="156">
@@ -6355,37 +6358,37 @@
         <v>47</v>
       </c>
       <c r="B156" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="C156" t="n">
-        <v>185.56</v>
+        <v>27.21</v>
       </c>
       <c r="D156" t="n">
-        <v>121.06</v>
+        <v>16.4</v>
       </c>
       <c r="E156" t="n">
-        <v>16.41</v>
+        <v>2.34</v>
       </c>
       <c r="F156" t="n">
-        <v>0.15</v>
+        <v>0.58</v>
       </c>
       <c r="G156" t="n">
-        <v>-0.42</v>
+        <v>0.41</v>
       </c>
       <c r="H156" t="n">
-        <v>-0.53</v>
+        <v>0.32</v>
       </c>
       <c r="I156" t="n">
-        <v>-0.1</v>
+        <v>0.39</v>
       </c>
       <c r="J156" t="n">
-        <v>-1.05</v>
+        <v>1.12</v>
       </c>
       <c r="K156" t="n">
         <v>0</v>
       </c>
       <c r="L156" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="157">
@@ -6393,37 +6396,37 @@
         <v>47</v>
       </c>
       <c r="B157" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="C157" t="n">
-        <v>184.69</v>
+        <v>28.76</v>
       </c>
       <c r="D157" t="n">
-        <v>113.21</v>
+        <v>18.46</v>
       </c>
       <c r="E157" t="n">
-        <v>27.89</v>
+        <v>2.92</v>
       </c>
       <c r="F157" t="n">
-        <v>0.01</v>
+        <v>0.52</v>
       </c>
       <c r="G157" t="n">
-        <v>-0.41</v>
+        <v>0.32</v>
       </c>
       <c r="H157" t="n">
-        <v>-0.37</v>
+        <v>-0.07</v>
       </c>
       <c r="I157" t="n">
-        <v>-1.4</v>
+        <v>0.08</v>
       </c>
       <c r="J157" t="n">
-        <v>-2.18</v>
+        <v>0.33</v>
       </c>
       <c r="K157" t="n">
         <v>0</v>
       </c>
       <c r="L157" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="158">
@@ -6431,37 +6434,37 @@
         <v>48</v>
       </c>
       <c r="B158" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="C158" t="n">
-        <v>127.33</v>
+        <v>92.53</v>
       </c>
       <c r="D158" t="n">
-        <v>14.12</v>
+        <v>4.31</v>
       </c>
       <c r="E158" t="n">
-        <v>4.2</v>
+        <v>6.96</v>
       </c>
       <c r="F158" t="n">
-        <v>0.17</v>
+        <v>0.06</v>
       </c>
       <c r="G158" t="n">
-        <v>0.03</v>
+        <v>-0.03</v>
       </c>
       <c r="H158" t="n">
-        <v>0.65</v>
+        <v>0.16</v>
       </c>
       <c r="I158" t="n">
-        <v>0.52</v>
+        <v>0.37</v>
       </c>
       <c r="J158" t="n">
-        <v>1.21</v>
+        <v>0.5</v>
       </c>
       <c r="K158" t="n">
         <v>0</v>
       </c>
       <c r="L158" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="159">
@@ -6469,37 +6472,37 @@
         <v>48</v>
       </c>
       <c r="B159" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C159" t="n">
-        <v>7.57</v>
+        <v>132.35</v>
       </c>
       <c r="D159" t="n">
-        <v>0.32</v>
+        <v>4.91</v>
       </c>
       <c r="E159" t="n">
-        <v>1.86</v>
+        <v>6.22</v>
       </c>
       <c r="F159" t="n">
-        <v>0.64</v>
+        <v>0.01</v>
       </c>
       <c r="G159" t="n">
-        <v>1.99</v>
+        <v>-1.98</v>
       </c>
       <c r="H159" t="n">
-        <v>1.75</v>
+        <v>-0.73</v>
       </c>
       <c r="I159" t="n">
-        <v>1.78</v>
+        <v>0.39</v>
       </c>
       <c r="J159" t="n">
-        <v>5.52</v>
+        <v>-2.32</v>
       </c>
       <c r="K159" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L159" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="160">
@@ -6507,37 +6510,37 @@
         <v>48</v>
       </c>
       <c r="B160" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C160" t="n">
-        <v>157.66</v>
+        <v>82.62</v>
       </c>
       <c r="D160" t="n">
-        <v>27.3</v>
+        <v>3.84</v>
       </c>
       <c r="E160" t="n">
-        <v>6.98</v>
+        <v>87.74</v>
       </c>
       <c r="F160" t="n">
-        <v>0.5</v>
+        <v>0.02</v>
       </c>
       <c r="G160" t="n">
-        <v>-0.46</v>
+        <v>0.46</v>
       </c>
       <c r="H160" t="n">
-        <v>-0.4</v>
+        <v>0.86</v>
       </c>
       <c r="I160" t="n">
-        <v>-0.98</v>
+        <v>-1.78</v>
       </c>
       <c r="J160" t="n">
-        <v>-1.84</v>
+        <v>-0.47</v>
       </c>
       <c r="K160" t="n">
         <v>0</v>
       </c>
       <c r="L160" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="161">
@@ -6545,37 +6548,31 @@
         <v>48</v>
       </c>
       <c r="B161" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C161" t="n">
-        <v>159.83</v>
+        <v>85.27</v>
       </c>
       <c r="D161" t="n">
-        <v>29.61</v>
-      </c>
-      <c r="E161" t="n">
-        <v>6.02</v>
-      </c>
-      <c r="F161" t="n">
-        <v>0.57</v>
-      </c>
+        <v>3.96</v>
+      </c>
+      <c r="E161"/>
+      <c r="F161"/>
       <c r="G161" t="n">
-        <v>-0.5</v>
+        <v>0.33</v>
       </c>
       <c r="H161" t="n">
-        <v>-0.58</v>
-      </c>
-      <c r="I161" t="n">
-        <v>-0.46</v>
-      </c>
+        <v>0.67</v>
+      </c>
+      <c r="I161"/>
       <c r="J161" t="n">
-        <v>-1.54</v>
+        <v>1</v>
       </c>
       <c r="K161" t="n">
         <v>0</v>
       </c>
       <c r="L161" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="162">
@@ -6583,37 +6580,37 @@
         <v>48</v>
       </c>
       <c r="B162" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="C162" t="n">
-        <v>160.35</v>
+        <v>78.06</v>
       </c>
       <c r="D162" t="n">
-        <v>30.62</v>
+        <v>3.94</v>
       </c>
       <c r="E162" t="n">
-        <v>5.83</v>
+        <v>1.68</v>
       </c>
       <c r="F162" t="n">
-        <v>0.63</v>
+        <v>0.01</v>
       </c>
       <c r="G162" t="n">
-        <v>-0.51</v>
+        <v>0.68</v>
       </c>
       <c r="H162" t="n">
-        <v>-0.66</v>
+        <v>0.7</v>
       </c>
       <c r="I162" t="n">
-        <v>-0.36</v>
+        <v>0.51</v>
       </c>
       <c r="J162" t="n">
-        <v>-1.53</v>
+        <v>1.89</v>
       </c>
       <c r="K162" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L162" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="163">
@@ -6621,37 +6618,37 @@
         <v>48</v>
       </c>
       <c r="B163" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C163" t="n">
-        <v>163.1</v>
+        <v>81.01</v>
       </c>
       <c r="D163" t="n">
-        <v>31.97</v>
+        <v>5.55</v>
       </c>
       <c r="E163" t="n">
-        <v>6.1</v>
+        <v>1.08</v>
       </c>
       <c r="F163" t="n">
-        <v>0.57</v>
+        <v>0.02</v>
       </c>
       <c r="G163" t="n">
-        <v>-0.55</v>
+        <v>0.54</v>
       </c>
       <c r="H163" t="n">
-        <v>-0.77</v>
+        <v>-1.67</v>
       </c>
       <c r="I163" t="n">
-        <v>-0.5</v>
+        <v>0.52</v>
       </c>
       <c r="J163" t="n">
-        <v>-1.82</v>
+        <v>-0.6</v>
       </c>
       <c r="K163" t="n">
         <v>0</v>
       </c>
       <c r="L163" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="164">
@@ -6659,31 +6656,37 @@
         <v>49</v>
       </c>
       <c r="B164" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C164" t="n">
-        <v>77.36</v>
+        <v>13.44</v>
       </c>
       <c r="D164" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="E164"/>
-      <c r="F164"/>
+        <v>13.89</v>
+      </c>
+      <c r="E164" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="F164" t="n">
+        <v>0</v>
+      </c>
       <c r="G164" t="n">
-        <v>1.01</v>
+        <v>-0.34</v>
       </c>
       <c r="H164" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="I164"/>
+        <v>-0.97</v>
+      </c>
+      <c r="I164" t="n">
+        <v>-1.15</v>
+      </c>
       <c r="J164" t="n">
-        <v>1.26</v>
+        <v>-2.47</v>
       </c>
       <c r="K164" t="n">
         <v>0</v>
       </c>
       <c r="L164" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
     </row>
     <row r="165">
@@ -6691,37 +6694,37 @@
         <v>49</v>
       </c>
       <c r="B165" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C165" t="n">
-        <v>103.5</v>
+        <v>12.91</v>
       </c>
       <c r="D165" t="n">
-        <v>3.44</v>
+        <v>12.65</v>
       </c>
       <c r="E165" t="n">
-        <v>1.48</v>
+        <v>2.41</v>
       </c>
       <c r="F165" t="n">
-        <v>0.02</v>
+        <v>0.2</v>
       </c>
       <c r="G165" t="n">
-        <v>-1.28</v>
+        <v>0.17</v>
       </c>
       <c r="H165" t="n">
-        <v>-1.85</v>
+        <v>0.24</v>
       </c>
       <c r="I165" t="n">
-        <v>0.47</v>
+        <v>-0.19</v>
       </c>
       <c r="J165" t="n">
-        <v>-2.66</v>
+        <v>0.22</v>
       </c>
       <c r="K165" t="n">
         <v>0</v>
       </c>
       <c r="L165" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
     </row>
     <row r="166">
@@ -6732,34 +6735,34 @@
         <v>16</v>
       </c>
       <c r="C166" t="n">
-        <v>88.49</v>
+        <v>13.36</v>
       </c>
       <c r="D166" t="n">
-        <v>2.24</v>
+        <v>12.3</v>
       </c>
       <c r="E166" t="n">
-        <v>2.24</v>
+        <v>1.4</v>
       </c>
       <c r="F166" t="n">
-        <v>0.09</v>
+        <v>0.19</v>
       </c>
       <c r="G166" t="n">
-        <v>0.04</v>
+        <v>-0.26</v>
       </c>
       <c r="H166" t="n">
-        <v>0.21</v>
+        <v>0.6</v>
       </c>
       <c r="I166" t="n">
-        <v>0.43</v>
+        <v>0.84</v>
       </c>
       <c r="J166" t="n">
-        <v>0.68</v>
+        <v>1.17</v>
       </c>
       <c r="K166" t="n">
         <v>0</v>
       </c>
       <c r="L166" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
     </row>
     <row r="167">
@@ -6767,37 +6770,37 @@
         <v>49</v>
       </c>
       <c r="B167" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C167" t="n">
-        <v>79.27</v>
+        <v>12.35</v>
       </c>
       <c r="D167" t="n">
-        <v>2.24</v>
+        <v>12.05</v>
       </c>
       <c r="E167" t="n">
-        <v>1.87</v>
+        <v>1.21</v>
       </c>
       <c r="F167" t="n">
-        <v>0.02</v>
+        <v>0.34</v>
       </c>
       <c r="G167" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="H167" t="n">
         <v>0.84</v>
       </c>
-      <c r="H167" t="n">
-        <v>0.21</v>
-      </c>
       <c r="I167" t="n">
-        <v>0.45</v>
+        <v>1.03</v>
       </c>
       <c r="J167" t="n">
-        <v>1.5</v>
+        <v>2.57</v>
       </c>
       <c r="K167" t="n">
         <v>1</v>
       </c>
       <c r="L167" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
     </row>
     <row r="168">
@@ -6805,37 +6808,37 @@
         <v>49</v>
       </c>
       <c r="B168" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C168" t="n">
-        <v>82.66</v>
+        <v>14.75</v>
       </c>
       <c r="D168" t="n">
-        <v>2.37</v>
+        <v>14.43</v>
       </c>
       <c r="E168" t="n">
-        <v>47.11</v>
+        <v>1.56</v>
       </c>
       <c r="F168" t="n">
-        <v>0</v>
+        <v>0.17</v>
       </c>
       <c r="G168" t="n">
-        <v>0.55</v>
+        <v>-1.59</v>
       </c>
       <c r="H168" t="n">
-        <v>-0.02</v>
+        <v>-1.51</v>
       </c>
       <c r="I168" t="n">
-        <v>-1.79</v>
+        <v>0.67</v>
       </c>
       <c r="J168" t="n">
-        <v>-1.26</v>
+        <v>-2.43</v>
       </c>
       <c r="K168" t="n">
         <v>0</v>
       </c>
       <c r="L168" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
     </row>
     <row r="169">
@@ -6843,265 +6846,37 @@
         <v>49</v>
       </c>
       <c r="B169" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C169" t="n">
-        <v>102.11</v>
+        <v>11.69</v>
       </c>
       <c r="D169" t="n">
-        <v>1.66</v>
+        <v>12.09</v>
       </c>
       <c r="E169" t="n">
-        <v>1.86</v>
+        <v>3.38</v>
       </c>
       <c r="F169" t="n">
-        <v>0.17</v>
+        <v>0.19</v>
       </c>
       <c r="G169" t="n">
-        <v>-1.16</v>
+        <v>1.33</v>
       </c>
       <c r="H169" t="n">
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
       <c r="I169" t="n">
-        <v>0.45</v>
+        <v>-1.19</v>
       </c>
       <c r="J169" t="n">
-        <v>0.49</v>
+        <v>0.94</v>
       </c>
       <c r="K169" t="n">
         <v>0</v>
       </c>
       <c r="L169" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="170">
-      <c r="A170" t="s">
         <v>50</v>
-      </c>
-      <c r="B170" t="s">
-        <v>13</v>
-      </c>
-      <c r="C170" t="n">
-        <v>175.04</v>
-      </c>
-      <c r="D170" t="n">
-        <v>61.59</v>
-      </c>
-      <c r="E170" t="n">
-        <v>8.93</v>
-      </c>
-      <c r="F170" t="n">
-        <v>0.19</v>
-      </c>
-      <c r="G170" t="n">
-        <v>-0.39</v>
-      </c>
-      <c r="H170" t="n">
-        <v>-0.32</v>
-      </c>
-      <c r="I170" t="n">
-        <v>0.54</v>
-      </c>
-      <c r="J170" t="n">
-        <v>-0.17</v>
-      </c>
-      <c r="K170" t="n">
-        <v>0</v>
-      </c>
-      <c r="L170" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="171">
-      <c r="A171" t="s">
-        <v>50</v>
-      </c>
-      <c r="B171" t="s">
-        <v>15</v>
-      </c>
-      <c r="C171" t="n">
-        <v>175.79</v>
-      </c>
-      <c r="D171" t="n">
-        <v>63.41</v>
-      </c>
-      <c r="E171" t="n">
-        <v>8.3</v>
-      </c>
-      <c r="F171" t="n">
-        <v>0.36</v>
-      </c>
-      <c r="G171" t="n">
-        <v>-0.4</v>
-      </c>
-      <c r="H171" t="n">
-        <v>-0.39</v>
-      </c>
-      <c r="I171" t="n">
-        <v>0.61</v>
-      </c>
-      <c r="J171" t="n">
-        <v>-0.18</v>
-      </c>
-      <c r="K171" t="n">
-        <v>0</v>
-      </c>
-      <c r="L171" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="172">
-      <c r="A172" t="s">
-        <v>50</v>
-      </c>
-      <c r="B172" t="s">
-        <v>19</v>
-      </c>
-      <c r="C172" t="n">
-        <v>176.73</v>
-      </c>
-      <c r="D172" t="n">
-        <v>65.95</v>
-      </c>
-      <c r="E172" t="n">
-        <v>21.75</v>
-      </c>
-      <c r="F172" t="n">
-        <v>0</v>
-      </c>
-      <c r="G172" t="n">
-        <v>-0.42</v>
-      </c>
-      <c r="H172" t="n">
-        <v>-0.48</v>
-      </c>
-      <c r="I172" t="n">
-        <v>-0.88</v>
-      </c>
-      <c r="J172" t="n">
-        <v>-1.78</v>
-      </c>
-      <c r="K172" t="n">
-        <v>0</v>
-      </c>
-      <c r="L172" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="173">
-      <c r="A173" t="s">
-        <v>50</v>
-      </c>
-      <c r="B173" t="s">
-        <v>17</v>
-      </c>
-      <c r="C173" t="n">
-        <v>3.21</v>
-      </c>
-      <c r="D173" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="E173" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="F173" t="n">
-        <v>0.21</v>
-      </c>
-      <c r="G173" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="H173" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="I173" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="J173" t="n">
-        <v>5.46</v>
-      </c>
-      <c r="K173" t="n">
-        <v>1</v>
-      </c>
-      <c r="L173" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="174">
-      <c r="A174" t="s">
-        <v>50</v>
-      </c>
-      <c r="B174" t="s">
-        <v>18</v>
-      </c>
-      <c r="C174" t="n">
-        <v>176.42</v>
-      </c>
-      <c r="D174" t="n">
-        <v>64.74</v>
-      </c>
-      <c r="E174" t="n">
-        <v>24.63</v>
-      </c>
-      <c r="F174" t="n">
-        <v>0.21</v>
-      </c>
-      <c r="G174" t="n">
-        <v>-0.41</v>
-      </c>
-      <c r="H174" t="n">
-        <v>-0.44</v>
-      </c>
-      <c r="I174" t="n">
-        <v>-1.2</v>
-      </c>
-      <c r="J174" t="n">
-        <v>-2.05</v>
-      </c>
-      <c r="K174" t="n">
-        <v>0</v>
-      </c>
-      <c r="L174" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="175">
-      <c r="A175" t="s">
-        <v>50</v>
-      </c>
-      <c r="B175" t="s">
-        <v>16</v>
-      </c>
-      <c r="C175" t="n">
-        <v>176.15</v>
-      </c>
-      <c r="D175" t="n">
-        <v>64.1</v>
-      </c>
-      <c r="E175" t="n">
-        <v>17.95</v>
-      </c>
-      <c r="F175" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="G175" t="n">
-        <v>-0.41</v>
-      </c>
-      <c r="H175" t="n">
-        <v>-0.41</v>
-      </c>
-      <c r="I175" t="n">
-        <v>-0.46</v>
-      </c>
-      <c r="J175" t="n">
-        <v>-1.28</v>
-      </c>
-      <c r="K175" t="n">
-        <v>0</v>
-      </c>
-      <c r="L175" t="s">
-        <v>51</v>
       </c>
     </row>
   </sheetData>

--- a/Outcome/Publish/figure_data/fig4.xlsx
+++ b/Outcome/Publish/figure_data/fig4.xlsx
@@ -53,7 +53,7 @@
     <t xml:space="preserve">Pneumonia</t>
   </si>
   <si>
-    <t xml:space="preserve">Hybrid*</t>
+    <t xml:space="preserve">Hybrid**</t>
   </si>
   <si>
     <t xml:space="preserve">Respiratory IDs</t>

--- a/Outcome/Publish/figure_data/fig4.xlsx
+++ b/Outcome/Publish/figure_data/fig4.xlsx
@@ -204,9 +204,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
-    <numFmt numFmtId="165" formatCode="mm/dd/yyyy"/>
-  </numFmts>
+  <numFmts count="0"/>
   <fonts count="2">
     <font>
       <sz val="11"/>
@@ -243,7 +241,7 @@
   </cellStyleXfs>
   <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyNumberFormat="1"/>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>

--- a/Outcome/Publish/figure_data/fig4.xlsx
+++ b/Outcome/Publish/figure_data/fig4.xlsx
@@ -207,9 +207,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
-    <numFmt numFmtId="165" formatCode="mm/dd/yyyy"/>
-  </numFmts>
+  <numFmts count="0"/>
   <fonts count="2">
     <font>
       <sz val="11"/>
@@ -246,7 +244,7 @@
   </cellStyleXfs>
   <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyNumberFormat="1"/>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>

--- a/Outcome/Publish/figure_data/fig4.xlsx
+++ b/Outcome/Publish/figure_data/fig4.xlsx
@@ -6,37 +6,38 @@
     <workbookView xWindow="0" yWindow="0" windowWidth="13125" windowHeight="6105" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet 1" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Sheet 2" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Sheet 3" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Sheet 4" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Sheet 5" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Sheet 6" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Sheet 7" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="Sheet 8" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="Sheet 9" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="Sheet 10" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="Sheet 11" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="Sheet 12" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="Sheet 13" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="Sheet 14" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet name="Sheet 15" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet name="Sheet 16" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet name="Sheet 17" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet name="Sheet 18" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet name="Sheet 19" sheetId="19" state="visible" r:id="rId19"/>
-    <sheet name="Sheet 20" sheetId="20" state="visible" r:id="rId20"/>
-    <sheet name="Sheet 21" sheetId="21" state="visible" r:id="rId21"/>
-    <sheet name="Sheet 22" sheetId="22" state="visible" r:id="rId22"/>
-    <sheet name="Sheet 23" sheetId="23" state="visible" r:id="rId23"/>
-    <sheet name="Sheet 24" sheetId="24" state="visible" r:id="rId24"/>
-    <sheet name="Sheet 25" sheetId="25" state="visible" r:id="rId25"/>
+    <sheet name="A" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="B" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="C" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="D" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="E" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="F" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="G" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="H" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="I" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="J" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="K" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="L" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="M" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="N" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="O" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="P" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="Q" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet name="R" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet name="S" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet name="T" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet name="U" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet name="V" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet name="W" sheetId="23" state="visible" r:id="rId23"/>
+    <sheet name="X" sheetId="24" state="visible" r:id="rId24"/>
+    <sheet name="Y" sheetId="25" state="visible" r:id="rId25"/>
+    <sheet name="Z" sheetId="26" state="visible" r:id="rId26"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="86">
   <si>
     <t xml:space="preserve">Group</t>
   </si>
@@ -202,14 +203,105 @@
   <si>
     <t xml:space="preserve">Decrease</t>
   </si>
+  <si>
+    <t xml:space="preserve">StartDate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">type</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EndDate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Period</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Recovery</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34 months</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Balance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">61 months</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43 months</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Not balanced</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56 months</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Not recovered</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35 months</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27 months</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32 months</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33 months</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7 months</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41 months</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4 months</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6 months</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9 months</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29 months</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36 months</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30 months</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54 months</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46 months</t>
+  </si>
+  <si>
+    <t xml:space="preserve">52 months</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40 months</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51 months</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44 months</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28 months</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
-    <numFmt numFmtId="165" formatCode="mm/dd/yyyy"/>
-  </numFmts>
+  <numFmts count="0"/>
   <fonts count="2">
     <font>
       <sz val="11"/>
@@ -246,7 +338,7 @@
   </cellStyleXfs>
   <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyNumberFormat="1"/>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -47500,6 +47592,850 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C1" t="s">
+        <v>56</v>
+      </c>
+      <c r="D1" t="s">
+        <v>57</v>
+      </c>
+      <c r="E1" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B2" s="1" t="n">
+        <v>43831</v>
+      </c>
+      <c r="C2" t="s">
+        <v>59</v>
+      </c>
+      <c r="D2" s="1" t="n">
+        <v>44866</v>
+      </c>
+      <c r="E2" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B3" s="1" t="n">
+        <v>43831</v>
+      </c>
+      <c r="C3" t="s">
+        <v>61</v>
+      </c>
+      <c r="D3" s="1" t="n">
+        <v>45689</v>
+      </c>
+      <c r="E3" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>41</v>
+      </c>
+      <c r="B4" s="1" t="n">
+        <v>43831</v>
+      </c>
+      <c r="C4" t="s">
+        <v>59</v>
+      </c>
+      <c r="D4" s="1" t="n">
+        <v>45139</v>
+      </c>
+      <c r="E4" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B5" s="1" t="n">
+        <v>43831</v>
+      </c>
+      <c r="C5" t="s">
+        <v>61</v>
+      </c>
+      <c r="D5" s="1" t="n">
+        <v>45992</v>
+      </c>
+      <c r="E5" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B6" s="1" t="n">
+        <v>43831</v>
+      </c>
+      <c r="C6" t="s">
+        <v>59</v>
+      </c>
+      <c r="D6" s="1" t="n">
+        <v>45689</v>
+      </c>
+      <c r="E6" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>40</v>
+      </c>
+      <c r="B7" s="1" t="n">
+        <v>43831</v>
+      </c>
+      <c r="C7" t="s">
+        <v>61</v>
+      </c>
+      <c r="D7" s="1" t="n">
+        <v>45992</v>
+      </c>
+      <c r="E7" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s">
+        <v>39</v>
+      </c>
+      <c r="B8" s="1" t="n">
+        <v>43831</v>
+      </c>
+      <c r="C8" t="s">
+        <v>59</v>
+      </c>
+      <c r="D8" s="1" t="n">
+        <v>45536</v>
+      </c>
+      <c r="E8" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s">
+        <v>39</v>
+      </c>
+      <c r="B9" s="1" t="n">
+        <v>43831</v>
+      </c>
+      <c r="C9" t="s">
+        <v>61</v>
+      </c>
+      <c r="D9" s="1" t="n">
+        <v>45992</v>
+      </c>
+      <c r="E9" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s">
+        <v>38</v>
+      </c>
+      <c r="B10" s="1" t="n">
+        <v>43831</v>
+      </c>
+      <c r="C10" t="s">
+        <v>59</v>
+      </c>
+      <c r="D10" s="1" t="n">
+        <v>45689</v>
+      </c>
+      <c r="E10" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s">
+        <v>38</v>
+      </c>
+      <c r="B11" s="1" t="n">
+        <v>43831</v>
+      </c>
+      <c r="C11" t="s">
+        <v>61</v>
+      </c>
+      <c r="D11" s="1" t="n">
+        <v>45992</v>
+      </c>
+      <c r="E11" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s">
+        <v>37</v>
+      </c>
+      <c r="B12" s="1" t="n">
+        <v>43831</v>
+      </c>
+      <c r="C12" t="s">
+        <v>59</v>
+      </c>
+      <c r="D12" s="1" t="n">
+        <v>45992</v>
+      </c>
+      <c r="E12" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s">
+        <v>37</v>
+      </c>
+      <c r="B13" s="1" t="n">
+        <v>43831</v>
+      </c>
+      <c r="C13" t="s">
+        <v>61</v>
+      </c>
+      <c r="D13" s="1" t="n">
+        <v>45992</v>
+      </c>
+      <c r="E13" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="s">
+        <v>35</v>
+      </c>
+      <c r="B14" s="1" t="n">
+        <v>43831</v>
+      </c>
+      <c r="C14" t="s">
+        <v>59</v>
+      </c>
+      <c r="D14" s="1" t="n">
+        <v>44896</v>
+      </c>
+      <c r="E14" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="s">
+        <v>35</v>
+      </c>
+      <c r="B15" s="1" t="n">
+        <v>43831</v>
+      </c>
+      <c r="C15" t="s">
+        <v>61</v>
+      </c>
+      <c r="D15" s="1" t="n">
+        <v>45992</v>
+      </c>
+      <c r="E15" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s">
+        <v>34</v>
+      </c>
+      <c r="B16" s="1" t="n">
+        <v>43831</v>
+      </c>
+      <c r="C16" t="s">
+        <v>59</v>
+      </c>
+      <c r="D16" s="1" t="n">
+        <v>45992</v>
+      </c>
+      <c r="E16" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s">
+        <v>34</v>
+      </c>
+      <c r="B17" s="1" t="n">
+        <v>43831</v>
+      </c>
+      <c r="C17" t="s">
+        <v>61</v>
+      </c>
+      <c r="D17" s="1" t="n">
+        <v>45992</v>
+      </c>
+      <c r="E17" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="s">
+        <v>33</v>
+      </c>
+      <c r="B18" s="1" t="n">
+        <v>43831</v>
+      </c>
+      <c r="C18" t="s">
+        <v>59</v>
+      </c>
+      <c r="D18" s="1" t="n">
+        <v>44652</v>
+      </c>
+      <c r="E18" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="s">
+        <v>33</v>
+      </c>
+      <c r="B19" s="1" t="n">
+        <v>43831</v>
+      </c>
+      <c r="C19" t="s">
+        <v>61</v>
+      </c>
+      <c r="D19" s="1" t="n">
+        <v>44805</v>
+      </c>
+      <c r="E19" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="s">
+        <v>32</v>
+      </c>
+      <c r="B20" s="1" t="n">
+        <v>43831</v>
+      </c>
+      <c r="C20" t="s">
+        <v>59</v>
+      </c>
+      <c r="D20" s="1" t="n">
+        <v>44652</v>
+      </c>
+      <c r="E20" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="s">
+        <v>32</v>
+      </c>
+      <c r="B21" s="1" t="n">
+        <v>43831</v>
+      </c>
+      <c r="C21" t="s">
+        <v>61</v>
+      </c>
+      <c r="D21" s="1" t="n">
+        <v>44835</v>
+      </c>
+      <c r="E21" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="s">
+        <v>31</v>
+      </c>
+      <c r="B22" s="1" t="n">
+        <v>43831</v>
+      </c>
+      <c r="C22" t="s">
+        <v>59</v>
+      </c>
+      <c r="D22" s="1" t="n">
+        <v>44044</v>
+      </c>
+      <c r="E22" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="s">
+        <v>31</v>
+      </c>
+      <c r="B23" s="1" t="n">
+        <v>43831</v>
+      </c>
+      <c r="C23" t="s">
+        <v>61</v>
+      </c>
+      <c r="D23" s="1" t="n">
+        <v>45078</v>
+      </c>
+      <c r="E23" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="s">
+        <v>30</v>
+      </c>
+      <c r="B24" s="1" t="n">
+        <v>43831</v>
+      </c>
+      <c r="C24" t="s">
+        <v>59</v>
+      </c>
+      <c r="D24" s="1" t="n">
+        <v>43952</v>
+      </c>
+      <c r="E24" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="s">
+        <v>30</v>
+      </c>
+      <c r="B25" s="1" t="n">
+        <v>43831</v>
+      </c>
+      <c r="C25" t="s">
+        <v>61</v>
+      </c>
+      <c r="D25" s="1" t="n">
+        <v>44013</v>
+      </c>
+      <c r="E25" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="s">
+        <v>28</v>
+      </c>
+      <c r="B26" s="1" t="n">
+        <v>43831</v>
+      </c>
+      <c r="C26" t="s">
+        <v>59</v>
+      </c>
+      <c r="D26" s="1" t="n">
+        <v>44105</v>
+      </c>
+      <c r="E26" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="s">
+        <v>28</v>
+      </c>
+      <c r="B27" s="1" t="n">
+        <v>43831</v>
+      </c>
+      <c r="C27" t="s">
+        <v>61</v>
+      </c>
+      <c r="D27" s="1" t="n">
+        <v>44805</v>
+      </c>
+      <c r="E27" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="s">
+        <v>27</v>
+      </c>
+      <c r="B28" s="1" t="n">
+        <v>43831</v>
+      </c>
+      <c r="C28" t="s">
+        <v>59</v>
+      </c>
+      <c r="D28" s="1" t="n">
+        <v>44713</v>
+      </c>
+      <c r="E28" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="s">
+        <v>27</v>
+      </c>
+      <c r="B29" s="1" t="n">
+        <v>43831</v>
+      </c>
+      <c r="C29" t="s">
+        <v>61</v>
+      </c>
+      <c r="D29" s="1" t="n">
+        <v>44927</v>
+      </c>
+      <c r="E29" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="s">
+        <v>26</v>
+      </c>
+      <c r="B30" s="1" t="n">
+        <v>43831</v>
+      </c>
+      <c r="C30" t="s">
+        <v>59</v>
+      </c>
+      <c r="D30" s="1" t="n">
+        <v>44713</v>
+      </c>
+      <c r="E30" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="s">
+        <v>26</v>
+      </c>
+      <c r="B31" s="1" t="n">
+        <v>43831</v>
+      </c>
+      <c r="C31" t="s">
+        <v>61</v>
+      </c>
+      <c r="D31" s="1" t="n">
+        <v>45992</v>
+      </c>
+      <c r="E31" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="s">
+        <v>25</v>
+      </c>
+      <c r="B32" s="1" t="n">
+        <v>43831</v>
+      </c>
+      <c r="C32" t="s">
+        <v>59</v>
+      </c>
+      <c r="D32" s="1" t="n">
+        <v>44743</v>
+      </c>
+      <c r="E32" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="s">
+        <v>25</v>
+      </c>
+      <c r="B33" s="1" t="n">
+        <v>43831</v>
+      </c>
+      <c r="C33" t="s">
+        <v>61</v>
+      </c>
+      <c r="D33" s="1" t="n">
+        <v>45474</v>
+      </c>
+      <c r="E33" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="s">
+        <v>24</v>
+      </c>
+      <c r="B34" s="1" t="n">
+        <v>43831</v>
+      </c>
+      <c r="C34" t="s">
+        <v>59</v>
+      </c>
+      <c r="D34" s="1" t="n">
+        <v>45231</v>
+      </c>
+      <c r="E34" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="s">
+        <v>24</v>
+      </c>
+      <c r="B35" s="1" t="n">
+        <v>43831</v>
+      </c>
+      <c r="C35" t="s">
+        <v>61</v>
+      </c>
+      <c r="D35" s="1" t="n">
+        <v>45992</v>
+      </c>
+      <c r="E35" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="s">
+        <v>22</v>
+      </c>
+      <c r="B36" s="1" t="n">
+        <v>43831</v>
+      </c>
+      <c r="C36" t="s">
+        <v>59</v>
+      </c>
+      <c r="D36" s="1" t="n">
+        <v>44866</v>
+      </c>
+      <c r="E36" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="s">
+        <v>22</v>
+      </c>
+      <c r="B37" s="1" t="n">
+        <v>43831</v>
+      </c>
+      <c r="C37" t="s">
+        <v>61</v>
+      </c>
+      <c r="D37" s="1" t="n">
+        <v>45689</v>
+      </c>
+      <c r="E37" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="s">
+        <v>21</v>
+      </c>
+      <c r="B38" s="1" t="n">
+        <v>43831</v>
+      </c>
+      <c r="C38" t="s">
+        <v>59</v>
+      </c>
+      <c r="D38" s="1" t="n">
+        <v>45992</v>
+      </c>
+      <c r="E38" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="s">
+        <v>21</v>
+      </c>
+      <c r="B39" s="1" t="n">
+        <v>43831</v>
+      </c>
+      <c r="C39" t="s">
+        <v>61</v>
+      </c>
+      <c r="D39" s="1" t="n">
+        <v>45992</v>
+      </c>
+      <c r="E39" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="s">
+        <v>20</v>
+      </c>
+      <c r="B40" s="1" t="n">
+        <v>43831</v>
+      </c>
+      <c r="C40" t="s">
+        <v>59</v>
+      </c>
+      <c r="D40" s="1" t="n">
+        <v>44927</v>
+      </c>
+      <c r="E40" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="s">
+        <v>20</v>
+      </c>
+      <c r="B41" s="1" t="n">
+        <v>43831</v>
+      </c>
+      <c r="C41" t="s">
+        <v>61</v>
+      </c>
+      <c r="D41" s="1" t="n">
+        <v>45413</v>
+      </c>
+      <c r="E41" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="s">
+        <v>19</v>
+      </c>
+      <c r="B42" s="1" t="n">
+        <v>43831</v>
+      </c>
+      <c r="C42" t="s">
+        <v>59</v>
+      </c>
+      <c r="D42" s="1" t="n">
+        <v>45047</v>
+      </c>
+      <c r="E42" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="s">
+        <v>19</v>
+      </c>
+      <c r="B43" s="1" t="n">
+        <v>43831</v>
+      </c>
+      <c r="C43" t="s">
+        <v>61</v>
+      </c>
+      <c r="D43" s="1" t="n">
+        <v>45536</v>
+      </c>
+      <c r="E43" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="s">
+        <v>18</v>
+      </c>
+      <c r="B44" s="1" t="n">
+        <v>43831</v>
+      </c>
+      <c r="C44" t="s">
+        <v>59</v>
+      </c>
+      <c r="D44" s="1" t="n">
+        <v>44927</v>
+      </c>
+      <c r="E44" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="s">
+        <v>18</v>
+      </c>
+      <c r="B45" s="1" t="n">
+        <v>43831</v>
+      </c>
+      <c r="C45" t="s">
+        <v>61</v>
+      </c>
+      <c r="D45" s="1" t="n">
+        <v>45383</v>
+      </c>
+      <c r="E45" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="s">
+        <v>17</v>
+      </c>
+      <c r="B46" s="1" t="n">
+        <v>43831</v>
+      </c>
+      <c r="C46" t="s">
+        <v>59</v>
+      </c>
+      <c r="D46" s="1" t="n">
+        <v>45170</v>
+      </c>
+      <c r="E46" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="s">
+        <v>17</v>
+      </c>
+      <c r="B47" s="1" t="n">
+        <v>43831</v>
+      </c>
+      <c r="C47" t="s">
+        <v>61</v>
+      </c>
+      <c r="D47" s="1" t="n">
+        <v>45992</v>
+      </c>
+      <c r="E47" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="s">
+        <v>8</v>
+      </c>
+      <c r="B48" s="1" t="n">
+        <v>43831</v>
+      </c>
+      <c r="C48" t="s">
+        <v>59</v>
+      </c>
+      <c r="D48" s="1" t="n">
+        <v>44682</v>
+      </c>
+      <c r="E48" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="s">
+        <v>8</v>
+      </c>
+      <c r="B49" s="1" t="n">
+        <v>43831</v>
+      </c>
+      <c r="C49" t="s">
+        <v>61</v>
+      </c>
+      <c r="D49" s="1" t="n">
+        <v>44866</v>
+      </c>
+      <c r="E49" t="s">
+        <v>60</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <dimension ref="A1"/>

--- a/Outcome/Publish/figure_data/fig4.xlsx
+++ b/Outcome/Publish/figure_data/fig4.xlsx
@@ -301,7 +301,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="165" formatCode="mm/dd/yyyy"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <sz val="11"/>
@@ -338,7 +340,7 @@
   </cellStyleXfs>
   <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -666,7 +668,7 @@
         <v>10</v>
       </c>
       <c r="E2" t="n">
-        <v>2.9</v>
+        <v>2.79</v>
       </c>
       <c r="F2" t="s">
         <v>11</v>
@@ -689,7 +691,7 @@
         <v>9</v>
       </c>
       <c r="E3" t="n">
-        <v>7.44</v>
+        <v>7.31</v>
       </c>
       <c r="F3" t="s">
         <v>12</v>
@@ -712,7 +714,7 @@
         <v>13</v>
       </c>
       <c r="E4" t="n">
-        <v>-1.3</v>
+        <v>-0.7</v>
       </c>
       <c r="F4" t="s">
         <v>11</v>
@@ -735,7 +737,7 @@
         <v>14</v>
       </c>
       <c r="E5" t="n">
-        <v>-11.78</v>
+        <v>-11.88</v>
       </c>
       <c r="F5" t="s">
         <v>11</v>
@@ -758,7 +760,7 @@
         <v>15</v>
       </c>
       <c r="E6" t="n">
-        <v>-2.79</v>
+        <v>-2.94</v>
       </c>
       <c r="F6" t="s">
         <v>11</v>
@@ -781,7 +783,7 @@
         <v>16</v>
       </c>
       <c r="E7" t="n">
-        <v>5.53</v>
+        <v>5.41</v>
       </c>
       <c r="F7" t="s">
         <v>11</v>
@@ -804,7 +806,7 @@
         <v>10</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.61</v>
+        <v>-0.73</v>
       </c>
       <c r="F8" t="s">
         <v>11</v>
@@ -827,7 +829,7 @@
         <v>9</v>
       </c>
       <c r="E9" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="F9" t="s">
         <v>11</v>
@@ -850,7 +852,7 @@
         <v>13</v>
       </c>
       <c r="E10" t="n">
-        <v>1.92</v>
+        <v>2.08</v>
       </c>
       <c r="F10" t="s">
         <v>12</v>
@@ -873,7 +875,7 @@
         <v>14</v>
       </c>
       <c r="E11" t="n">
-        <v>0.63</v>
+        <v>0.69</v>
       </c>
       <c r="F11" t="s">
         <v>11</v>
@@ -896,7 +898,7 @@
         <v>15</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.82</v>
+        <v>-0.75</v>
       </c>
       <c r="F12" t="s">
         <v>11</v>
@@ -919,7 +921,7 @@
         <v>16</v>
       </c>
       <c r="E13" t="n">
-        <v>-2.31</v>
+        <v>-2.48</v>
       </c>
       <c r="F13" t="s">
         <v>11</v>
@@ -942,7 +944,7 @@
         <v>10</v>
       </c>
       <c r="E14" t="n">
-        <v>-4.02</v>
+        <v>-3.99</v>
       </c>
       <c r="F14" t="s">
         <v>11</v>
@@ -965,7 +967,7 @@
         <v>9</v>
       </c>
       <c r="E15" t="n">
-        <v>3.07</v>
+        <v>3.1</v>
       </c>
       <c r="F15" t="s">
         <v>11</v>
@@ -988,7 +990,7 @@
         <v>13</v>
       </c>
       <c r="E16" t="n">
-        <v>3.99</v>
+        <v>3.91</v>
       </c>
       <c r="F16" t="s">
         <v>12</v>
@@ -1057,7 +1059,7 @@
         <v>16</v>
       </c>
       <c r="E19" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="F19" t="s">
         <v>11</v>
@@ -1080,7 +1082,7 @@
         <v>10</v>
       </c>
       <c r="E20" t="n">
-        <v>9.16</v>
+        <v>9.17</v>
       </c>
       <c r="F20" t="s">
         <v>12</v>
@@ -1103,7 +1105,7 @@
         <v>9</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.57</v>
+        <v>-2.56</v>
       </c>
       <c r="F21" t="s">
         <v>11</v>
@@ -1126,7 +1128,7 @@
         <v>13</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.1</v>
+        <v>-1.13</v>
       </c>
       <c r="F22" t="s">
         <v>11</v>
@@ -1149,7 +1151,7 @@
         <v>14</v>
       </c>
       <c r="E23" t="n">
-        <v>2.93</v>
+        <v>2.94</v>
       </c>
       <c r="F23" t="s">
         <v>11</v>
@@ -1195,7 +1197,7 @@
         <v>16</v>
       </c>
       <c r="E25" t="n">
-        <v>3.67</v>
+        <v>3.68</v>
       </c>
       <c r="F25" t="s">
         <v>11</v>
@@ -1218,7 +1220,7 @@
         <v>10</v>
       </c>
       <c r="E26" t="n">
-        <v>2.29</v>
+        <v>2.31</v>
       </c>
       <c r="F26" t="s">
         <v>11</v>
@@ -1241,7 +1243,7 @@
         <v>9</v>
       </c>
       <c r="E27" t="n">
-        <v>2.92</v>
+        <v>2.91</v>
       </c>
       <c r="F27" t="s">
         <v>11</v>
@@ -1264,7 +1266,7 @@
         <v>13</v>
       </c>
       <c r="E28" t="n">
-        <v>4.85</v>
+        <v>4.84</v>
       </c>
       <c r="F28" t="s">
         <v>12</v>
@@ -1310,7 +1312,7 @@
         <v>15</v>
       </c>
       <c r="E30" t="n">
-        <v>0.07</v>
+        <v>0.1</v>
       </c>
       <c r="F30" t="s">
         <v>11</v>
@@ -1333,7 +1335,7 @@
         <v>16</v>
       </c>
       <c r="E31" t="n">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="F31" t="s">
         <v>11</v>
@@ -1356,7 +1358,7 @@
         <v>10</v>
       </c>
       <c r="E32" t="n">
-        <v>8.35</v>
+        <v>8.41</v>
       </c>
       <c r="F32" t="s">
         <v>12</v>
@@ -1379,7 +1381,7 @@
         <v>9</v>
       </c>
       <c r="E33" t="n">
-        <v>1.47</v>
+        <v>1.58</v>
       </c>
       <c r="F33" t="s">
         <v>11</v>
@@ -1402,7 +1404,7 @@
         <v>13</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.07</v>
+        <v>-0.69</v>
       </c>
       <c r="F34" t="s">
         <v>11</v>
@@ -1425,7 +1427,7 @@
         <v>14</v>
       </c>
       <c r="E35" t="n">
-        <v>-14.08</v>
+        <v>-13.89</v>
       </c>
       <c r="F35" t="s">
         <v>11</v>
@@ -1448,7 +1450,7 @@
         <v>15</v>
       </c>
       <c r="E36" t="n">
-        <v>4.06</v>
+        <v>4.22</v>
       </c>
       <c r="F36" t="s">
         <v>11</v>
@@ -1471,7 +1473,7 @@
         <v>16</v>
       </c>
       <c r="E37" t="n">
-        <v>0.27</v>
+        <v>0.37</v>
       </c>
       <c r="F37" t="s">
         <v>11</v>
@@ -1494,7 +1496,7 @@
         <v>10</v>
       </c>
       <c r="E38" t="n">
-        <v>-6.06</v>
+        <v>-6.07</v>
       </c>
       <c r="F38" t="s">
         <v>11</v>
@@ -1517,7 +1519,7 @@
         <v>9</v>
       </c>
       <c r="E39" t="n">
-        <v>3.81</v>
+        <v>3.79</v>
       </c>
       <c r="F39" t="s">
         <v>11</v>
@@ -1540,7 +1542,7 @@
         <v>13</v>
       </c>
       <c r="E40" t="n">
-        <v>4.03</v>
+        <v>4.13</v>
       </c>
       <c r="F40" t="s">
         <v>11</v>
@@ -1563,7 +1565,7 @@
         <v>14</v>
       </c>
       <c r="E41" t="n">
-        <v>0.02</v>
+        <v>-0.01</v>
       </c>
       <c r="F41" t="s">
         <v>11</v>
@@ -1586,7 +1588,7 @@
         <v>15</v>
       </c>
       <c r="E42" t="n">
-        <v>-8.79</v>
+        <v>-8.8</v>
       </c>
       <c r="F42" t="s">
         <v>11</v>
@@ -1609,7 +1611,7 @@
         <v>16</v>
       </c>
       <c r="E43" t="n">
-        <v>6.98</v>
+        <v>6.96</v>
       </c>
       <c r="F43" t="s">
         <v>12</v>
@@ -1655,7 +1657,7 @@
         <v>9</v>
       </c>
       <c r="E45" t="n">
-        <v>-0.94</v>
+        <v>-0.95</v>
       </c>
       <c r="F45" t="s">
         <v>11</v>
@@ -1701,7 +1703,7 @@
         <v>14</v>
       </c>
       <c r="E47" t="n">
-        <v>-5.9</v>
+        <v>-5.91</v>
       </c>
       <c r="F47" t="s">
         <v>11</v>
@@ -1770,7 +1772,7 @@
         <v>10</v>
       </c>
       <c r="E50" t="n">
-        <v>-3.3</v>
+        <v>-3.31</v>
       </c>
       <c r="F50" t="s">
         <v>11</v>
@@ -1793,7 +1795,7 @@
         <v>9</v>
       </c>
       <c r="E51" t="n">
-        <v>-1.53</v>
+        <v>-1.54</v>
       </c>
       <c r="F51" t="s">
         <v>11</v>
@@ -1816,7 +1818,7 @@
         <v>13</v>
       </c>
       <c r="E52" t="n">
-        <v>4.79</v>
+        <v>4.84</v>
       </c>
       <c r="F52" t="s">
         <v>12</v>
@@ -1839,7 +1841,7 @@
         <v>14</v>
       </c>
       <c r="E53" t="n">
-        <v>-1.1</v>
+        <v>-1.12</v>
       </c>
       <c r="F53" t="s">
         <v>11</v>
@@ -1862,7 +1864,7 @@
         <v>15</v>
       </c>
       <c r="E54" t="n">
-        <v>2.05</v>
+        <v>2.03</v>
       </c>
       <c r="F54" t="s">
         <v>11</v>
@@ -1908,7 +1910,7 @@
         <v>10</v>
       </c>
       <c r="E56" t="n">
-        <v>6.92</v>
+        <v>6.94</v>
       </c>
       <c r="F56" t="s">
         <v>12</v>
@@ -1931,7 +1933,7 @@
         <v>9</v>
       </c>
       <c r="E57" t="n">
-        <v>-5.69</v>
+        <v>-5.7</v>
       </c>
       <c r="F57" t="s">
         <v>11</v>
@@ -1954,7 +1956,7 @@
         <v>13</v>
       </c>
       <c r="E58" t="n">
-        <v>0.91</v>
+        <v>0.86</v>
       </c>
       <c r="F58" t="s">
         <v>11</v>
@@ -1977,7 +1979,7 @@
         <v>14</v>
       </c>
       <c r="E59" t="n">
-        <v>-2.12</v>
+        <v>-2.13</v>
       </c>
       <c r="F59" t="s">
         <v>11</v>
@@ -2000,7 +2002,7 @@
         <v>15</v>
       </c>
       <c r="E60" t="n">
-        <v>3.87</v>
+        <v>3.94</v>
       </c>
       <c r="F60" t="s">
         <v>11</v>
@@ -2023,7 +2025,7 @@
         <v>16</v>
       </c>
       <c r="E61" t="n">
-        <v>-3.89</v>
+        <v>-3.9</v>
       </c>
       <c r="F61" t="s">
         <v>11</v>
@@ -2069,7 +2071,7 @@
         <v>9</v>
       </c>
       <c r="E63" t="n">
-        <v>2.79</v>
+        <v>2.8</v>
       </c>
       <c r="F63" t="s">
         <v>11</v>
@@ -2092,7 +2094,7 @@
         <v>13</v>
       </c>
       <c r="E64" t="n">
-        <v>0.62</v>
+        <v>0.59</v>
       </c>
       <c r="F64" t="s">
         <v>11</v>
@@ -2115,7 +2117,7 @@
         <v>14</v>
       </c>
       <c r="E65" t="n">
-        <v>-14.37</v>
+        <v>-14.36</v>
       </c>
       <c r="F65" t="s">
         <v>11</v>
@@ -2161,7 +2163,7 @@
         <v>16</v>
       </c>
       <c r="E67" t="n">
-        <v>4.92</v>
+        <v>4.93</v>
       </c>
       <c r="F67" t="s">
         <v>12</v>
@@ -2230,7 +2232,7 @@
         <v>13</v>
       </c>
       <c r="E70" t="n">
-        <v>5.29</v>
+        <v>5.23</v>
       </c>
       <c r="F70" t="s">
         <v>12</v>
@@ -2253,7 +2255,7 @@
         <v>14</v>
       </c>
       <c r="E71" t="n">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="F71" t="s">
         <v>11</v>
@@ -2276,7 +2278,7 @@
         <v>15</v>
       </c>
       <c r="E72" t="n">
-        <v>2.31</v>
+        <v>2.32</v>
       </c>
       <c r="F72" t="s">
         <v>11</v>
@@ -2299,7 +2301,7 @@
         <v>16</v>
       </c>
       <c r="E73" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="F73" t="s">
         <v>11</v>
@@ -2322,7 +2324,7 @@
         <v>10</v>
       </c>
       <c r="E74" t="n">
-        <v>-1.81</v>
+        <v>-1.82</v>
       </c>
       <c r="F74" t="s">
         <v>11</v>
@@ -2345,7 +2347,7 @@
         <v>9</v>
       </c>
       <c r="E75" t="n">
-        <v>5.12</v>
+        <v>5.11</v>
       </c>
       <c r="F75" t="s">
         <v>12</v>
@@ -2368,7 +2370,7 @@
         <v>13</v>
       </c>
       <c r="E76" t="n">
-        <v>3.48</v>
+        <v>3.52</v>
       </c>
       <c r="F76" t="s">
         <v>11</v>
@@ -2414,7 +2416,7 @@
         <v>15</v>
       </c>
       <c r="E78" t="n">
-        <v>-1.24</v>
+        <v>-1.25</v>
       </c>
       <c r="F78" t="s">
         <v>11</v>
@@ -2437,7 +2439,7 @@
         <v>16</v>
       </c>
       <c r="E79" t="n">
-        <v>4.02</v>
+        <v>4.01</v>
       </c>
       <c r="F79" t="s">
         <v>11</v>
@@ -2460,7 +2462,7 @@
         <v>10</v>
       </c>
       <c r="E80" t="n">
-        <v>-4.77</v>
+        <v>-4.76</v>
       </c>
       <c r="F80" t="s">
         <v>11</v>
@@ -2483,7 +2485,7 @@
         <v>9</v>
       </c>
       <c r="E81" t="n">
-        <v>3.23</v>
+        <v>3.22</v>
       </c>
       <c r="F81" t="s">
         <v>11</v>
@@ -2506,7 +2508,7 @@
         <v>13</v>
       </c>
       <c r="E82" t="n">
-        <v>3.82</v>
+        <v>3.88</v>
       </c>
       <c r="F82" t="s">
         <v>12</v>
@@ -2529,7 +2531,7 @@
         <v>14</v>
       </c>
       <c r="E83" t="n">
-        <v>-7.83</v>
+        <v>-7.86</v>
       </c>
       <c r="F83" t="s">
         <v>11</v>
@@ -2552,7 +2554,7 @@
         <v>15</v>
       </c>
       <c r="E84" t="n">
-        <v>2.53</v>
+        <v>2.52</v>
       </c>
       <c r="F84" t="s">
         <v>11</v>
@@ -2575,7 +2577,7 @@
         <v>16</v>
       </c>
       <c r="E85" t="n">
-        <v>3.01</v>
+        <v>3</v>
       </c>
       <c r="F85" t="s">
         <v>11</v>
@@ -2782,7 +2784,7 @@
         <v>13</v>
       </c>
       <c r="E94" t="n">
-        <v>0.48</v>
+        <v>0.47</v>
       </c>
       <c r="F94" t="s">
         <v>11</v>
@@ -2828,7 +2830,7 @@
         <v>15</v>
       </c>
       <c r="E96" t="n">
-        <v>-7.63</v>
+        <v>-7.62</v>
       </c>
       <c r="F96" t="s">
         <v>11</v>
@@ -2874,7 +2876,7 @@
         <v>10</v>
       </c>
       <c r="E98" t="n">
-        <v>-0.83</v>
+        <v>-0.8</v>
       </c>
       <c r="F98" t="s">
         <v>11</v>
@@ -2897,7 +2899,7 @@
         <v>9</v>
       </c>
       <c r="E99" t="n">
-        <v>0.37</v>
+        <v>0.43</v>
       </c>
       <c r="F99" t="s">
         <v>11</v>
@@ -2920,7 +2922,7 @@
         <v>13</v>
       </c>
       <c r="E100" t="n">
-        <v>1.7</v>
+        <v>1.66</v>
       </c>
       <c r="F100" t="s">
         <v>11</v>
@@ -2943,7 +2945,7 @@
         <v>14</v>
       </c>
       <c r="E101" t="n">
-        <v>-6.9</v>
+        <v>-6.95</v>
       </c>
       <c r="F101" t="s">
         <v>11</v>
@@ -2966,7 +2968,7 @@
         <v>15</v>
       </c>
       <c r="E102" t="n">
-        <v>3.66</v>
+        <v>3.63</v>
       </c>
       <c r="F102" t="s">
         <v>12</v>
@@ -2989,7 +2991,7 @@
         <v>16</v>
       </c>
       <c r="E103" t="n">
-        <v>1.99</v>
+        <v>2.03</v>
       </c>
       <c r="F103" t="s">
         <v>11</v>
@@ -3035,7 +3037,7 @@
         <v>9</v>
       </c>
       <c r="E105" t="n">
-        <v>2.37</v>
+        <v>2.36</v>
       </c>
       <c r="F105" t="s">
         <v>11</v>
@@ -3058,7 +3060,7 @@
         <v>13</v>
       </c>
       <c r="E106" t="n">
-        <v>3.25</v>
+        <v>3.31</v>
       </c>
       <c r="F106" t="s">
         <v>11</v>
@@ -3081,7 +3083,7 @@
         <v>14</v>
       </c>
       <c r="E107" t="n">
-        <v>0.39</v>
+        <v>0.37</v>
       </c>
       <c r="F107" t="s">
         <v>11</v>
@@ -3104,7 +3106,7 @@
         <v>15</v>
       </c>
       <c r="E108" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="F108" t="s">
         <v>11</v>
@@ -3127,7 +3129,7 @@
         <v>16</v>
       </c>
       <c r="E109" t="n">
-        <v>7.24</v>
+        <v>7.23</v>
       </c>
       <c r="F109" t="s">
         <v>12</v>
@@ -3150,7 +3152,7 @@
         <v>10</v>
       </c>
       <c r="E110" t="n">
-        <v>-1.8</v>
+        <v>-1.79</v>
       </c>
       <c r="F110" t="s">
         <v>11</v>
@@ -3173,7 +3175,7 @@
         <v>9</v>
       </c>
       <c r="E111" t="n">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="F111" t="s">
         <v>11</v>
@@ -3196,7 +3198,7 @@
         <v>13</v>
       </c>
       <c r="E112" t="n">
-        <v>2.29</v>
+        <v>2.21</v>
       </c>
       <c r="F112" t="s">
         <v>11</v>
@@ -3219,7 +3221,7 @@
         <v>14</v>
       </c>
       <c r="E113" t="n">
-        <v>-6.72</v>
+        <v>-6.7</v>
       </c>
       <c r="F113" t="s">
         <v>11</v>
@@ -3242,7 +3244,7 @@
         <v>15</v>
       </c>
       <c r="E114" t="n">
-        <v>0.5</v>
+        <v>0.52</v>
       </c>
       <c r="F114" t="s">
         <v>11</v>
@@ -3265,7 +3267,7 @@
         <v>16</v>
       </c>
       <c r="E115" t="n">
-        <v>4.99</v>
+        <v>5</v>
       </c>
       <c r="F115" t="s">
         <v>12</v>
@@ -3288,7 +3290,7 @@
         <v>10</v>
       </c>
       <c r="E116" t="n">
-        <v>-2.61</v>
+        <v>-2.64</v>
       </c>
       <c r="F116" t="s">
         <v>11</v>
@@ -3311,7 +3313,7 @@
         <v>9</v>
       </c>
       <c r="E117" t="n">
-        <v>2.76</v>
+        <v>2.73</v>
       </c>
       <c r="F117" t="s">
         <v>11</v>
@@ -3334,7 +3336,7 @@
         <v>13</v>
       </c>
       <c r="E118" t="n">
-        <v>2</v>
+        <v>2.15</v>
       </c>
       <c r="F118" t="s">
         <v>11</v>
@@ -3357,7 +3359,7 @@
         <v>14</v>
       </c>
       <c r="E119" t="n">
-        <v>-12.33</v>
+        <v>-12.38</v>
       </c>
       <c r="F119" t="s">
         <v>11</v>
@@ -3380,7 +3382,7 @@
         <v>15</v>
       </c>
       <c r="E120" t="n">
-        <v>2.29</v>
+        <v>2.27</v>
       </c>
       <c r="F120" t="s">
         <v>11</v>
@@ -3403,7 +3405,7 @@
         <v>16</v>
       </c>
       <c r="E121" t="n">
-        <v>7.9</v>
+        <v>7.87</v>
       </c>
       <c r="F121" t="s">
         <v>12</v>
@@ -3426,7 +3428,7 @@
         <v>10</v>
       </c>
       <c r="E122" t="n">
-        <v>-10.6</v>
+        <v>-10.61</v>
       </c>
       <c r="F122" t="s">
         <v>11</v>
@@ -3449,7 +3451,7 @@
         <v>9</v>
       </c>
       <c r="E123" t="n">
-        <v>6.97</v>
+        <v>6.89</v>
       </c>
       <c r="F123" t="s">
         <v>12</v>
@@ -3472,7 +3474,7 @@
         <v>13</v>
       </c>
       <c r="E124" t="n">
-        <v>4.34</v>
+        <v>4.56</v>
       </c>
       <c r="F124" t="s">
         <v>11</v>
@@ -3495,7 +3497,7 @@
         <v>14</v>
       </c>
       <c r="E125" t="n">
-        <v>-4.46</v>
+        <v>-4.52</v>
       </c>
       <c r="F125" t="s">
         <v>11</v>
@@ -3518,7 +3520,7 @@
         <v>15</v>
       </c>
       <c r="E126" t="n">
-        <v>0.67</v>
+        <v>0.66</v>
       </c>
       <c r="F126" t="s">
         <v>11</v>
@@ -3541,7 +3543,7 @@
         <v>16</v>
       </c>
       <c r="E127" t="n">
-        <v>3.08</v>
+        <v>3.02</v>
       </c>
       <c r="F127" t="s">
         <v>11</v>
@@ -3564,7 +3566,7 @@
         <v>10</v>
       </c>
       <c r="E128" t="n">
-        <v>-12.85</v>
+        <v>-12.82</v>
       </c>
       <c r="F128" t="s">
         <v>11</v>
@@ -3587,7 +3589,7 @@
         <v>9</v>
       </c>
       <c r="E129" t="n">
-        <v>-3.76</v>
+        <v>-3.77</v>
       </c>
       <c r="F129" t="s">
         <v>11</v>
@@ -3610,7 +3612,7 @@
         <v>13</v>
       </c>
       <c r="E130" t="n">
-        <v>4.21</v>
+        <v>4.24</v>
       </c>
       <c r="F130" t="s">
         <v>11</v>
@@ -3633,7 +3635,7 @@
         <v>14</v>
       </c>
       <c r="E131" t="n">
-        <v>10.81</v>
+        <v>10.78</v>
       </c>
       <c r="F131" t="s">
         <v>12</v>
@@ -3656,7 +3658,7 @@
         <v>15</v>
       </c>
       <c r="E132" t="n">
-        <v>5.06</v>
+        <v>5.05</v>
       </c>
       <c r="F132" t="s">
         <v>11</v>
@@ -3679,7 +3681,7 @@
         <v>16</v>
       </c>
       <c r="E133" t="n">
-        <v>-3.47</v>
+        <v>-3.48</v>
       </c>
       <c r="F133" t="s">
         <v>11</v>
@@ -3702,7 +3704,7 @@
         <v>10</v>
       </c>
       <c r="E134" t="n">
-        <v>-13.37</v>
+        <v>-13.36</v>
       </c>
       <c r="F134" t="s">
         <v>11</v>
@@ -3748,7 +3750,7 @@
         <v>13</v>
       </c>
       <c r="E136" t="n">
-        <v>3.05</v>
+        <v>3.03</v>
       </c>
       <c r="F136" t="s">
         <v>11</v>
@@ -3817,7 +3819,7 @@
         <v>16</v>
       </c>
       <c r="E139" t="n">
-        <v>4.27</v>
+        <v>4.28</v>
       </c>
       <c r="F139" t="s">
         <v>11</v>
@@ -3840,7 +3842,7 @@
         <v>10</v>
       </c>
       <c r="E140" t="n">
-        <v>-0.27</v>
+        <v>-0.25</v>
       </c>
       <c r="F140" t="s">
         <v>11</v>
@@ -3863,7 +3865,7 @@
         <v>9</v>
       </c>
       <c r="E141" t="n">
-        <v>-3.9</v>
+        <v>-3.88</v>
       </c>
       <c r="F141" t="s">
         <v>11</v>
@@ -3886,7 +3888,7 @@
         <v>13</v>
       </c>
       <c r="E142" t="n">
-        <v>2.19</v>
+        <v>2.12</v>
       </c>
       <c r="F142" t="s">
         <v>11</v>
@@ -3909,7 +3911,7 @@
         <v>14</v>
       </c>
       <c r="E143" t="n">
-        <v>-7.23</v>
+        <v>-7.22</v>
       </c>
       <c r="F143" t="s">
         <v>11</v>
@@ -3932,7 +3934,7 @@
         <v>15</v>
       </c>
       <c r="E144" t="n">
-        <v>-0.6</v>
+        <v>-0.58</v>
       </c>
       <c r="F144" t="s">
         <v>11</v>
@@ -3955,7 +3957,7 @@
         <v>16</v>
       </c>
       <c r="E145" t="n">
-        <v>9.8</v>
+        <v>9.82</v>
       </c>
       <c r="F145" t="s">
         <v>12</v>

--- a/Outcome/Publish/figure_data/fig4.xlsx
+++ b/Outcome/Publish/figure_data/fig4.xlsx
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="87">
   <si>
     <t xml:space="preserve">Group</t>
   </si>
@@ -96,7 +96,7 @@
     <t xml:space="preserve">Genital herpes</t>
   </si>
   <si>
-    <t xml:space="preserve">CA</t>
+    <t xml:space="preserve">CA (HPV)</t>
   </si>
   <si>
     <t xml:space="preserve">HBV</t>
@@ -202,6 +202,9 @@
   </si>
   <si>
     <t xml:space="preserve">Decrease</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CA</t>
   </si>
   <si>
     <t xml:space="preserve">StartDate</t>
@@ -668,7 +671,7 @@
         <v>10</v>
       </c>
       <c r="E2" t="n">
-        <v>2.79</v>
+        <v>2.82</v>
       </c>
       <c r="F2" t="s">
         <v>11</v>
@@ -691,7 +694,7 @@
         <v>9</v>
       </c>
       <c r="E3" t="n">
-        <v>7.31</v>
+        <v>7.36</v>
       </c>
       <c r="F3" t="s">
         <v>12</v>
@@ -714,7 +717,7 @@
         <v>13</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.7</v>
+        <v>-0.85</v>
       </c>
       <c r="F4" t="s">
         <v>11</v>
@@ -737,7 +740,7 @@
         <v>14</v>
       </c>
       <c r="E5" t="n">
-        <v>-11.88</v>
+        <v>-11.86</v>
       </c>
       <c r="F5" t="s">
         <v>11</v>
@@ -760,7 +763,7 @@
         <v>15</v>
       </c>
       <c r="E6" t="n">
-        <v>-2.94</v>
+        <v>-2.91</v>
       </c>
       <c r="F6" t="s">
         <v>11</v>
@@ -783,7 +786,7 @@
         <v>16</v>
       </c>
       <c r="E7" t="n">
-        <v>5.41</v>
+        <v>5.44</v>
       </c>
       <c r="F7" t="s">
         <v>11</v>
@@ -806,7 +809,7 @@
         <v>10</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.73</v>
+        <v>-0.62</v>
       </c>
       <c r="F8" t="s">
         <v>11</v>
@@ -829,7 +832,7 @@
         <v>9</v>
       </c>
       <c r="E9" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="F9" t="s">
         <v>11</v>
@@ -852,7 +855,7 @@
         <v>13</v>
       </c>
       <c r="E10" t="n">
-        <v>2.08</v>
+        <v>1.97</v>
       </c>
       <c r="F10" t="s">
         <v>12</v>
@@ -875,7 +878,7 @@
         <v>14</v>
       </c>
       <c r="E11" t="n">
-        <v>0.69</v>
+        <v>0.62</v>
       </c>
       <c r="F11" t="s">
         <v>11</v>
@@ -898,7 +901,7 @@
         <v>15</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.75</v>
+        <v>-0.83</v>
       </c>
       <c r="F12" t="s">
         <v>11</v>
@@ -921,7 +924,7 @@
         <v>16</v>
       </c>
       <c r="E13" t="n">
-        <v>-2.48</v>
+        <v>-2.32</v>
       </c>
       <c r="F13" t="s">
         <v>11</v>
@@ -944,7 +947,7 @@
         <v>10</v>
       </c>
       <c r="E14" t="n">
-        <v>-3.99</v>
+        <v>-4.03</v>
       </c>
       <c r="F14" t="s">
         <v>11</v>
@@ -967,7 +970,7 @@
         <v>9</v>
       </c>
       <c r="E15" t="n">
-        <v>3.1</v>
+        <v>3.06</v>
       </c>
       <c r="F15" t="s">
         <v>11</v>
@@ -990,7 +993,7 @@
         <v>13</v>
       </c>
       <c r="E16" t="n">
-        <v>3.91</v>
+        <v>4.04</v>
       </c>
       <c r="F16" t="s">
         <v>12</v>
@@ -1013,7 +1016,7 @@
         <v>14</v>
       </c>
       <c r="E17" t="n">
-        <v>-4.78</v>
+        <v>-4.79</v>
       </c>
       <c r="F17" t="s">
         <v>11</v>
@@ -1059,7 +1062,7 @@
         <v>16</v>
       </c>
       <c r="E19" t="n">
-        <v>1.77</v>
+        <v>1.74</v>
       </c>
       <c r="F19" t="s">
         <v>11</v>
@@ -1082,7 +1085,7 @@
         <v>10</v>
       </c>
       <c r="E20" t="n">
-        <v>9.17</v>
+        <v>9.16</v>
       </c>
       <c r="F20" t="s">
         <v>12</v>
@@ -1105,7 +1108,7 @@
         <v>9</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.56</v>
+        <v>-2.58</v>
       </c>
       <c r="F21" t="s">
         <v>11</v>
@@ -1128,7 +1131,7 @@
         <v>13</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.13</v>
+        <v>-1.08</v>
       </c>
       <c r="F22" t="s">
         <v>11</v>
@@ -1151,7 +1154,7 @@
         <v>14</v>
       </c>
       <c r="E23" t="n">
-        <v>2.94</v>
+        <v>2.93</v>
       </c>
       <c r="F23" t="s">
         <v>11</v>
@@ -1197,7 +1200,7 @@
         <v>16</v>
       </c>
       <c r="E25" t="n">
-        <v>3.68</v>
+        <v>3.67</v>
       </c>
       <c r="F25" t="s">
         <v>11</v>
@@ -1220,7 +1223,7 @@
         <v>10</v>
       </c>
       <c r="E26" t="n">
-        <v>2.31</v>
+        <v>2.4</v>
       </c>
       <c r="F26" t="s">
         <v>11</v>
@@ -1243,7 +1246,7 @@
         <v>9</v>
       </c>
       <c r="E27" t="n">
-        <v>2.91</v>
+        <v>3.01</v>
       </c>
       <c r="F27" t="s">
         <v>11</v>
@@ -1266,7 +1269,7 @@
         <v>13</v>
       </c>
       <c r="E28" t="n">
-        <v>4.84</v>
+        <v>4.43</v>
       </c>
       <c r="F28" t="s">
         <v>12</v>
@@ -1289,7 +1292,7 @@
         <v>14</v>
       </c>
       <c r="E29" t="n">
-        <v>-11.78</v>
+        <v>-11.74</v>
       </c>
       <c r="F29" t="s">
         <v>11</v>
@@ -1312,7 +1315,7 @@
         <v>15</v>
       </c>
       <c r="E30" t="n">
-        <v>0.1</v>
+        <v>0.18</v>
       </c>
       <c r="F30" t="s">
         <v>11</v>
@@ -1335,7 +1338,7 @@
         <v>16</v>
       </c>
       <c r="E31" t="n">
-        <v>1.62</v>
+        <v>1.72</v>
       </c>
       <c r="F31" t="s">
         <v>11</v>
@@ -1358,7 +1361,7 @@
         <v>10</v>
       </c>
       <c r="E32" t="n">
-        <v>8.41</v>
+        <v>8.38</v>
       </c>
       <c r="F32" t="s">
         <v>12</v>
@@ -1381,7 +1384,7 @@
         <v>9</v>
       </c>
       <c r="E33" t="n">
-        <v>1.58</v>
+        <v>1.52</v>
       </c>
       <c r="F33" t="s">
         <v>11</v>
@@ -1404,7 +1407,7 @@
         <v>13</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.69</v>
+        <v>-0.34</v>
       </c>
       <c r="F34" t="s">
         <v>11</v>
@@ -1427,7 +1430,7 @@
         <v>14</v>
       </c>
       <c r="E35" t="n">
-        <v>-13.89</v>
+        <v>-14</v>
       </c>
       <c r="F35" t="s">
         <v>11</v>
@@ -1450,7 +1453,7 @@
         <v>15</v>
       </c>
       <c r="E36" t="n">
-        <v>4.22</v>
+        <v>4.12</v>
       </c>
       <c r="F36" t="s">
         <v>11</v>
@@ -1473,7 +1476,7 @@
         <v>16</v>
       </c>
       <c r="E37" t="n">
-        <v>0.37</v>
+        <v>0.32</v>
       </c>
       <c r="F37" t="s">
         <v>11</v>
@@ -1496,7 +1499,7 @@
         <v>10</v>
       </c>
       <c r="E38" t="n">
-        <v>-6.07</v>
+        <v>-6.06</v>
       </c>
       <c r="F38" t="s">
         <v>11</v>
@@ -1519,7 +1522,7 @@
         <v>9</v>
       </c>
       <c r="E39" t="n">
-        <v>3.79</v>
+        <v>3.77</v>
       </c>
       <c r="F39" t="s">
         <v>11</v>
@@ -1542,7 +1545,7 @@
         <v>13</v>
       </c>
       <c r="E40" t="n">
-        <v>4.13</v>
+        <v>4.23</v>
       </c>
       <c r="F40" t="s">
         <v>11</v>
@@ -1565,7 +1568,7 @@
         <v>14</v>
       </c>
       <c r="E41" t="n">
-        <v>-0.01</v>
+        <v>-0.06</v>
       </c>
       <c r="F41" t="s">
         <v>11</v>
@@ -1611,7 +1614,7 @@
         <v>16</v>
       </c>
       <c r="E43" t="n">
-        <v>6.96</v>
+        <v>6.92</v>
       </c>
       <c r="F43" t="s">
         <v>12</v>
@@ -1657,7 +1660,7 @@
         <v>9</v>
       </c>
       <c r="E45" t="n">
-        <v>-0.95</v>
+        <v>-0.94</v>
       </c>
       <c r="F45" t="s">
         <v>11</v>
@@ -1680,7 +1683,7 @@
         <v>13</v>
       </c>
       <c r="E46" t="n">
-        <v>9.07</v>
+        <v>9.04</v>
       </c>
       <c r="F46" t="s">
         <v>12</v>
@@ -1703,7 +1706,7 @@
         <v>14</v>
       </c>
       <c r="E47" t="n">
-        <v>-5.91</v>
+        <v>-5.89</v>
       </c>
       <c r="F47" t="s">
         <v>11</v>
@@ -1726,7 +1729,7 @@
         <v>15</v>
       </c>
       <c r="E48" t="n">
-        <v>-0.18</v>
+        <v>-0.17</v>
       </c>
       <c r="F48" t="s">
         <v>11</v>
@@ -1749,7 +1752,7 @@
         <v>16</v>
       </c>
       <c r="E49" t="n">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="F49" t="s">
         <v>11</v>
@@ -1818,7 +1821,7 @@
         <v>13</v>
       </c>
       <c r="E52" t="n">
-        <v>4.84</v>
+        <v>4.83</v>
       </c>
       <c r="F52" t="s">
         <v>12</v>
@@ -1841,7 +1844,7 @@
         <v>14</v>
       </c>
       <c r="E53" t="n">
-        <v>-1.12</v>
+        <v>-1.11</v>
       </c>
       <c r="F53" t="s">
         <v>11</v>
@@ -1864,7 +1867,7 @@
         <v>15</v>
       </c>
       <c r="E54" t="n">
-        <v>2.03</v>
+        <v>2.04</v>
       </c>
       <c r="F54" t="s">
         <v>11</v>
@@ -1910,7 +1913,7 @@
         <v>10</v>
       </c>
       <c r="E56" t="n">
-        <v>6.94</v>
+        <v>6.93</v>
       </c>
       <c r="F56" t="s">
         <v>12</v>
@@ -1933,7 +1936,7 @@
         <v>9</v>
       </c>
       <c r="E57" t="n">
-        <v>-5.7</v>
+        <v>-5.69</v>
       </c>
       <c r="F57" t="s">
         <v>11</v>
@@ -1956,7 +1959,7 @@
         <v>13</v>
       </c>
       <c r="E58" t="n">
-        <v>0.86</v>
+        <v>0.85</v>
       </c>
       <c r="F58" t="s">
         <v>11</v>
@@ -1979,7 +1982,7 @@
         <v>14</v>
       </c>
       <c r="E59" t="n">
-        <v>-2.13</v>
+        <v>-2.12</v>
       </c>
       <c r="F59" t="s">
         <v>11</v>
@@ -2002,7 +2005,7 @@
         <v>15</v>
       </c>
       <c r="E60" t="n">
-        <v>3.94</v>
+        <v>3.92</v>
       </c>
       <c r="F60" t="s">
         <v>11</v>
@@ -2025,7 +2028,7 @@
         <v>16</v>
       </c>
       <c r="E61" t="n">
-        <v>-3.9</v>
+        <v>-3.88</v>
       </c>
       <c r="F61" t="s">
         <v>11</v>
@@ -2048,7 +2051,7 @@
         <v>10</v>
       </c>
       <c r="E62" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="F62" t="s">
         <v>11</v>
@@ -2071,7 +2074,7 @@
         <v>9</v>
       </c>
       <c r="E63" t="n">
-        <v>2.8</v>
+        <v>2.77</v>
       </c>
       <c r="F63" t="s">
         <v>11</v>
@@ -2094,7 +2097,7 @@
         <v>13</v>
       </c>
       <c r="E64" t="n">
-        <v>0.59</v>
+        <v>0.7</v>
       </c>
       <c r="F64" t="s">
         <v>11</v>
@@ -2117,7 +2120,7 @@
         <v>14</v>
       </c>
       <c r="E65" t="n">
-        <v>-14.36</v>
+        <v>-14.38</v>
       </c>
       <c r="F65" t="s">
         <v>11</v>
@@ -2140,7 +2143,7 @@
         <v>15</v>
       </c>
       <c r="E66" t="n">
-        <v>3.96</v>
+        <v>3.94</v>
       </c>
       <c r="F66" t="s">
         <v>11</v>
@@ -2163,7 +2166,7 @@
         <v>16</v>
       </c>
       <c r="E67" t="n">
-        <v>4.93</v>
+        <v>4.91</v>
       </c>
       <c r="F67" t="s">
         <v>12</v>
@@ -2186,7 +2189,7 @@
         <v>10</v>
       </c>
       <c r="E68" t="n">
-        <v>-8.44</v>
+        <v>-8.43</v>
       </c>
       <c r="F68" t="s">
         <v>11</v>
@@ -2232,7 +2235,7 @@
         <v>13</v>
       </c>
       <c r="E70" t="n">
-        <v>5.23</v>
+        <v>5.24</v>
       </c>
       <c r="F70" t="s">
         <v>12</v>
@@ -2278,7 +2281,7 @@
         <v>15</v>
       </c>
       <c r="E72" t="n">
-        <v>2.32</v>
+        <v>2.31</v>
       </c>
       <c r="F72" t="s">
         <v>11</v>
@@ -2347,7 +2350,7 @@
         <v>9</v>
       </c>
       <c r="E75" t="n">
-        <v>5.11</v>
+        <v>5.12</v>
       </c>
       <c r="F75" t="s">
         <v>12</v>
@@ -2370,7 +2373,7 @@
         <v>13</v>
       </c>
       <c r="E76" t="n">
-        <v>3.52</v>
+        <v>3.49</v>
       </c>
       <c r="F76" t="s">
         <v>11</v>
@@ -2393,7 +2396,7 @@
         <v>14</v>
       </c>
       <c r="E77" t="n">
-        <v>-9.57</v>
+        <v>-9.56</v>
       </c>
       <c r="F77" t="s">
         <v>11</v>
@@ -2462,7 +2465,7 @@
         <v>10</v>
       </c>
       <c r="E80" t="n">
-        <v>-4.76</v>
+        <v>-4.75</v>
       </c>
       <c r="F80" t="s">
         <v>11</v>
@@ -2485,7 +2488,7 @@
         <v>9</v>
       </c>
       <c r="E81" t="n">
-        <v>3.22</v>
+        <v>3.25</v>
       </c>
       <c r="F81" t="s">
         <v>11</v>
@@ -2508,7 +2511,7 @@
         <v>13</v>
       </c>
       <c r="E82" t="n">
-        <v>3.88</v>
+        <v>3.73</v>
       </c>
       <c r="F82" t="s">
         <v>12</v>
@@ -2531,7 +2534,7 @@
         <v>14</v>
       </c>
       <c r="E83" t="n">
-        <v>-7.86</v>
+        <v>-7.81</v>
       </c>
       <c r="F83" t="s">
         <v>11</v>
@@ -2554,7 +2557,7 @@
         <v>15</v>
       </c>
       <c r="E84" t="n">
-        <v>2.52</v>
+        <v>2.55</v>
       </c>
       <c r="F84" t="s">
         <v>11</v>
@@ -2577,7 +2580,7 @@
         <v>16</v>
       </c>
       <c r="E85" t="n">
-        <v>3</v>
+        <v>3.03</v>
       </c>
       <c r="F85" t="s">
         <v>11</v>
@@ -2646,7 +2649,7 @@
         <v>13</v>
       </c>
       <c r="E88" t="n">
-        <v>3.26</v>
+        <v>3.27</v>
       </c>
       <c r="F88" t="s">
         <v>12</v>
@@ -2669,7 +2672,7 @@
         <v>14</v>
       </c>
       <c r="E89" t="n">
-        <v>-8.25</v>
+        <v>-8.26</v>
       </c>
       <c r="F89" t="s">
         <v>11</v>
@@ -2876,7 +2879,7 @@
         <v>10</v>
       </c>
       <c r="E98" t="n">
-        <v>-0.8</v>
+        <v>-0.79</v>
       </c>
       <c r="F98" t="s">
         <v>11</v>
@@ -2899,7 +2902,7 @@
         <v>9</v>
       </c>
       <c r="E99" t="n">
-        <v>0.43</v>
+        <v>0.42</v>
       </c>
       <c r="F99" t="s">
         <v>11</v>
@@ -2922,7 +2925,7 @@
         <v>13</v>
       </c>
       <c r="E100" t="n">
-        <v>1.66</v>
+        <v>1.57</v>
       </c>
       <c r="F100" t="s">
         <v>11</v>
@@ -2945,7 +2948,7 @@
         <v>14</v>
       </c>
       <c r="E101" t="n">
-        <v>-6.95</v>
+        <v>-6.91</v>
       </c>
       <c r="F101" t="s">
         <v>11</v>
@@ -2968,7 +2971,7 @@
         <v>15</v>
       </c>
       <c r="E102" t="n">
-        <v>3.63</v>
+        <v>3.67</v>
       </c>
       <c r="F102" t="s">
         <v>12</v>
@@ -2991,7 +2994,7 @@
         <v>16</v>
       </c>
       <c r="E103" t="n">
-        <v>2.03</v>
+        <v>2.04</v>
       </c>
       <c r="F103" t="s">
         <v>11</v>
@@ -3014,7 +3017,7 @@
         <v>10</v>
       </c>
       <c r="E104" t="n">
-        <v>-14.45</v>
+        <v>-14.48</v>
       </c>
       <c r="F104" t="s">
         <v>11</v>
@@ -3037,7 +3040,7 @@
         <v>9</v>
       </c>
       <c r="E105" t="n">
-        <v>2.36</v>
+        <v>2.32</v>
       </c>
       <c r="F105" t="s">
         <v>11</v>
@@ -3060,7 +3063,7 @@
         <v>13</v>
       </c>
       <c r="E106" t="n">
-        <v>3.31</v>
+        <v>3.48</v>
       </c>
       <c r="F106" t="s">
         <v>11</v>
@@ -3083,7 +3086,7 @@
         <v>14</v>
       </c>
       <c r="E107" t="n">
-        <v>0.37</v>
+        <v>0.33</v>
       </c>
       <c r="F107" t="s">
         <v>11</v>
@@ -3106,7 +3109,7 @@
         <v>15</v>
       </c>
       <c r="E108" t="n">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="F108" t="s">
         <v>11</v>
@@ -3129,7 +3132,7 @@
         <v>16</v>
       </c>
       <c r="E109" t="n">
-        <v>7.23</v>
+        <v>7.19</v>
       </c>
       <c r="F109" t="s">
         <v>12</v>
@@ -3152,7 +3155,7 @@
         <v>10</v>
       </c>
       <c r="E110" t="n">
-        <v>-1.79</v>
+        <v>-1.82</v>
       </c>
       <c r="F110" t="s">
         <v>11</v>
@@ -3175,7 +3178,7 @@
         <v>9</v>
       </c>
       <c r="E111" t="n">
-        <v>0.76</v>
+        <v>0.72</v>
       </c>
       <c r="F111" t="s">
         <v>11</v>
@@ -3198,7 +3201,7 @@
         <v>13</v>
       </c>
       <c r="E112" t="n">
-        <v>2.21</v>
+        <v>2.43</v>
       </c>
       <c r="F112" t="s">
         <v>11</v>
@@ -3221,7 +3224,7 @@
         <v>14</v>
       </c>
       <c r="E113" t="n">
-        <v>-6.7</v>
+        <v>-6.76</v>
       </c>
       <c r="F113" t="s">
         <v>11</v>
@@ -3244,7 +3247,7 @@
         <v>15</v>
       </c>
       <c r="E114" t="n">
-        <v>0.52</v>
+        <v>0.47</v>
       </c>
       <c r="F114" t="s">
         <v>11</v>
@@ -3267,7 +3270,7 @@
         <v>16</v>
       </c>
       <c r="E115" t="n">
-        <v>5</v>
+        <v>4.96</v>
       </c>
       <c r="F115" t="s">
         <v>12</v>
@@ -3313,7 +3316,7 @@
         <v>9</v>
       </c>
       <c r="E117" t="n">
-        <v>2.73</v>
+        <v>2.74</v>
       </c>
       <c r="F117" t="s">
         <v>11</v>
@@ -3336,7 +3339,7 @@
         <v>13</v>
       </c>
       <c r="E118" t="n">
-        <v>2.15</v>
+        <v>2.13</v>
       </c>
       <c r="F118" t="s">
         <v>11</v>
@@ -3359,7 +3362,7 @@
         <v>14</v>
       </c>
       <c r="E119" t="n">
-        <v>-12.38</v>
+        <v>-12.37</v>
       </c>
       <c r="F119" t="s">
         <v>11</v>
@@ -3428,7 +3431,7 @@
         <v>10</v>
       </c>
       <c r="E122" t="n">
-        <v>-10.61</v>
+        <v>-10.67</v>
       </c>
       <c r="F122" t="s">
         <v>11</v>
@@ -3451,7 +3454,7 @@
         <v>9</v>
       </c>
       <c r="E123" t="n">
-        <v>6.89</v>
+        <v>6.71</v>
       </c>
       <c r="F123" t="s">
         <v>12</v>
@@ -3474,7 +3477,7 @@
         <v>13</v>
       </c>
       <c r="E124" t="n">
-        <v>4.56</v>
+        <v>5.12</v>
       </c>
       <c r="F124" t="s">
         <v>11</v>
@@ -3497,7 +3500,7 @@
         <v>14</v>
       </c>
       <c r="E125" t="n">
-        <v>-4.52</v>
+        <v>-4.64</v>
       </c>
       <c r="F125" t="s">
         <v>11</v>
@@ -3520,7 +3523,7 @@
         <v>15</v>
       </c>
       <c r="E126" t="n">
-        <v>0.66</v>
+        <v>0.61</v>
       </c>
       <c r="F126" t="s">
         <v>11</v>
@@ -3543,7 +3546,7 @@
         <v>16</v>
       </c>
       <c r="E127" t="n">
-        <v>3.02</v>
+        <v>2.87</v>
       </c>
       <c r="F127" t="s">
         <v>11</v>
@@ -3566,7 +3569,7 @@
         <v>10</v>
       </c>
       <c r="E128" t="n">
-        <v>-12.82</v>
+        <v>-12.8</v>
       </c>
       <c r="F128" t="s">
         <v>11</v>
@@ -3589,7 +3592,7 @@
         <v>9</v>
       </c>
       <c r="E129" t="n">
-        <v>-3.77</v>
+        <v>-3.81</v>
       </c>
       <c r="F129" t="s">
         <v>11</v>
@@ -3612,7 +3615,7 @@
         <v>13</v>
       </c>
       <c r="E130" t="n">
-        <v>4.24</v>
+        <v>4.43</v>
       </c>
       <c r="F130" t="s">
         <v>11</v>
@@ -3635,7 +3638,7 @@
         <v>14</v>
       </c>
       <c r="E131" t="n">
-        <v>10.78</v>
+        <v>10.69</v>
       </c>
       <c r="F131" t="s">
         <v>12</v>
@@ -3658,7 +3661,7 @@
         <v>15</v>
       </c>
       <c r="E132" t="n">
-        <v>5.05</v>
+        <v>5</v>
       </c>
       <c r="F132" t="s">
         <v>11</v>
@@ -3681,7 +3684,7 @@
         <v>16</v>
       </c>
       <c r="E133" t="n">
-        <v>-3.48</v>
+        <v>-3.51</v>
       </c>
       <c r="F133" t="s">
         <v>11</v>
@@ -3704,7 +3707,7 @@
         <v>10</v>
       </c>
       <c r="E134" t="n">
-        <v>-13.36</v>
+        <v>-13.33</v>
       </c>
       <c r="F134" t="s">
         <v>11</v>
@@ -3727,7 +3730,7 @@
         <v>9</v>
       </c>
       <c r="E135" t="n">
-        <v>5.9</v>
+        <v>5.98</v>
       </c>
       <c r="F135" t="s">
         <v>11</v>
@@ -3750,7 +3753,7 @@
         <v>13</v>
       </c>
       <c r="E136" t="n">
-        <v>3.03</v>
+        <v>2.72</v>
       </c>
       <c r="F136" t="s">
         <v>11</v>
@@ -3773,7 +3776,7 @@
         <v>14</v>
       </c>
       <c r="E137" t="n">
-        <v>-6.39</v>
+        <v>-6.34</v>
       </c>
       <c r="F137" t="s">
         <v>11</v>
@@ -3796,7 +3799,7 @@
         <v>15</v>
       </c>
       <c r="E138" t="n">
-        <v>6.54</v>
+        <v>6.62</v>
       </c>
       <c r="F138" t="s">
         <v>12</v>
@@ -3819,7 +3822,7 @@
         <v>16</v>
       </c>
       <c r="E139" t="n">
-        <v>4.28</v>
+        <v>4.35</v>
       </c>
       <c r="F139" t="s">
         <v>11</v>
@@ -3842,7 +3845,7 @@
         <v>10</v>
       </c>
       <c r="E140" t="n">
-        <v>-0.25</v>
+        <v>-0.27</v>
       </c>
       <c r="F140" t="s">
         <v>11</v>
@@ -3865,7 +3868,7 @@
         <v>9</v>
       </c>
       <c r="E141" t="n">
-        <v>-3.88</v>
+        <v>-3.9</v>
       </c>
       <c r="F141" t="s">
         <v>11</v>
@@ -3888,7 +3891,7 @@
         <v>13</v>
       </c>
       <c r="E142" t="n">
-        <v>2.12</v>
+        <v>2.19</v>
       </c>
       <c r="F142" t="s">
         <v>11</v>
@@ -3911,7 +3914,7 @@
         <v>14</v>
       </c>
       <c r="E143" t="n">
-        <v>-7.22</v>
+        <v>-7.23</v>
       </c>
       <c r="F143" t="s">
         <v>11</v>
@@ -3934,7 +3937,7 @@
         <v>15</v>
       </c>
       <c r="E144" t="n">
-        <v>-0.58</v>
+        <v>-0.6</v>
       </c>
       <c r="F144" t="s">
         <v>11</v>
@@ -3957,7 +3960,7 @@
         <v>16</v>
       </c>
       <c r="E145" t="n">
-        <v>9.82</v>
+        <v>9.8</v>
       </c>
       <c r="F145" t="s">
         <v>12</v>
@@ -37381,7 +37384,7 @@
         <v>494.308233182257</v>
       </c>
       <c r="D2" t="s">
-        <v>19</v>
+        <v>55</v>
       </c>
       <c r="E2" t="n">
         <v>413.439949791173</v>
@@ -37416,7 +37419,7 @@
         <v>365.852031010568</v>
       </c>
       <c r="D3" t="s">
-        <v>19</v>
+        <v>55</v>
       </c>
       <c r="E3" t="n">
         <v>309.801048730283</v>
@@ -37451,7 +37454,7 @@
         <v>377.666758990437</v>
       </c>
       <c r="D4" t="s">
-        <v>19</v>
+        <v>55</v>
       </c>
       <c r="E4" t="n">
         <v>311.58212786386</v>
@@ -37486,7 +37489,7 @@
         <v>354.265166160463</v>
       </c>
       <c r="D5" t="s">
-        <v>19</v>
+        <v>55</v>
       </c>
       <c r="E5" t="n">
         <v>291.687258028857</v>
@@ -37521,7 +37524,7 @@
         <v>377.070576955142</v>
       </c>
       <c r="D6" t="s">
-        <v>19</v>
+        <v>55</v>
       </c>
       <c r="E6" t="n">
         <v>303.659473706482</v>
@@ -37556,7 +37559,7 @@
         <v>404.704638595481</v>
       </c>
       <c r="D7" t="s">
-        <v>19</v>
+        <v>55</v>
       </c>
       <c r="E7" t="n">
         <v>330.797590406623</v>
@@ -37591,7 +37594,7 @@
         <v>369.826157397408</v>
       </c>
       <c r="D8" t="s">
-        <v>19</v>
+        <v>55</v>
       </c>
       <c r="E8" t="n">
         <v>300.890352843286</v>
@@ -37626,7 +37629,7 @@
         <v>366.508448777447</v>
       </c>
       <c r="D9" t="s">
-        <v>19</v>
+        <v>55</v>
       </c>
       <c r="E9" t="n">
         <v>289.246804876259</v>
@@ -37661,7 +37664,7 @@
         <v>363.900010052863</v>
       </c>
       <c r="D10" t="s">
-        <v>19</v>
+        <v>55</v>
       </c>
       <c r="E10" t="n">
         <v>289.703616027498</v>
@@ -37696,7 +37699,7 @@
         <v>344.534831033978</v>
       </c>
       <c r="D11" t="s">
-        <v>19</v>
+        <v>55</v>
       </c>
       <c r="E11" t="n">
         <v>265.286113839099</v>
@@ -37731,7 +37734,7 @@
         <v>309.79048686187</v>
       </c>
       <c r="D12" t="s">
-        <v>19</v>
+        <v>55</v>
       </c>
       <c r="E12" t="n">
         <v>242.256866629261</v>
@@ -37766,7 +37769,7 @@
         <v>254.785042325196</v>
       </c>
       <c r="D13" t="s">
-        <v>19</v>
+        <v>55</v>
       </c>
       <c r="E13" t="n">
         <v>195.644796727382</v>
@@ -37801,7 +37804,7 @@
         <v>511.381865686907</v>
       </c>
       <c r="D14" t="s">
-        <v>19</v>
+        <v>55</v>
       </c>
       <c r="E14" t="n">
         <v>375.794902495792</v>
@@ -37836,7 +37839,7 @@
         <v>375.605668454839</v>
       </c>
       <c r="D15" t="s">
-        <v>19</v>
+        <v>55</v>
       </c>
       <c r="E15" t="n">
         <v>289.04055249987</v>
@@ -37871,7 +37874,7 @@
         <v>391.801571473241</v>
       </c>
       <c r="D16" t="s">
-        <v>19</v>
+        <v>55</v>
       </c>
       <c r="E16" t="n">
         <v>289.354702503198</v>
@@ -37906,7 +37909,7 @@
         <v>362.10332287284</v>
       </c>
       <c r="D17" t="s">
-        <v>19</v>
+        <v>55</v>
       </c>
       <c r="E17" t="n">
         <v>267.417984145623</v>
@@ -37941,7 +37944,7 @@
         <v>384.727756984891</v>
       </c>
       <c r="D18" t="s">
-        <v>19</v>
+        <v>55</v>
       </c>
       <c r="E18" t="n">
         <v>284.579926851619</v>
@@ -37976,7 +37979,7 @@
         <v>415.896976855163</v>
       </c>
       <c r="D19" t="s">
-        <v>19</v>
+        <v>55</v>
       </c>
       <c r="E19" t="n">
         <v>294.750747039384</v>
@@ -38011,7 +38014,7 @@
         <v>382.123805333673</v>
       </c>
       <c r="D20" t="s">
-        <v>19</v>
+        <v>55</v>
       </c>
       <c r="E20" t="n">
         <v>265.272886030123</v>
@@ -38046,7 +38049,7 @@
         <v>378.603956431466</v>
       </c>
       <c r="D21" t="s">
-        <v>19</v>
+        <v>55</v>
       </c>
       <c r="E21" t="n">
         <v>259.323846812261</v>
@@ -38081,7 +38084,7 @@
         <v>374.538549643369</v>
       </c>
       <c r="D22" t="s">
-        <v>19</v>
+        <v>55</v>
       </c>
       <c r="E22" t="n">
         <v>259.062638969318</v>
@@ -38116,7 +38119,7 @@
         <v>357.015660758243</v>
       </c>
       <c r="D23" t="s">
-        <v>19</v>
+        <v>55</v>
       </c>
       <c r="E23" t="n">
         <v>248.33036598006</v>
@@ -38151,7 +38154,7 @@
         <v>324.87973880864</v>
       </c>
       <c r="D24" t="s">
-        <v>19</v>
+        <v>55</v>
       </c>
       <c r="E24" t="n">
         <v>216.151747510379</v>
@@ -38186,7 +38189,7 @@
         <v>262.87831762474</v>
       </c>
       <c r="D25" t="s">
-        <v>19</v>
+        <v>55</v>
       </c>
       <c r="E25" t="n">
         <v>177.493968223263</v>
@@ -38221,7 +38224,7 @@
         <v>526.392480641543</v>
       </c>
       <c r="D26" t="s">
-        <v>19</v>
+        <v>55</v>
       </c>
       <c r="E26" t="n">
         <v>331.748666612938</v>
@@ -38256,7 +38259,7 @@
         <v>387.177738712109</v>
       </c>
       <c r="D27" t="s">
-        <v>19</v>
+        <v>55</v>
       </c>
       <c r="E27" t="n">
         <v>244.565649144479</v>
@@ -38291,7 +38294,7 @@
         <v>403.386586121864</v>
       </c>
       <c r="D28" t="s">
-        <v>19</v>
+        <v>55</v>
       </c>
       <c r="E28" t="n">
         <v>254.700930634148</v>
@@ -38326,7 +38329,7 @@
         <v>372.293588405335</v>
       </c>
       <c r="D29" t="s">
-        <v>19</v>
+        <v>55</v>
       </c>
       <c r="E29" t="n">
         <v>227.872255863823</v>
@@ -38361,7 +38364,7 @@
         <v>399.988728931133</v>
       </c>
       <c r="D30" t="s">
-        <v>19</v>
+        <v>55</v>
       </c>
       <c r="E30" t="n">
         <v>243.051009610468</v>
@@ -38396,7 +38399,7 @@
         <v>422.117812572791</v>
       </c>
       <c r="D31" t="s">
-        <v>19</v>
+        <v>55</v>
       </c>
       <c r="E31" t="n">
         <v>255.3353788045</v>
@@ -38431,7 +38434,7 @@
         <v>391.644600664945</v>
       </c>
       <c r="D32" t="s">
-        <v>19</v>
+        <v>55</v>
       </c>
       <c r="E32" t="n">
         <v>216.179208542611</v>
@@ -38466,7 +38469,7 @@
         <v>392.775504579769</v>
       </c>
       <c r="D33" t="s">
-        <v>19</v>
+        <v>55</v>
       </c>
       <c r="E33" t="n">
         <v>225.471542464049</v>
@@ -38501,7 +38504,7 @@
         <v>385.227353456753</v>
       </c>
       <c r="D34" t="s">
-        <v>19</v>
+        <v>55</v>
       </c>
       <c r="E34" t="n">
         <v>218.580241577468</v>
@@ -38536,7 +38539,7 @@
         <v>363.083453239583</v>
       </c>
       <c r="D35" t="s">
-        <v>19</v>
+        <v>55</v>
       </c>
       <c r="E35" t="n">
         <v>207.694760442988</v>
@@ -38571,7 +38574,7 @@
         <v>328.473124536934</v>
       </c>
       <c r="D36" t="s">
-        <v>19</v>
+        <v>55</v>
       </c>
       <c r="E36" t="n">
         <v>183.248489523866</v>
@@ -38606,7 +38609,7 @@
         <v>265.554603113142</v>
       </c>
       <c r="D37" t="s">
-        <v>19</v>
+        <v>55</v>
       </c>
       <c r="E37" t="n">
         <v>143.97244037828</v>
@@ -38641,7 +38644,7 @@
         <v>526.450454268275</v>
       </c>
       <c r="D38" t="s">
-        <v>19</v>
+        <v>55</v>
       </c>
       <c r="E38" t="n">
         <v>275.840458336603</v>
@@ -38676,7 +38679,7 @@
         <v>392.915039936062</v>
       </c>
       <c r="D39" t="s">
-        <v>19</v>
+        <v>55</v>
       </c>
       <c r="E39" t="n">
         <v>214.707637294358</v>
@@ -38711,7 +38714,7 @@
         <v>418.005238273735</v>
       </c>
       <c r="D40" t="s">
-        <v>19</v>
+        <v>55</v>
       </c>
       <c r="E40" t="n">
         <v>205.301023370712</v>
@@ -38746,7 +38749,7 @@
         <v>379.493431448992</v>
       </c>
       <c r="D41" t="s">
-        <v>19</v>
+        <v>55</v>
       </c>
       <c r="E41" t="n">
         <v>192.580218007593</v>
@@ -38781,7 +38784,7 @@
         <v>411.308287755981</v>
       </c>
       <c r="D42" t="s">
-        <v>19</v>
+        <v>55</v>
       </c>
       <c r="E42" t="n">
         <v>205.588980509442</v>
@@ -38816,7 +38819,7 @@
         <v>442.052239123703</v>
       </c>
       <c r="D43" t="s">
-        <v>19</v>
+        <v>55</v>
       </c>
       <c r="E43" t="n">
         <v>206.675202981696</v>
@@ -38851,7 +38854,7 @@
         <v>406.14589821074</v>
       </c>
       <c r="D44" t="s">
-        <v>19</v>
+        <v>55</v>
       </c>
       <c r="E44" t="n">
         <v>186.482799091191</v>
@@ -38886,7 +38889,7 @@
         <v>399.042863803449</v>
       </c>
       <c r="D45" t="s">
-        <v>19</v>
+        <v>55</v>
       </c>
       <c r="E45" t="n">
         <v>186.080661793845</v>
@@ -38921,7 +38924,7 @@
         <v>395.505016988318</v>
       </c>
       <c r="D46" t="s">
-        <v>19</v>
+        <v>55</v>
       </c>
       <c r="E46" t="n">
         <v>180.864573571089</v>
@@ -38956,7 +38959,7 @@
         <v>379.891388503893</v>
       </c>
       <c r="D47" t="s">
-        <v>19</v>
+        <v>55</v>
       </c>
       <c r="E47" t="n">
         <v>175.736844427534</v>
@@ -38991,7 +38994,7 @@
         <v>339.476799591901</v>
       </c>
       <c r="D48" t="s">
-        <v>19</v>
+        <v>55</v>
       </c>
       <c r="E48" t="n">
         <v>146.801782232348</v>
@@ -39026,7 +39029,7 @@
         <v>275.867451782119</v>
       </c>
       <c r="D49" t="s">
-        <v>19</v>
+        <v>55</v>
       </c>
       <c r="E49" t="n">
         <v>118.974396722822</v>
@@ -39061,7 +39064,7 @@
         <v>539.101785018432</v>
       </c>
       <c r="D50" t="s">
-        <v>19</v>
+        <v>55</v>
       </c>
       <c r="E50" t="n">
         <v>236.453914406581</v>
@@ -39096,7 +39099,7 @@
         <v>413.914928199779</v>
       </c>
       <c r="D51" t="s">
-        <v>19</v>
+        <v>55</v>
       </c>
       <c r="E51" t="n">
         <v>170.891233027753</v>
@@ -39131,7 +39134,7 @@
         <v>410.964278521811</v>
       </c>
       <c r="D52" t="s">
-        <v>19</v>
+        <v>55</v>
       </c>
       <c r="E52" t="n">
         <v>170.654818111986</v>
@@ -39166,7 +39169,7 @@
         <v>386.347815372926</v>
       </c>
       <c r="D53" t="s">
-        <v>19</v>
+        <v>55</v>
       </c>
       <c r="E53" t="n">
         <v>154.800057453604</v>
@@ -39201,7 +39204,7 @@
         <v>433.653922385135</v>
       </c>
       <c r="D54" t="s">
-        <v>19</v>
+        <v>55</v>
       </c>
       <c r="E54" t="n">
         <v>160.508511300147</v>
@@ -39236,7 +39239,7 @@
         <v>441.545553789029</v>
       </c>
       <c r="D55" t="s">
-        <v>19</v>
+        <v>55</v>
       </c>
       <c r="E55" t="n">
         <v>160.835177625991</v>
@@ -39271,7 +39274,7 @@
         <v>402.114546003464</v>
       </c>
       <c r="D56" t="s">
-        <v>19</v>
+        <v>55</v>
       </c>
       <c r="E56" t="n">
         <v>152.587012962377</v>
@@ -39306,7 +39309,7 @@
         <v>415.604020634171</v>
       </c>
       <c r="D57" t="s">
-        <v>19</v>
+        <v>55</v>
       </c>
       <c r="E57" t="n">
         <v>147.242026755211</v>
@@ -39341,7 +39344,7 @@
         <v>388.678093719617</v>
       </c>
       <c r="D58" t="s">
-        <v>19</v>
+        <v>55</v>
       </c>
       <c r="E58" t="n">
         <v>143.0361002888</v>
@@ -39376,7 +39379,7 @@
         <v>381.921024584033</v>
       </c>
       <c r="D59" t="s">
-        <v>19</v>
+        <v>55</v>
       </c>
       <c r="E59" t="n">
         <v>135.651717358873</v>
@@ -39411,7 +39414,7 @@
         <v>343.871642712242</v>
       </c>
       <c r="D60" t="s">
-        <v>19</v>
+        <v>55</v>
       </c>
       <c r="E60" t="n">
         <v>125.516116605586</v>
@@ -39446,7 +39449,7 @@
         <v>278.392849844334</v>
       </c>
       <c r="D61" t="s">
-        <v>19</v>
+        <v>55</v>
       </c>
       <c r="E61" t="n">
         <v>96.4309076650008</v>
@@ -39481,7 +39484,7 @@
         <v>552.999588059656</v>
       </c>
       <c r="D62" t="s">
-        <v>19</v>
+        <v>55</v>
       </c>
       <c r="E62" t="n">
         <v>181.667062324639</v>
@@ -39516,7 +39519,7 @@
         <v>415.919790097539</v>
       </c>
       <c r="D63" t="s">
-        <v>19</v>
+        <v>55</v>
       </c>
       <c r="E63" t="n">
         <v>144.240735887236</v>
@@ -39551,7 +39554,7 @@
         <v>403.270015645571</v>
       </c>
       <c r="D64" t="s">
-        <v>19</v>
+        <v>55</v>
       </c>
       <c r="E64" t="n">
         <v>131.478449269083</v>
@@ -39586,7 +39589,7 @@
         <v>395.589266620817</v>
       </c>
       <c r="D65" t="s">
-        <v>19</v>
+        <v>55</v>
       </c>
       <c r="E65" t="n">
         <v>109.565240701725</v>
@@ -39621,7 +39624,7 @@
         <v>411.996529003578</v>
       </c>
       <c r="D66" t="s">
-        <v>19</v>
+        <v>55</v>
       </c>
       <c r="E66" t="n">
         <v>132.525603476139</v>
@@ -39656,7 +39659,7 @@
         <v>443.587186594379</v>
       </c>
       <c r="D67" t="s">
-        <v>19</v>
+        <v>55</v>
       </c>
       <c r="E67" t="n">
         <v>132.039951050908</v>
@@ -39691,7 +39694,7 @@
         <v>396.906692877017</v>
       </c>
       <c r="D68" t="s">
-        <v>19</v>
+        <v>55</v>
       </c>
       <c r="E68" t="n">
         <v>118.797875624517</v>
@@ -39726,7 +39729,7 @@
         <v>416.07367240518</v>
       </c>
       <c r="D69" t="s">
-        <v>19</v>
+        <v>55</v>
       </c>
       <c r="E69" t="n">
         <v>119.980621619756</v>
@@ -39761,7 +39764,7 @@
         <v>402.012920526603</v>
       </c>
       <c r="D70" t="s">
-        <v>19</v>
+        <v>55</v>
       </c>
       <c r="E70" t="n">
         <v>117.069765846411</v>
@@ -39796,7 +39799,7 @@
         <v>406.487468711936</v>
       </c>
       <c r="D71" t="s">
-        <v>19</v>
+        <v>55</v>
       </c>
       <c r="E71" t="n">
         <v>112.877077338639</v>
@@ -39831,7 +39834,7 @@
         <v>344.200200096181</v>
       </c>
       <c r="D72" t="s">
-        <v>19</v>
+        <v>55</v>
       </c>
       <c r="E72" t="n">
         <v>94.5031491164587</v>
@@ -39866,7 +39869,7 @@
         <v>285.324134585366</v>
       </c>
       <c r="D73" t="s">
-        <v>19</v>
+        <v>55</v>
       </c>
       <c r="E73" t="n">
         <v>74.0949383909342</v>
@@ -47604,16 +47607,16 @@
         <v>46</v>
       </c>
       <c r="B1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="2">
@@ -47624,13 +47627,13 @@
         <v>43831</v>
       </c>
       <c r="C2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D2" s="1" t="n">
         <v>44866</v>
       </c>
       <c r="E2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="3">
@@ -47641,13 +47644,13 @@
         <v>43831</v>
       </c>
       <c r="C3" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D3" s="1" t="n">
         <v>45689</v>
       </c>
       <c r="E3" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="4">
@@ -47658,13 +47661,13 @@
         <v>43831</v>
       </c>
       <c r="C4" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D4" s="1" t="n">
         <v>45139</v>
       </c>
       <c r="E4" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="5">
@@ -47675,13 +47678,13 @@
         <v>43831</v>
       </c>
       <c r="C5" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D5" s="1" t="n">
         <v>45992</v>
       </c>
       <c r="E5" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="6">
@@ -47692,13 +47695,13 @@
         <v>43831</v>
       </c>
       <c r="C6" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D6" s="1" t="n">
         <v>45689</v>
       </c>
       <c r="E6" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="7">
@@ -47709,13 +47712,13 @@
         <v>43831</v>
       </c>
       <c r="C7" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D7" s="1" t="n">
         <v>45992</v>
       </c>
       <c r="E7" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="8">
@@ -47726,13 +47729,13 @@
         <v>43831</v>
       </c>
       <c r="C8" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D8" s="1" t="n">
         <v>45536</v>
       </c>
       <c r="E8" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="9">
@@ -47743,13 +47746,13 @@
         <v>43831</v>
       </c>
       <c r="C9" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D9" s="1" t="n">
         <v>45992</v>
       </c>
       <c r="E9" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="10">
@@ -47760,13 +47763,13 @@
         <v>43831</v>
       </c>
       <c r="C10" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D10" s="1" t="n">
         <v>45689</v>
       </c>
       <c r="E10" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="11">
@@ -47777,13 +47780,13 @@
         <v>43831</v>
       </c>
       <c r="C11" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D11" s="1" t="n">
         <v>45992</v>
       </c>
       <c r="E11" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="12">
@@ -47794,13 +47797,13 @@
         <v>43831</v>
       </c>
       <c r="C12" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D12" s="1" t="n">
         <v>45992</v>
       </c>
       <c r="E12" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="13">
@@ -47811,13 +47814,13 @@
         <v>43831</v>
       </c>
       <c r="C13" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D13" s="1" t="n">
         <v>45992</v>
       </c>
       <c r="E13" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="14">
@@ -47828,13 +47831,13 @@
         <v>43831</v>
       </c>
       <c r="C14" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D14" s="1" t="n">
         <v>44896</v>
       </c>
       <c r="E14" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="15">
@@ -47845,13 +47848,13 @@
         <v>43831</v>
       </c>
       <c r="C15" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D15" s="1" t="n">
         <v>45992</v>
       </c>
       <c r="E15" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="16">
@@ -47862,13 +47865,13 @@
         <v>43831</v>
       </c>
       <c r="C16" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D16" s="1" t="n">
         <v>45992</v>
       </c>
       <c r="E16" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="17">
@@ -47879,13 +47882,13 @@
         <v>43831</v>
       </c>
       <c r="C17" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D17" s="1" t="n">
         <v>45992</v>
       </c>
       <c r="E17" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="18">
@@ -47896,13 +47899,13 @@
         <v>43831</v>
       </c>
       <c r="C18" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D18" s="1" t="n">
         <v>44652</v>
       </c>
       <c r="E18" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="19">
@@ -47913,13 +47916,13 @@
         <v>43831</v>
       </c>
       <c r="C19" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D19" s="1" t="n">
         <v>44805</v>
       </c>
       <c r="E19" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="20">
@@ -47930,13 +47933,13 @@
         <v>43831</v>
       </c>
       <c r="C20" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D20" s="1" t="n">
         <v>44652</v>
       </c>
       <c r="E20" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="21">
@@ -47947,13 +47950,13 @@
         <v>43831</v>
       </c>
       <c r="C21" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D21" s="1" t="n">
         <v>44835</v>
       </c>
       <c r="E21" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="22">
@@ -47964,13 +47967,13 @@
         <v>43831</v>
       </c>
       <c r="C22" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D22" s="1" t="n">
         <v>44044</v>
       </c>
       <c r="E22" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="23">
@@ -47981,13 +47984,13 @@
         <v>43831</v>
       </c>
       <c r="C23" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D23" s="1" t="n">
         <v>45078</v>
       </c>
       <c r="E23" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="24">
@@ -47998,13 +48001,13 @@
         <v>43831</v>
       </c>
       <c r="C24" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D24" s="1" t="n">
         <v>43952</v>
       </c>
       <c r="E24" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="25">
@@ -48015,13 +48018,13 @@
         <v>43831</v>
       </c>
       <c r="C25" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D25" s="1" t="n">
         <v>44013</v>
       </c>
       <c r="E25" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="26">
@@ -48032,13 +48035,13 @@
         <v>43831</v>
       </c>
       <c r="C26" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D26" s="1" t="n">
         <v>44105</v>
       </c>
       <c r="E26" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="27">
@@ -48049,13 +48052,13 @@
         <v>43831</v>
       </c>
       <c r="C27" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D27" s="1" t="n">
         <v>44805</v>
       </c>
       <c r="E27" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="28">
@@ -48066,13 +48069,13 @@
         <v>43831</v>
       </c>
       <c r="C28" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D28" s="1" t="n">
         <v>44713</v>
       </c>
       <c r="E28" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="29">
@@ -48083,13 +48086,13 @@
         <v>43831</v>
       </c>
       <c r="C29" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D29" s="1" t="n">
         <v>44927</v>
       </c>
       <c r="E29" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="30">
@@ -48100,13 +48103,13 @@
         <v>43831</v>
       </c>
       <c r="C30" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D30" s="1" t="n">
         <v>44713</v>
       </c>
       <c r="E30" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="31">
@@ -48117,13 +48120,13 @@
         <v>43831</v>
       </c>
       <c r="C31" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D31" s="1" t="n">
         <v>45992</v>
       </c>
       <c r="E31" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="32">
@@ -48134,13 +48137,13 @@
         <v>43831</v>
       </c>
       <c r="C32" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D32" s="1" t="n">
         <v>44743</v>
       </c>
       <c r="E32" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="33">
@@ -48151,13 +48154,13 @@
         <v>43831</v>
       </c>
       <c r="C33" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D33" s="1" t="n">
         <v>45474</v>
       </c>
       <c r="E33" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="34">
@@ -48168,13 +48171,13 @@
         <v>43831</v>
       </c>
       <c r="C34" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D34" s="1" t="n">
         <v>45231</v>
       </c>
       <c r="E34" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="35">
@@ -48185,13 +48188,13 @@
         <v>43831</v>
       </c>
       <c r="C35" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D35" s="1" t="n">
         <v>45992</v>
       </c>
       <c r="E35" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="36">
@@ -48202,13 +48205,13 @@
         <v>43831</v>
       </c>
       <c r="C36" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D36" s="1" t="n">
         <v>44866</v>
       </c>
       <c r="E36" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="37">
@@ -48219,13 +48222,13 @@
         <v>43831</v>
       </c>
       <c r="C37" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D37" s="1" t="n">
         <v>45689</v>
       </c>
       <c r="E37" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="38">
@@ -48236,13 +48239,13 @@
         <v>43831</v>
       </c>
       <c r="C38" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D38" s="1" t="n">
         <v>45992</v>
       </c>
       <c r="E38" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="39">
@@ -48253,13 +48256,13 @@
         <v>43831</v>
       </c>
       <c r="C39" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D39" s="1" t="n">
         <v>45992</v>
       </c>
       <c r="E39" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="40">
@@ -48270,13 +48273,13 @@
         <v>43831</v>
       </c>
       <c r="C40" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D40" s="1" t="n">
         <v>44927</v>
       </c>
       <c r="E40" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="41">
@@ -48287,47 +48290,47 @@
         <v>43831</v>
       </c>
       <c r="C41" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D41" s="1" t="n">
         <v>45413</v>
       </c>
       <c r="E41" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>19</v>
+        <v>55</v>
       </c>
       <c r="B42" s="1" t="n">
         <v>43831</v>
       </c>
       <c r="C42" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D42" s="1" t="n">
         <v>45047</v>
       </c>
       <c r="E42" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>19</v>
+        <v>55</v>
       </c>
       <c r="B43" s="1" t="n">
         <v>43831</v>
       </c>
       <c r="C43" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D43" s="1" t="n">
         <v>45536</v>
       </c>
       <c r="E43" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="44">
@@ -48338,13 +48341,13 @@
         <v>43831</v>
       </c>
       <c r="C44" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D44" s="1" t="n">
         <v>44927</v>
       </c>
       <c r="E44" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="45">
@@ -48355,13 +48358,13 @@
         <v>43831</v>
       </c>
       <c r="C45" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D45" s="1" t="n">
         <v>45383</v>
       </c>
       <c r="E45" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="46">
@@ -48372,13 +48375,13 @@
         <v>43831</v>
       </c>
       <c r="C46" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D46" s="1" t="n">
         <v>45170</v>
       </c>
       <c r="E46" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="47">
@@ -48389,13 +48392,13 @@
         <v>43831</v>
       </c>
       <c r="C47" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D47" s="1" t="n">
         <v>45992</v>
       </c>
       <c r="E47" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="48">
@@ -48406,13 +48409,13 @@
         <v>43831</v>
       </c>
       <c r="C48" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D48" s="1" t="n">
         <v>44682</v>
       </c>
       <c r="E48" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="49">
@@ -48423,13 +48426,13 @@
         <v>43831</v>
       </c>
       <c r="C49" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D49" s="1" t="n">
         <v>44866</v>
       </c>
       <c r="E49" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
   </sheetData>

--- a/Outcome/Publish/figure_data/fig4.xlsx
+++ b/Outcome/Publish/figure_data/fig4.xlsx
@@ -161,19 +161,17 @@
     <t xml:space="preserve">Pre-COVID (Observed)</t>
   </si>
   <si>
-    <t xml:space="preserve">Post-Recovery (Observed)</t>
+    <t xml:space="preserve">Post-PHSM (Observed)</t>
   </si>
   <si>
-    <t xml:space="preserve">Post-Recovery (Predicted)</t>
+    <t xml:space="preserve">Post-PHSM (Predicted)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
-    <numFmt numFmtId="165" formatCode="mm/dd/yyyy"/>
-  </numFmts>
+  <numFmts count="0"/>
   <fonts count="2">
     <font>
       <sz val="11"/>
@@ -210,7 +208,7 @@
   </cellStyleXfs>
   <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyNumberFormat="1"/>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>

--- a/Outcome/Publish/figure_data/fig4.xlsx
+++ b/Outcome/Publish/figure_data/fig4.xlsx
@@ -128,10 +128,10 @@
     <t xml:space="preserve">1</t>
   </si>
   <si>
+    <t xml:space="preserve">3</t>
+  </si>
+  <si>
     <t xml:space="preserve">2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3</t>
   </si>
 </sst>
 </file>
@@ -479,7 +479,7 @@
         <v>4</v>
       </c>
       <c r="C2" t="n">
-        <v>213705.771933232</v>
+        <v>208566.151363084</v>
       </c>
     </row>
     <row r="3">
@@ -490,7 +490,7 @@
         <v>4</v>
       </c>
       <c r="C3" t="n">
-        <v>1463430.69537175</v>
+        <v>1233435.52803022</v>
       </c>
     </row>
     <row r="4">
@@ -501,7 +501,7 @@
         <v>4</v>
       </c>
       <c r="C4" t="n">
-        <v>174707.761078267</v>
+        <v>198994.908037956</v>
       </c>
     </row>
     <row r="5">
@@ -512,7 +512,7 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>3745.37810794006</v>
+        <v>8179.716350703</v>
       </c>
     </row>
     <row r="6">
@@ -523,7 +523,7 @@
         <v>4</v>
       </c>
       <c r="C6" t="n">
-        <v>8693.5799836956</v>
+        <v>8600.00859599406</v>
       </c>
     </row>
     <row r="7">
@@ -534,7 +534,7 @@
         <v>4</v>
       </c>
       <c r="C7" t="n">
-        <v>2036.62855184469</v>
+        <v>1906.1196847482</v>
       </c>
     </row>
     <row r="8">
@@ -545,7 +545,7 @@
         <v>11</v>
       </c>
       <c r="C8" t="n">
-        <v>136125.791770204</v>
+        <v>137280.410343388</v>
       </c>
     </row>
     <row r="9">
@@ -556,7 +556,7 @@
         <v>11</v>
       </c>
       <c r="C9" t="n">
-        <v>1649.43203417845</v>
+        <v>4027.18165844523</v>
       </c>
     </row>
     <row r="10">
@@ -567,7 +567,7 @@
         <v>11</v>
       </c>
       <c r="C10" t="n">
-        <v>1179.28089114645</v>
+        <v>710.483364008151</v>
       </c>
     </row>
     <row r="11">
@@ -578,7 +578,7 @@
         <v>11</v>
       </c>
       <c r="C11" t="n">
-        <v>1096.79125120878</v>
+        <v>940.730508061435</v>
       </c>
     </row>
     <row r="12">
@@ -589,7 +589,7 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>26.0660434837536</v>
+        <v>31.4334749638212</v>
       </c>
     </row>
     <row r="13">
@@ -600,7 +600,7 @@
         <v>17</v>
       </c>
       <c r="C13" t="n">
-        <v>56282.6746473634</v>
+        <v>55530.4852673625</v>
       </c>
     </row>
     <row r="14">
@@ -611,7 +611,7 @@
         <v>17</v>
       </c>
       <c r="C14" t="n">
-        <v>276.479934279954</v>
+        <v>521.658880940343</v>
       </c>
     </row>
     <row r="15">
@@ -622,7 +622,7 @@
         <v>17</v>
       </c>
       <c r="C15" t="n">
-        <v>249.981486597994</v>
+        <v>1029.49366483948</v>
       </c>
     </row>
     <row r="16">
@@ -633,7 +633,7 @@
         <v>17</v>
       </c>
       <c r="C16" t="n">
-        <v>1002.62606493129</v>
+        <v>1021.62267886647</v>
       </c>
     </row>
     <row r="17">
@@ -644,7 +644,7 @@
         <v>17</v>
       </c>
       <c r="C17" t="n">
-        <v>614.318530576056</v>
+        <v>1062.12555896263</v>
       </c>
     </row>
     <row r="18">
@@ -655,7 +655,7 @@
         <v>23</v>
       </c>
       <c r="C18" t="n">
-        <v>9741.16384132806</v>
+        <v>8799.23152575949</v>
       </c>
     </row>
     <row r="19">
@@ -666,7 +666,7 @@
         <v>23</v>
       </c>
       <c r="C19" t="n">
-        <v>37927.8163321939</v>
+        <v>5061.21321793091</v>
       </c>
     </row>
     <row r="20">
@@ -677,7 +677,7 @@
         <v>23</v>
       </c>
       <c r="C20" t="n">
-        <v>4793.86718554297</v>
+        <v>4501.92785514261</v>
       </c>
     </row>
     <row r="21">
@@ -688,7 +688,7 @@
         <v>23</v>
       </c>
       <c r="C21" t="n">
-        <v>3838.25573626451</v>
+        <v>4016.24392719755</v>
       </c>
     </row>
     <row r="22">
@@ -699,7 +699,7 @@
         <v>23</v>
       </c>
       <c r="C22" t="n">
-        <v>1599.7034947874</v>
+        <v>1637.46763124693</v>
       </c>
     </row>
     <row r="23">
@@ -710,7 +710,7 @@
         <v>23</v>
       </c>
       <c r="C23" t="n">
-        <v>1515.37339858964</v>
+        <v>1615.14096911446</v>
       </c>
     </row>
     <row r="24">
@@ -721,7 +721,7 @@
         <v>23</v>
       </c>
       <c r="C24" t="n">
-        <v>146.669525368677</v>
+        <v>163.934353869879</v>
       </c>
     </row>
   </sheetData>
@@ -760,13 +760,13 @@
         <v>4</v>
       </c>
       <c r="C2" t="n">
-        <v>0.279365719412144</v>
+        <v>0.274491213557867</v>
       </c>
       <c r="D2" t="n">
-        <v>2.26864092765106</v>
+        <v>2.25623000075569</v>
       </c>
       <c r="E2" t="n">
-        <v>27.94</v>
+        <v>27.45</v>
       </c>
     </row>
     <row r="3">
@@ -777,13 +777,13 @@
         <v>4</v>
       </c>
       <c r="C3" t="n">
-        <v>0.825178955136324</v>
+        <v>0.770826612703138</v>
       </c>
       <c r="D3" t="n">
-        <v>4.06120153402493</v>
+        <v>5.38441292750874</v>
       </c>
       <c r="E3" t="n">
-        <v>82.52</v>
+        <v>77.08</v>
       </c>
     </row>
     <row r="4">
@@ -794,13 +794,13 @@
         <v>4</v>
       </c>
       <c r="C4" t="n">
-        <v>0.52732133779276</v>
+        <v>0.593818056246074</v>
       </c>
       <c r="D4" t="n">
-        <v>0.656981044371095</v>
+        <v>1.31801984955663</v>
       </c>
       <c r="E4" t="n">
-        <v>52.73</v>
+        <v>59.38</v>
       </c>
     </row>
     <row r="5">
@@ -811,13 +811,13 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>0.532969487397903</v>
+        <v>0.622613255785912</v>
       </c>
       <c r="D5" t="n">
-        <v>3.6807482079489</v>
+        <v>1.33911575013123</v>
       </c>
       <c r="E5" t="n">
-        <v>53.3</v>
+        <v>62.26</v>
       </c>
     </row>
     <row r="6">
@@ -828,13 +828,13 @@
         <v>4</v>
       </c>
       <c r="C6" t="n">
-        <v>0.752979061768441</v>
+        <v>0.750960717843188</v>
       </c>
       <c r="D6" t="n">
-        <v>7.96248900453676</v>
+        <v>7.81258703681891</v>
       </c>
       <c r="E6" t="n">
-        <v>75.3</v>
+        <v>75.1</v>
       </c>
     </row>
     <row r="7">
@@ -845,13 +845,13 @@
         <v>4</v>
       </c>
       <c r="C7" t="n">
-        <v>0.826678417215016</v>
+        <v>0.816983242312284</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0683963575558215</v>
+        <v>0.0752496396590436</v>
       </c>
       <c r="E7" t="n">
-        <v>82.67</v>
+        <v>81.7</v>
       </c>
     </row>
     <row r="8">
@@ -862,13 +862,13 @@
         <v>11</v>
       </c>
       <c r="C8" t="n">
-        <v>0.520828806653862</v>
+        <v>0.522936315833308</v>
       </c>
       <c r="D8" t="n">
-        <v>4.01123798425685</v>
+        <v>3.98803982999847</v>
       </c>
       <c r="E8" t="n">
-        <v>52.08</v>
+        <v>52.29</v>
       </c>
     </row>
     <row r="9">
@@ -879,13 +879,13 @@
         <v>11</v>
       </c>
       <c r="C9" t="n">
-        <v>0.162131326836121</v>
+        <v>0.315803347718012</v>
       </c>
       <c r="D9" t="n">
-        <v>6.85014917582655</v>
+        <v>2.05501599388022</v>
       </c>
       <c r="E9" t="n">
-        <v>16.21</v>
+        <v>31.58</v>
       </c>
     </row>
     <row r="10">
@@ -896,13 +896,13 @@
         <v>11</v>
       </c>
       <c r="C10" t="n">
-        <v>0.268306149334371</v>
+        <v>0.203899198184402</v>
       </c>
       <c r="D10" t="n">
-        <v>5.25376762935413</v>
+        <v>8.51681481550408</v>
       </c>
       <c r="E10" t="n">
-        <v>26.83</v>
+        <v>20.39</v>
       </c>
     </row>
     <row r="11">
@@ -913,13 +913,13 @@
         <v>11</v>
       </c>
       <c r="C11" t="n">
-        <v>0.158615236724181</v>
+        <v>0.139187456422384</v>
       </c>
       <c r="D11" t="n">
-        <v>2.10577811305707</v>
+        <v>2.13890275428367</v>
       </c>
       <c r="E11" t="n">
-        <v>15.86</v>
+        <v>13.92</v>
       </c>
     </row>
     <row r="12">
@@ -930,13 +930,13 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>0.182195878553904</v>
+        <v>0.211768099961836</v>
       </c>
       <c r="D12" t="n">
-        <v>4.21262045164963</v>
+        <v>4.3070090372524</v>
       </c>
       <c r="E12" t="n">
-        <v>18.22</v>
+        <v>21.18</v>
       </c>
     </row>
     <row r="13">
@@ -947,13 +947,13 @@
         <v>17</v>
       </c>
       <c r="C13" t="n">
-        <v>0.490358290163932</v>
+        <v>0.486996377527185</v>
       </c>
       <c r="D13" t="n">
-        <v>5.92905752727299</v>
+        <v>5.54954574978561</v>
       </c>
       <c r="E13" t="n">
-        <v>49.04</v>
+        <v>48.7</v>
       </c>
     </row>
     <row r="14">
@@ -964,13 +964,13 @@
         <v>17</v>
       </c>
       <c r="C14" t="n">
-        <v>0.0840752991672098</v>
+        <v>0.138127084649609</v>
       </c>
       <c r="D14" t="n">
-        <v>4.03899779835412</v>
+        <v>5.91244538148531</v>
       </c>
       <c r="E14" t="n">
-        <v>8.41</v>
+        <v>13.81</v>
       </c>
     </row>
     <row r="15">
@@ -981,13 +981,13 @@
         <v>17</v>
       </c>
       <c r="C15" t="n">
-        <v>0.193486895277608</v>
+        <v>0.348450117558607</v>
       </c>
       <c r="D15" t="n">
-        <v>2.85154236856698</v>
+        <v>7.26279853475374</v>
       </c>
       <c r="E15" t="n">
-        <v>19.35</v>
+        <v>34.85</v>
       </c>
     </row>
     <row r="16">
@@ -998,13 +998,13 @@
         <v>17</v>
       </c>
       <c r="C16" t="n">
-        <v>0.48142394922171</v>
+        <v>0.486111369628677</v>
       </c>
       <c r="D16" t="n">
-        <v>2.60435297119371</v>
+        <v>2.6757566376574</v>
       </c>
       <c r="E16" t="n">
-        <v>48.14</v>
+        <v>48.61</v>
       </c>
     </row>
     <row r="17">
@@ -1015,13 +1015,13 @@
         <v>17</v>
       </c>
       <c r="C17" t="n">
-        <v>0.352586808781139</v>
+        <v>0.307583822489706</v>
       </c>
       <c r="D17" t="n">
-        <v>2.49338008207189</v>
+        <v>0.708060899050319</v>
       </c>
       <c r="E17" t="n">
-        <v>35.26</v>
+        <v>30.76</v>
       </c>
     </row>
     <row r="18">
@@ -1032,13 +1032,13 @@
         <v>23</v>
       </c>
       <c r="C18" t="n">
-        <v>0.343081309845054</v>
+        <v>0.320540501707639</v>
       </c>
       <c r="D18" t="n">
-        <v>1.82697939334667</v>
+        <v>1.89154911330883</v>
       </c>
       <c r="E18" t="n">
-        <v>34.31</v>
+        <v>32.05</v>
       </c>
     </row>
     <row r="19">
@@ -1049,13 +1049,13 @@
         <v>23</v>
       </c>
       <c r="C19" t="n">
-        <v>0.246484884507112</v>
+        <v>0.124399328837739</v>
       </c>
       <c r="D19" t="n">
-        <v>0.987770430596723</v>
+        <v>1.55601404266236</v>
       </c>
       <c r="E19" t="n">
-        <v>24.65</v>
+        <v>12.44</v>
       </c>
     </row>
     <row r="20">
@@ -1066,13 +1066,13 @@
         <v>23</v>
       </c>
       <c r="C20" t="n">
-        <v>0.209175973782021</v>
+        <v>0.212817585744397</v>
       </c>
       <c r="D20" t="n">
-        <v>3.06490315259725</v>
+        <v>3.09913502283175</v>
       </c>
       <c r="E20" t="n">
-        <v>20.92</v>
+        <v>21.28</v>
       </c>
     </row>
     <row r="21">
@@ -1083,13 +1083,13 @@
         <v>23</v>
       </c>
       <c r="C21" t="n">
-        <v>0.232350403525653</v>
+        <v>0.246482374091248</v>
       </c>
       <c r="D21" t="n">
-        <v>2.84453657101213</v>
+        <v>2.52831076732444</v>
       </c>
       <c r="E21" t="n">
-        <v>23.24</v>
+        <v>24.65</v>
       </c>
     </row>
     <row r="22">
@@ -1100,13 +1100,13 @@
         <v>23</v>
       </c>
       <c r="C22" t="n">
-        <v>0.244913673142701</v>
+        <v>0.249254235374948</v>
       </c>
       <c r="D22" t="n">
-        <v>3.2674244746727</v>
+        <v>3.23488709521482</v>
       </c>
       <c r="E22" t="n">
-        <v>24.49</v>
+        <v>24.93</v>
       </c>
     </row>
     <row r="23">
@@ -1117,13 +1117,13 @@
         <v>23</v>
       </c>
       <c r="C23" t="n">
-        <v>0.241556384788178</v>
+        <v>0.253429349349366</v>
       </c>
       <c r="D23" t="n">
-        <v>1.55568983384528</v>
+        <v>1.48212624796213</v>
       </c>
       <c r="E23" t="n">
-        <v>24.16</v>
+        <v>25.34</v>
       </c>
     </row>
     <row r="24">
@@ -1134,13 +1134,13 @@
         <v>23</v>
       </c>
       <c r="C24" t="n">
-        <v>0.13893507565017</v>
+        <v>0.172756264120203</v>
       </c>
       <c r="D24" t="n">
-        <v>16.2242913160414</v>
+        <v>15.4607994636716</v>
       </c>
       <c r="E24" t="n">
-        <v>13.89</v>
+        <v>17.28</v>
       </c>
     </row>
   </sheetData>
@@ -1182,10 +1182,10 @@
         <v>31</v>
       </c>
       <c r="D2" t="n">
-        <v>2.26864092765106</v>
+        <v>2.25623000075569</v>
       </c>
       <c r="E2" t="n">
-        <v>213705.771933232</v>
+        <v>208566.151363084</v>
       </c>
     </row>
     <row r="3">
@@ -1196,217 +1196,217 @@
         <v>4</v>
       </c>
       <c r="C3" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D3" t="n">
-        <v>4.06120153402493</v>
+        <v>5.38441292750874</v>
       </c>
       <c r="E3" t="n">
-        <v>1463430.69537175</v>
+        <v>1233435.52803022</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B4" t="s">
         <v>4</v>
       </c>
       <c r="C4" t="n">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="D4" t="n">
-        <v>3.6807482079489</v>
+        <v>1.31801984955663</v>
       </c>
       <c r="E4" t="n">
-        <v>3745.37810794006</v>
+        <v>198994.908037956</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B5" t="s">
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="D5" t="n">
-        <v>7.96248900453676</v>
+        <v>1.33911575013123</v>
       </c>
       <c r="E5" t="n">
-        <v>8693.5799836956</v>
+        <v>8179.716350703</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B6" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="C6" t="n">
-        <v>34</v>
+        <v>61</v>
       </c>
       <c r="D6" t="n">
-        <v>4.01123798425685</v>
+        <v>7.81258703681891</v>
       </c>
       <c r="E6" t="n">
-        <v>136125.791770204</v>
+        <v>8600.00859599406</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B7" t="s">
         <v>11</v>
       </c>
       <c r="C7" t="n">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="D7" t="n">
-        <v>6.85014917582655</v>
+        <v>3.98803982999847</v>
       </c>
       <c r="E7" t="n">
-        <v>1649.43203417845</v>
+        <v>137280.410343388</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B8" t="s">
         <v>11</v>
       </c>
       <c r="C8" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D8" t="n">
-        <v>5.25376762935413</v>
+        <v>2.05501599388022</v>
       </c>
       <c r="E8" t="n">
-        <v>1179.28089114645</v>
+        <v>4027.18165844523</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B9" t="s">
         <v>11</v>
       </c>
       <c r="C9" t="n">
-        <v>25</v>
+        <v>6</v>
       </c>
       <c r="D9" t="n">
-        <v>2.10577811305707</v>
+        <v>8.51681481550408</v>
       </c>
       <c r="E9" t="n">
-        <v>1096.79125120878</v>
+        <v>710.483364008151</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B10" t="s">
         <v>11</v>
       </c>
       <c r="C10" t="n">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="D10" t="n">
-        <v>4.21262045164963</v>
+        <v>2.13890275428367</v>
       </c>
       <c r="E10" t="n">
-        <v>26.0660434837536</v>
+        <v>940.730508061435</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B11" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="C11" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D11" t="n">
-        <v>5.92905752727299</v>
+        <v>4.3070090372524</v>
       </c>
       <c r="E11" t="n">
-        <v>56282.6746473634</v>
+        <v>31.4334749638212</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B12" t="s">
         <v>17</v>
       </c>
       <c r="C12" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D12" t="n">
-        <v>4.03899779835412</v>
+        <v>5.54954574978561</v>
       </c>
       <c r="E12" t="n">
-        <v>276.479934279954</v>
+        <v>55530.4852673625</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B13" t="s">
         <v>17</v>
       </c>
       <c r="C13" t="n">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="D13" t="n">
-        <v>2.85154236856698</v>
+        <v>5.91244538148531</v>
       </c>
       <c r="E13" t="n">
-        <v>249.981486597994</v>
+        <v>521.658880940343</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B14" t="s">
         <v>17</v>
       </c>
       <c r="C14" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D14" t="n">
-        <v>2.60435297119371</v>
+        <v>7.26279853475374</v>
       </c>
       <c r="E14" t="n">
-        <v>1002.62606493129</v>
+        <v>1029.49366483948</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B15" t="s">
         <v>17</v>
       </c>
       <c r="C15" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="D15" t="n">
-        <v>2.49338008207189</v>
+        <v>2.6757566376574</v>
       </c>
       <c r="E15" t="n">
-        <v>614.318530576056</v>
+        <v>1021.62267886647</v>
       </c>
     </row>
     <row r="16">
@@ -1417,98 +1417,115 @@
         <v>23</v>
       </c>
       <c r="C16" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D16" t="n">
-        <v>1.82697939334667</v>
+        <v>1.89154911330883</v>
       </c>
       <c r="E16" t="n">
-        <v>9741.16384132806</v>
+        <v>8799.23152575949</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B17" t="s">
         <v>23</v>
       </c>
       <c r="C17" t="n">
-        <v>39</v>
+        <v>20</v>
       </c>
       <c r="D17" t="n">
-        <v>3.06490315259725</v>
+        <v>1.55601404266236</v>
       </c>
       <c r="E17" t="n">
-        <v>4793.86718554297</v>
+        <v>5061.21321793091</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B18" t="s">
         <v>23</v>
       </c>
       <c r="C18" t="n">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="D18" t="n">
-        <v>2.84453657101213</v>
+        <v>3.09913502283175</v>
       </c>
       <c r="E18" t="n">
-        <v>3838.25573626451</v>
+        <v>4501.92785514261</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B19" t="s">
         <v>23</v>
       </c>
       <c r="C19" t="n">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="D19" t="n">
-        <v>3.2674244746727</v>
+        <v>2.52831076732444</v>
       </c>
       <c r="E19" t="n">
-        <v>1599.7034947874</v>
+        <v>4016.24392719755</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B20" t="s">
         <v>23</v>
       </c>
       <c r="C20" t="n">
-        <v>46</v>
+        <v>35</v>
       </c>
       <c r="D20" t="n">
-        <v>1.55568983384528</v>
+        <v>3.23488709521482</v>
       </c>
       <c r="E20" t="n">
-        <v>1515.37339858964</v>
+        <v>1637.46763124693</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
+        <v>28</v>
+      </c>
+      <c r="B21" t="s">
+        <v>23</v>
+      </c>
+      <c r="C21" t="n">
+        <v>46</v>
+      </c>
+      <c r="D21" t="n">
+        <v>1.48212624796213</v>
+      </c>
+      <c r="E21" t="n">
+        <v>1615.14096911446</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="s">
         <v>29</v>
       </c>
-      <c r="B21" t="s">
-        <v>23</v>
-      </c>
-      <c r="C21" t="n">
+      <c r="B22" t="s">
+        <v>23</v>
+      </c>
+      <c r="C22" t="n">
         <v>28</v>
       </c>
-      <c r="D21" t="n">
-        <v>16.2242913160414</v>
-      </c>
-      <c r="E21" t="n">
-        <v>146.669525368677</v>
+      <c r="D22" t="n">
+        <v>15.4607994636716</v>
+      </c>
+      <c r="E22" t="n">
+        <v>163.934353869879</v>
       </c>
     </row>
   </sheetData>
@@ -1547,13 +1564,13 @@
         <v>3</v>
       </c>
       <c r="B2" t="n">
-        <v>0.279365719412144</v>
+        <v>0.274491213557867</v>
       </c>
       <c r="C2" t="n">
-        <v>2.26864092765106</v>
+        <v>2.25623000075569</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.553826886638229</v>
+        <v>-0.561471552723567</v>
       </c>
       <c r="E2" t="s">
         <v>36</v>
@@ -1567,13 +1584,13 @@
         <v>5</v>
       </c>
       <c r="B3" t="n">
-        <v>0.825178955136324</v>
+        <v>0.770826612703138</v>
       </c>
       <c r="C3" t="n">
-        <v>4.06120153402493</v>
+        <v>5.38441292750874</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.0834518565407574</v>
+        <v>-0.113043299789024</v>
       </c>
       <c r="E3" t="s">
         <v>37</v>
@@ -1587,16 +1604,16 @@
         <v>6</v>
       </c>
       <c r="B4" t="n">
-        <v>0.52732133779276</v>
+        <v>0.593818056246074</v>
       </c>
       <c r="C4" t="n">
-        <v>0.656981044371095</v>
+        <v>1.31801984955663</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.277924654805158</v>
+        <v>-0.22634660093194</v>
       </c>
       <c r="E4" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="F4" t="s">
         <v>4</v>
@@ -1607,16 +1624,16 @@
         <v>7</v>
       </c>
       <c r="B5" t="n">
-        <v>0.532969487397903</v>
+        <v>0.622613255785912</v>
       </c>
       <c r="C5" t="n">
-        <v>3.6807482079489</v>
+        <v>1.33911575013123</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.27329765370145</v>
+        <v>-0.205781637181627</v>
       </c>
       <c r="E5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F5" t="s">
         <v>4</v>
@@ -1627,13 +1644,13 @@
         <v>8</v>
       </c>
       <c r="B6" t="n">
-        <v>0.752979061768441</v>
+        <v>0.750960717843188</v>
       </c>
       <c r="C6" t="n">
-        <v>7.96248900453676</v>
+        <v>7.81258703681891</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.12321710014041</v>
+        <v>-0.124382780000001</v>
       </c>
       <c r="E6" t="s">
         <v>37</v>
@@ -1647,16 +1664,16 @@
         <v>9</v>
       </c>
       <c r="B7" t="n">
-        <v>0.826678417215016</v>
+        <v>0.816983242312284</v>
       </c>
       <c r="C7" t="n">
-        <v>0.0683963575558215</v>
+        <v>0.0752496396590436</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.0826634007135609</v>
+        <v>-0.0877868514797552</v>
       </c>
       <c r="E7" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="F7" t="s">
         <v>4</v>
@@ -1667,16 +1684,16 @@
         <v>10</v>
       </c>
       <c r="B8" t="n">
-        <v>0.520828806653862</v>
+        <v>0.522936315833308</v>
       </c>
       <c r="C8" t="n">
-        <v>4.01123798425685</v>
+        <v>3.98803982999847</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.28330500327083</v>
+        <v>-0.281551197110188</v>
       </c>
       <c r="E8" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F8" t="s">
         <v>11</v>
@@ -1687,16 +1704,16 @@
         <v>12</v>
       </c>
       <c r="B9" t="n">
-        <v>0.162131326836121</v>
+        <v>0.315803347718012</v>
       </c>
       <c r="C9" t="n">
-        <v>6.85014917582655</v>
+        <v>2.05501599388022</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.790133063142851</v>
+        <v>-0.5005832705033</v>
       </c>
       <c r="E9" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F9" t="s">
         <v>11</v>
@@ -1707,16 +1724,16 @@
         <v>13</v>
       </c>
       <c r="B10" t="n">
-        <v>0.268306149334371</v>
+        <v>0.203899198184402</v>
       </c>
       <c r="C10" t="n">
-        <v>5.25376762935413</v>
+        <v>8.51681481550408</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.571369373577109</v>
+        <v>-0.690584482043215</v>
       </c>
       <c r="E10" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F10" t="s">
         <v>11</v>
@@ -1727,16 +1744,16 @@
         <v>14</v>
       </c>
       <c r="B11" t="n">
-        <v>0.158615236724181</v>
+        <v>0.139187456422384</v>
       </c>
       <c r="C11" t="n">
-        <v>2.10577811305707</v>
+        <v>2.13890275428367</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.799655096290825</v>
+        <v>-0.856399901593301</v>
       </c>
       <c r="E11" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F11" t="s">
         <v>11</v>
@@ -1747,16 +1764,16 @@
         <v>15</v>
       </c>
       <c r="B12" t="n">
-        <v>0.182195878553904</v>
+        <v>0.211768099961836</v>
       </c>
       <c r="C12" t="n">
-        <v>4.21262045164963</v>
+        <v>4.3070090372524</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.739461451410998</v>
+        <v>-0.67413945996959</v>
       </c>
       <c r="E12" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F12" t="s">
         <v>11</v>
@@ -1767,13 +1784,13 @@
         <v>16</v>
       </c>
       <c r="B13" t="n">
-        <v>0.490358290163932</v>
+        <v>0.486996377527185</v>
       </c>
       <c r="C13" t="n">
-        <v>5.92905752727299</v>
+        <v>5.54954574978561</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.30948647797175</v>
+        <v>-0.312474269228498</v>
       </c>
       <c r="E13" t="s">
         <v>37</v>
@@ -1787,16 +1804,16 @@
         <v>18</v>
       </c>
       <c r="B14" t="n">
-        <v>0.0840752991672098</v>
+        <v>0.138127084649609</v>
       </c>
       <c r="C14" t="n">
-        <v>4.03899779835412</v>
+        <v>5.91244538148531</v>
       </c>
       <c r="D14" t="n">
-        <v>-1.07533157864982</v>
+        <v>-0.859721154436951</v>
       </c>
       <c r="E14" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F14" t="s">
         <v>17</v>
@@ -1807,16 +1824,16 @@
         <v>19</v>
       </c>
       <c r="B15" t="n">
-        <v>0.193486895277608</v>
+        <v>0.348450117558607</v>
       </c>
       <c r="C15" t="n">
-        <v>2.85154236856698</v>
+        <v>7.26279853475374</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.713348444088747</v>
+        <v>-0.457859384623648</v>
       </c>
       <c r="E15" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F15" t="s">
         <v>17</v>
@@ -1827,16 +1844,16 @@
         <v>20</v>
       </c>
       <c r="B16" t="n">
-        <v>0.48142394922171</v>
+        <v>0.486111369628677</v>
       </c>
       <c r="C16" t="n">
-        <v>2.60435297119371</v>
+        <v>2.6757566376574</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.317472308834312</v>
+        <v>-0.313264221119964</v>
       </c>
       <c r="E16" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="F16" t="s">
         <v>17</v>
@@ -1847,13 +1864,13 @@
         <v>21</v>
       </c>
       <c r="B17" t="n">
-        <v>0.352586808781139</v>
+        <v>0.307583822489706</v>
       </c>
       <c r="C17" t="n">
-        <v>2.49338008207189</v>
+        <v>0.708060899050319</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.452733939854977</v>
+        <v>-0.512036510184687</v>
       </c>
       <c r="E17" t="s">
         <v>36</v>
@@ -1867,13 +1884,13 @@
         <v>22</v>
       </c>
       <c r="B18" t="n">
-        <v>0.343081309845054</v>
+        <v>0.320540501707639</v>
       </c>
       <c r="C18" t="n">
-        <v>1.82697939334667</v>
+        <v>1.89154911330883</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.464602940504748</v>
+        <v>-0.494117087652739</v>
       </c>
       <c r="E18" t="s">
         <v>36</v>
@@ -1887,13 +1904,13 @@
         <v>24</v>
       </c>
       <c r="B19" t="n">
-        <v>0.246484884507112</v>
+        <v>0.124399328837739</v>
       </c>
       <c r="C19" t="n">
-        <v>0.987770430596723</v>
+        <v>1.55601404266236</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.608209708339822</v>
+        <v>-0.905181962754949</v>
       </c>
       <c r="E19" t="s">
         <v>36</v>
@@ -1907,16 +1924,16 @@
         <v>25</v>
       </c>
       <c r="B20" t="n">
-        <v>0.209175973782021</v>
+        <v>0.212817585744397</v>
       </c>
       <c r="C20" t="n">
-        <v>3.06490315259725</v>
+        <v>3.09913502283175</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.679488200555833</v>
+        <v>-0.671992487861044</v>
       </c>
       <c r="E20" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F20" t="s">
         <v>23</v>
@@ -1927,16 +1944,16 @@
         <v>26</v>
       </c>
       <c r="B21" t="n">
-        <v>0.232350403525653</v>
+        <v>0.246482374091248</v>
       </c>
       <c r="C21" t="n">
-        <v>2.84453657101213</v>
+        <v>2.52831076732444</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.633856568940172</v>
+        <v>-0.608214131594058</v>
       </c>
       <c r="E21" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F21" t="s">
         <v>23</v>
@@ -1947,16 +1964,16 @@
         <v>27</v>
       </c>
       <c r="B22" t="n">
-        <v>0.244913673142701</v>
+        <v>0.249254235374948</v>
       </c>
       <c r="C22" t="n">
-        <v>3.2674244746727</v>
+        <v>3.23488709521482</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.610986968224968</v>
+        <v>-0.603357453339913</v>
       </c>
       <c r="E22" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F22" t="s">
         <v>23</v>
@@ -1967,13 +1984,13 @@
         <v>28</v>
       </c>
       <c r="B23" t="n">
-        <v>0.241556384788178</v>
+        <v>0.253429349349366</v>
       </c>
       <c r="C23" t="n">
-        <v>1.55568983384528</v>
+        <v>1.48212624796213</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.616981478808273</v>
+        <v>-0.596143091416335</v>
       </c>
       <c r="E23" t="s">
         <v>36</v>

--- a/Outcome/Publish/figure_data/fig4.xlsx
+++ b/Outcome/Publish/figure_data/fig4.xlsx
@@ -128,10 +128,10 @@
     <t xml:space="preserve">1</t>
   </si>
   <si>
+    <t xml:space="preserve">2</t>
+  </si>
+  <si>
     <t xml:space="preserve">3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2</t>
   </si>
 </sst>
 </file>
@@ -501,7 +501,7 @@
         <v>4</v>
       </c>
       <c r="C4" t="n">
-        <v>198994.908037956</v>
+        <v>198994.910071112</v>
       </c>
     </row>
     <row r="5">
@@ -567,7 +567,7 @@
         <v>11</v>
       </c>
       <c r="C10" t="n">
-        <v>710.483364008151</v>
+        <v>710.483368250585</v>
       </c>
     </row>
     <row r="11">
@@ -578,7 +578,7 @@
         <v>11</v>
       </c>
       <c r="C11" t="n">
-        <v>940.730508061435</v>
+        <v>941.808742228531</v>
       </c>
     </row>
     <row r="12">
@@ -600,7 +600,7 @@
         <v>17</v>
       </c>
       <c r="C13" t="n">
-        <v>55530.4852673625</v>
+        <v>57740.5466290565</v>
       </c>
     </row>
     <row r="14">
@@ -611,7 +611,7 @@
         <v>17</v>
       </c>
       <c r="C14" t="n">
-        <v>521.658880940343</v>
+        <v>249.868633941053</v>
       </c>
     </row>
     <row r="15">
@@ -622,7 +622,7 @@
         <v>17</v>
       </c>
       <c r="C15" t="n">
-        <v>1029.49366483948</v>
+        <v>684.322051325585</v>
       </c>
     </row>
     <row r="16">
@@ -633,7 +633,7 @@
         <v>17</v>
       </c>
       <c r="C16" t="n">
-        <v>1021.62267886647</v>
+        <v>1042.49991372976</v>
       </c>
     </row>
     <row r="17">
@@ -644,7 +644,7 @@
         <v>17</v>
       </c>
       <c r="C17" t="n">
-        <v>1062.12555896263</v>
+        <v>1161.73959105307</v>
       </c>
     </row>
     <row r="18">
@@ -666,7 +666,7 @@
         <v>23</v>
       </c>
       <c r="C19" t="n">
-        <v>5061.21321793091</v>
+        <v>2103.174118453</v>
       </c>
     </row>
     <row r="20">
@@ -688,7 +688,7 @@
         <v>23</v>
       </c>
       <c r="C21" t="n">
-        <v>4016.24392719755</v>
+        <v>3622.00955535986</v>
       </c>
     </row>
     <row r="22">
@@ -699,7 +699,7 @@
         <v>23</v>
       </c>
       <c r="C22" t="n">
-        <v>1637.46763124693</v>
+        <v>1638.11793719671</v>
       </c>
     </row>
     <row r="23">
@@ -721,7 +721,7 @@
         <v>23</v>
       </c>
       <c r="C24" t="n">
-        <v>163.934353869879</v>
+        <v>163.934353869906</v>
       </c>
     </row>
   </sheetData>
@@ -794,10 +794,10 @@
         <v>4</v>
       </c>
       <c r="C4" t="n">
-        <v>0.593818056246074</v>
+        <v>0.593818058710427</v>
       </c>
       <c r="D4" t="n">
-        <v>1.31801984955663</v>
+        <v>1.31801985854874</v>
       </c>
       <c r="E4" t="n">
         <v>59.38</v>
@@ -896,10 +896,10 @@
         <v>11</v>
       </c>
       <c r="C10" t="n">
-        <v>0.203899198184402</v>
+        <v>0.203899199153672</v>
       </c>
       <c r="D10" t="n">
-        <v>8.51681481550408</v>
+        <v>8.51681486409554</v>
       </c>
       <c r="E10" t="n">
         <v>20.39</v>
@@ -913,13 +913,13 @@
         <v>11</v>
       </c>
       <c r="C11" t="n">
-        <v>0.139187456422384</v>
+        <v>0.139324761711829</v>
       </c>
       <c r="D11" t="n">
-        <v>2.13890275428367</v>
+        <v>2.13851126674038</v>
       </c>
       <c r="E11" t="n">
-        <v>13.92</v>
+        <v>13.93</v>
       </c>
     </row>
     <row r="12">
@@ -947,13 +947,13 @@
         <v>17</v>
       </c>
       <c r="C13" t="n">
-        <v>0.486996377527185</v>
+        <v>0.49675036211565</v>
       </c>
       <c r="D13" t="n">
-        <v>5.54954574978561</v>
+        <v>5.27889248759791</v>
       </c>
       <c r="E13" t="n">
-        <v>48.7</v>
+        <v>49.68</v>
       </c>
     </row>
     <row r="14">
@@ -964,13 +964,13 @@
         <v>17</v>
       </c>
       <c r="C14" t="n">
-        <v>0.138127084649609</v>
+        <v>0.0766029113928961</v>
       </c>
       <c r="D14" t="n">
-        <v>5.91244538148531</v>
+        <v>4.34103148571146</v>
       </c>
       <c r="E14" t="n">
-        <v>13.81</v>
+        <v>7.66</v>
       </c>
     </row>
     <row r="15">
@@ -981,13 +981,13 @@
         <v>17</v>
       </c>
       <c r="C15" t="n">
-        <v>0.348450117558607</v>
+        <v>0.321531250827086</v>
       </c>
       <c r="D15" t="n">
-        <v>7.26279853475374</v>
+        <v>17.8885309688549</v>
       </c>
       <c r="E15" t="n">
-        <v>34.85</v>
+        <v>32.15</v>
       </c>
     </row>
     <row r="16">
@@ -998,13 +998,13 @@
         <v>17</v>
       </c>
       <c r="C16" t="n">
-        <v>0.486111369628677</v>
+        <v>0.491166057056667</v>
       </c>
       <c r="D16" t="n">
-        <v>2.6757566376574</v>
+        <v>2.66345767681024</v>
       </c>
       <c r="E16" t="n">
-        <v>48.61</v>
+        <v>49.12</v>
       </c>
     </row>
     <row r="17">
@@ -1015,13 +1015,13 @@
         <v>17</v>
       </c>
       <c r="C17" t="n">
-        <v>0.307583822489706</v>
+        <v>0.326998239324576</v>
       </c>
       <c r="D17" t="n">
-        <v>0.708060899050319</v>
+        <v>0.695767449023808</v>
       </c>
       <c r="E17" t="n">
-        <v>30.76</v>
+        <v>32.7</v>
       </c>
     </row>
     <row r="18">
@@ -1049,13 +1049,13 @@
         <v>23</v>
       </c>
       <c r="C19" t="n">
-        <v>0.124399328837739</v>
+        <v>0.0665073692658114</v>
       </c>
       <c r="D19" t="n">
-        <v>1.55601404266236</v>
+        <v>1.92277733046749</v>
       </c>
       <c r="E19" t="n">
-        <v>12.44</v>
+        <v>6.65</v>
       </c>
     </row>
     <row r="20">
@@ -1083,13 +1083,13 @@
         <v>23</v>
       </c>
       <c r="C21" t="n">
-        <v>0.246482374091248</v>
+        <v>0.25364195600278</v>
       </c>
       <c r="D21" t="n">
-        <v>2.52831076732444</v>
+        <v>2.70630202222186</v>
       </c>
       <c r="E21" t="n">
-        <v>24.65</v>
+        <v>25.36</v>
       </c>
     </row>
     <row r="22">
@@ -1100,10 +1100,10 @@
         <v>23</v>
       </c>
       <c r="C22" t="n">
-        <v>0.249254235374948</v>
+        <v>0.249328543696683</v>
       </c>
       <c r="D22" t="n">
-        <v>3.23488709521482</v>
+        <v>3.23441633610315</v>
       </c>
       <c r="E22" t="n">
         <v>24.93</v>
@@ -1134,10 +1134,10 @@
         <v>23</v>
       </c>
       <c r="C24" t="n">
-        <v>0.172756264120203</v>
+        <v>0.172756264120226</v>
       </c>
       <c r="D24" t="n">
-        <v>15.4607994636716</v>
+        <v>15.4607994636717</v>
       </c>
       <c r="E24" t="n">
         <v>17.28</v>
@@ -1216,10 +1216,10 @@
         <v>66</v>
       </c>
       <c r="D4" t="n">
-        <v>1.31801984955663</v>
+        <v>1.31801985854874</v>
       </c>
       <c r="E4" t="n">
-        <v>198994.908037956</v>
+        <v>198994.910071112</v>
       </c>
     </row>
     <row r="5">
@@ -1301,10 +1301,10 @@
         <v>6</v>
       </c>
       <c r="D9" t="n">
-        <v>8.51681481550408</v>
+        <v>8.51681486409554</v>
       </c>
       <c r="E9" t="n">
-        <v>710.483364008151</v>
+        <v>710.483368250585</v>
       </c>
     </row>
     <row r="10">
@@ -1318,10 +1318,10 @@
         <v>24</v>
       </c>
       <c r="D10" t="n">
-        <v>2.13890275428367</v>
+        <v>2.13851126674038</v>
       </c>
       <c r="E10" t="n">
-        <v>940.730508061435</v>
+        <v>941.808742228531</v>
       </c>
     </row>
     <row r="11">
@@ -1352,10 +1352,10 @@
         <v>9</v>
       </c>
       <c r="D12" t="n">
-        <v>5.54954574978561</v>
+        <v>5.27889248759791</v>
       </c>
       <c r="E12" t="n">
-        <v>55530.4852673625</v>
+        <v>57740.5466290565</v>
       </c>
     </row>
     <row r="13">
@@ -1366,13 +1366,13 @@
         <v>17</v>
       </c>
       <c r="C13" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="D13" t="n">
-        <v>5.91244538148531</v>
+        <v>4.34103148571146</v>
       </c>
       <c r="E13" t="n">
-        <v>521.658880940343</v>
+        <v>249.868633941053</v>
       </c>
     </row>
     <row r="14">
@@ -1386,10 +1386,10 @@
         <v>31</v>
       </c>
       <c r="D14" t="n">
-        <v>7.26279853475374</v>
+        <v>17.8885309688549</v>
       </c>
       <c r="E14" t="n">
-        <v>1029.49366483948</v>
+        <v>684.322051325585</v>
       </c>
     </row>
     <row r="15">
@@ -1403,10 +1403,10 @@
         <v>30</v>
       </c>
       <c r="D15" t="n">
-        <v>2.6757566376574</v>
+        <v>2.66345767681024</v>
       </c>
       <c r="E15" t="n">
-        <v>1021.62267886647</v>
+        <v>1042.49991372976</v>
       </c>
     </row>
     <row r="16">
@@ -1434,13 +1434,13 @@
         <v>23</v>
       </c>
       <c r="C17" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="D17" t="n">
-        <v>1.55601404266236</v>
+        <v>1.92277733046749</v>
       </c>
       <c r="E17" t="n">
-        <v>5061.21321793091</v>
+        <v>2103.174118453</v>
       </c>
     </row>
     <row r="18">
@@ -1468,13 +1468,13 @@
         <v>23</v>
       </c>
       <c r="C19" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="D19" t="n">
-        <v>2.52831076732444</v>
+        <v>2.70630202222186</v>
       </c>
       <c r="E19" t="n">
-        <v>4016.24392719755</v>
+        <v>3622.00955535986</v>
       </c>
     </row>
     <row r="20">
@@ -1488,10 +1488,10 @@
         <v>35</v>
       </c>
       <c r="D20" t="n">
-        <v>3.23488709521482</v>
+        <v>3.23441633610315</v>
       </c>
       <c r="E20" t="n">
-        <v>1637.46763124693</v>
+        <v>1638.11793719671</v>
       </c>
     </row>
     <row r="21">
@@ -1522,10 +1522,10 @@
         <v>28</v>
       </c>
       <c r="D22" t="n">
-        <v>15.4607994636716</v>
+        <v>15.4607994636717</v>
       </c>
       <c r="E22" t="n">
-        <v>163.934353869879</v>
+        <v>163.934353869906</v>
       </c>
     </row>
   </sheetData>
@@ -1604,16 +1604,16 @@
         <v>6</v>
       </c>
       <c r="B4" t="n">
-        <v>0.593818056246074</v>
+        <v>0.593818058710427</v>
       </c>
       <c r="C4" t="n">
-        <v>1.31801984955663</v>
+        <v>1.31801985854874</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.22634660093194</v>
+        <v>-0.226346599129612</v>
       </c>
       <c r="E4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F4" t="s">
         <v>4</v>
@@ -1633,7 +1633,7 @@
         <v>-0.205781637181627</v>
       </c>
       <c r="E5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F5" t="s">
         <v>4</v>
@@ -1673,7 +1673,7 @@
         <v>-0.0877868514797552</v>
       </c>
       <c r="E7" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F7" t="s">
         <v>4</v>
@@ -1693,7 +1693,7 @@
         <v>-0.281551197110188</v>
       </c>
       <c r="E8" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F8" t="s">
         <v>11</v>
@@ -1724,16 +1724,16 @@
         <v>13</v>
       </c>
       <c r="B10" t="n">
-        <v>0.203899198184402</v>
+        <v>0.203899199153672</v>
       </c>
       <c r="C10" t="n">
-        <v>8.51681481550408</v>
+        <v>8.51681486409554</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.690584482043215</v>
+        <v>-0.690584479978721</v>
       </c>
       <c r="E10" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F10" t="s">
         <v>11</v>
@@ -1744,13 +1744,13 @@
         <v>14</v>
       </c>
       <c r="B11" t="n">
-        <v>0.139187456422384</v>
+        <v>0.139324761711829</v>
       </c>
       <c r="C11" t="n">
-        <v>2.13890275428367</v>
+        <v>2.13851126674038</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.856399901593301</v>
+        <v>-0.855971691048192</v>
       </c>
       <c r="E11" t="s">
         <v>36</v>
@@ -1784,13 +1784,13 @@
         <v>16</v>
       </c>
       <c r="B13" t="n">
-        <v>0.486996377527185</v>
+        <v>0.49675036211565</v>
       </c>
       <c r="C13" t="n">
-        <v>5.54954574978561</v>
+        <v>5.27889248759791</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.312474269228498</v>
+        <v>-0.303861807630786</v>
       </c>
       <c r="E13" t="s">
         <v>37</v>
@@ -1804,13 +1804,13 @@
         <v>18</v>
       </c>
       <c r="B14" t="n">
-        <v>0.138127084649609</v>
+        <v>0.0766029113928961</v>
       </c>
       <c r="C14" t="n">
-        <v>5.91244538148531</v>
+        <v>4.34103148571146</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.859721154436951</v>
+        <v>-1.11575472412926</v>
       </c>
       <c r="E14" t="s">
         <v>36</v>
@@ -1824,16 +1824,16 @@
         <v>19</v>
       </c>
       <c r="B15" t="n">
-        <v>0.348450117558607</v>
+        <v>0.321531250827086</v>
       </c>
       <c r="C15" t="n">
-        <v>7.26279853475374</v>
+        <v>17.8885309688549</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.457859384623648</v>
+        <v>-0.492776809980265</v>
       </c>
       <c r="E15" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F15" t="s">
         <v>17</v>
@@ -1844,16 +1844,16 @@
         <v>20</v>
       </c>
       <c r="B16" t="n">
-        <v>0.486111369628677</v>
+        <v>0.491166057056667</v>
       </c>
       <c r="C16" t="n">
-        <v>2.6757566376574</v>
+        <v>2.66345767681024</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.313264221119964</v>
+        <v>-0.308771653557316</v>
       </c>
       <c r="E16" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F16" t="s">
         <v>17</v>
@@ -1864,13 +1864,13 @@
         <v>21</v>
       </c>
       <c r="B17" t="n">
-        <v>0.307583822489706</v>
+        <v>0.326998239324576</v>
       </c>
       <c r="C17" t="n">
-        <v>0.708060899050319</v>
+        <v>0.695767449023808</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.512036510184687</v>
+        <v>-0.485454585730172</v>
       </c>
       <c r="E17" t="s">
         <v>36</v>
@@ -1904,13 +1904,13 @@
         <v>24</v>
       </c>
       <c r="B19" t="n">
-        <v>0.124399328837739</v>
+        <v>0.0665073692658114</v>
       </c>
       <c r="C19" t="n">
-        <v>1.55601404266236</v>
+        <v>1.92277733046749</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.905181962754949</v>
+        <v>-1.17713023057417</v>
       </c>
       <c r="E19" t="s">
         <v>36</v>
@@ -1944,13 +1944,13 @@
         <v>26</v>
       </c>
       <c r="B21" t="n">
-        <v>0.246482374091248</v>
+        <v>0.25364195600278</v>
       </c>
       <c r="C21" t="n">
-        <v>2.52831076732444</v>
+        <v>2.70630202222186</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.608214131594058</v>
+        <v>-0.59577890633692</v>
       </c>
       <c r="E21" t="s">
         <v>36</v>
@@ -1964,13 +1964,13 @@
         <v>27</v>
       </c>
       <c r="B22" t="n">
-        <v>0.249254235374948</v>
+        <v>0.249328543696683</v>
       </c>
       <c r="C22" t="n">
-        <v>3.23488709521482</v>
+        <v>3.23441633610315</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.603357453339913</v>
+        <v>-0.603227999633599</v>
       </c>
       <c r="E22" t="s">
         <v>36</v>
